--- a/alianza/Informe_Financiero_ALIANZA_DEL_ACERO_INFORME2_09062026_AJUSTADO_A_10_AÑOS_CON_GUIA.xlsx
+++ b/alianza/Informe_Financiero_ALIANZA_DEL_ACERO_INFORME2_09062026_AJUSTADO_A_10_AÑOS_CON_GUIA.xlsx
@@ -43439,7 +43439,7 @@
     <tabColor rgb="FF2E75B6"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O115"/>
+  <dimension ref="A1:O116"/>
   <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -43563,7 +43563,7 @@
       <c r="N6" s="341"/>
       <c r="O6" s="341"/>
     </row>
-    <row r="7" ht="17.2" customHeight="1">
+    <row r="7" ht="30.4" customHeight="1">
       <c r="B7" s="344">
         <v>1</v>
       </c>
@@ -43574,11 +43574,11 @@
       </c>
       <c r="D7" s="342" t="inlineStr">
         <is>
-          <t>Producción!D28 − Ej_Producción!O33</t>
+          <t>Producción!D28 − SUMA(Ej_Producción!C22:N32)</t>
         </is>
       </c>
       <c r="E7" s="350">
-        <f>ROUND('Producción'!D28-'Ej_Producción'!O33,2)</f>
+        <f>ROUND('Producción'!D28-SUM('Ej_Producción'!C22:N32),2)</f>
         <v>0.0</v>
       </c>
       <c r="F7" s="344" t="inlineStr">
@@ -43592,7 +43592,7 @@
       </c>
       <c r="H7" s="342" t="inlineStr">
         <is>
-          <t>B4 (Producción!D26) y C1-C2: revisar que Producción!D6:D26 (filas pares) tomen Ej_Producción!O22:O32.</t>
+          <t>B4 (totales Ej_Producción!O31:O32 y Producción!D26) y C1-C2: revisar que Producción!D6:D26 (filas pares) tomen Ej_Producción!O22:O32.</t>
         </is>
       </c>
       <c r="I7" s="342"/>
@@ -43603,7 +43603,7 @@
       <c r="N7" s="342"/>
       <c r="O7" s="342"/>
     </row>
-    <row r="8" ht="17.2" customHeight="1">
+    <row r="8" ht="30.4" customHeight="1">
       <c r="B8" s="344">
         <v>2</v>
       </c>
@@ -43614,11 +43614,11 @@
       </c>
       <c r="D8" s="342" t="inlineStr">
         <is>
-          <t>Producción!E28 − Ej_Producción!AD33</t>
+          <t>Producción!E28 − SUMA(Ej_Producción!R22:AC32)</t>
         </is>
       </c>
       <c r="E8" s="350">
-        <f>ROUND('Producción'!E28-'Ej_Producción'!AD33,2)</f>
+        <f>ROUND('Producción'!E28-SUM('Ej_Producción'!R22:AC32),2)</f>
         <v>0.0</v>
       </c>
       <c r="F8" s="344" t="inlineStr">
@@ -43654,11 +43654,11 @@
       </c>
       <c r="D9" s="342" t="inlineStr">
         <is>
-          <t>|Producción!D29 − Ej_Producción!O48| + |E29 − AD48|</t>
+          <t>|Producción!D29 − SUMA(Ej_Producción!C37:N47)| + |E29 − SUMA(R37:AC47)|</t>
         </is>
       </c>
       <c r="E9" s="350">
-        <f>ROUND(ABS('Producción'!D29-'Ej_Producción'!O48)+ABS('Producción'!E29-'Ej_Producción'!AD48),2)</f>
+        <f>ROUND(ABS('Producción'!D29-SUM('Ej_Producción'!C37:N47))+ABS('Producción'!E29-SUM('Ej_Producción'!R37:AC47)),2)</f>
         <v>0.0</v>
       </c>
       <c r="F9" s="344" t="inlineStr">
@@ -43672,7 +43672,7 @@
       </c>
       <c r="H9" s="342" t="inlineStr">
         <is>
-          <t>C1-C3: revisar Ej_Producción filas 37-47 (ventas).</t>
+          <t>B4 (totales Ej_Producción!O46:O47) y C1-C3: revisar Ej_Producción filas 37-47 (ventas).</t>
         </is>
       </c>
       <c r="I9" s="342"/>
@@ -43712,7 +43712,7 @@
       </c>
       <c r="H10" s="342" t="inlineStr">
         <is>
-          <t>C1-C3: revisar precios Ej_Ingresos!C8:AC18 y que Ingresos!D/E tomen las columnas O/AD.</t>
+          <t>C1-C3: revisar precios Ej_Ingresos!C8:AC18 y que Ingresos!D/E tomen las columnas O/AD. Si Steel Frame o Accesorios venden en 2026, verificar los totales Ej_Producción!O46:O47 (paso B4).</t>
         </is>
       </c>
       <c r="I10" s="342"/>
@@ -43872,7 +43872,7 @@
       </c>
       <c r="H14" s="342" t="inlineStr">
         <is>
-          <t>B4 y B5: Producción!D26 vinculada y Ej_Costos!O18:O19 con fórmula.</t>
+          <t>B4 (totales Ej_Producción!O31:O32 y Producción!D26) y B5 (Ej_Costos!O18:O19 con fórmula).</t>
         </is>
       </c>
       <c r="I14" s="342"/>
@@ -43889,16 +43889,16 @@
       </c>
       <c r="C15" s="343" t="inlineStr">
         <is>
-          <t>Producción de Accesorios del año 1 vinculada</t>
+          <t>Steel Frame y Accesorios del año 1 vinculados</t>
         </is>
       </c>
       <c r="D15" s="342" t="inlineStr">
         <is>
-          <t>¿Producción!D26 es fórmula?</t>
+          <t>¿Producción!D26 y Ej_Producción!O31, O32, O46 y O47 son fórmulas?</t>
         </is>
       </c>
       <c r="E15" s="344" t="b">
-        <f>_xlfn.ISFORMULA('Producción'!D26)</f>
+        <f>AND(_xlfn.ISFORMULA('Producción'!D26),_xlfn.ISFORMULA('Ej_Producción'!O31),_xlfn.ISFORMULA('Ej_Producción'!O32),_xlfn.ISFORMULA('Ej_Producción'!O46),_xlfn.ISFORMULA('Ej_Producción'!O47))</f>
         <v>0</v>
       </c>
       <c r="F15" s="344" t="inlineStr">
@@ -43912,7 +43912,7 @@
       </c>
       <c r="H15" s="342" t="inlineStr">
         <is>
-          <t>B4: escribir =+Ej_Producción!O32 en Producción!D26.</t>
+          <t>B4: crear los totales Ej_Producción!O31, O32, O46 y O47 (hoy vacíos) y escribir =+Ej_Producción!O32 en Producción!D26.</t>
         </is>
       </c>
       <c r="I15" s="342"/>
@@ -44003,36 +44003,36 @@
       <c r="N17" s="342"/>
       <c r="O17" s="342"/>
     </row>
-    <row r="18" ht="30.4" customHeight="1">
+    <row r="18" ht="43.6" customHeight="1">
       <c r="B18" s="344">
         <v>12</v>
       </c>
       <c r="C18" s="343" t="inlineStr">
         <is>
-          <t>Impuesto maquila del flujo 2028 = Resultados (USD)</t>
+          <t>Impuesto maquila pagado 2028-2035 = Resultados (USD)</t>
         </is>
       </c>
       <c r="D18" s="342" t="inlineStr">
         <is>
-          <t>Ej_Flujo!AO24 − Resultados!E13</t>
+          <t>Ej_Flujo fila 24 (totales 2028-2035) − (impuesto dic-2027 + SUMA(Resultados!E13:L13) − 1/12 de L13)</t>
         </is>
       </c>
       <c r="E18" s="350">
-        <f>ROUND('Ej_Flujo'!AO24-'Resultados'!E13,2)</f>
-        <v>-23755.41</v>
+        <f>ROUND(('Ej_Flujo'!AO24+'Ej_Flujo'!BB24+'Ej_Flujo'!BO24+'Ej_Flujo'!CB24+'Ej_Flujo'!CO24+'Ej_Flujo'!DB24+'Ej_Flujo'!DO24+'Ej_Flujo'!EB24)-('Ej_Resultados'!AC18+SUM('Resultados'!E13:L13)-'Resultados'!L13/12),2)</f>
+        <v>-612871.03</v>
       </c>
       <c r="F18" s="344" t="inlineStr">
         <is>
-          <t>≈ 0 (± 500)</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G18" s="344" t="str">
-        <f>IF(ABS(E18)&lt;500,"OK","REVISAR")</f>
+        <f>IF(ABS(E18)&lt;1,"OK","REVISAR")</f>
         <v>REVISAR</v>
       </c>
       <c r="H18" s="342" t="inlineStr">
         <is>
-          <t>B2: vincular Ej_Flujo!AC24:EA24 al 1% de las ventas de cada año.</t>
+          <t>B2: vincular Ej_Flujo!AC24:EA24 al 1% de las ventas de cada año (se paga al mes siguiente).</t>
         </is>
       </c>
       <c r="I18" s="342"/>
@@ -44072,7 +44072,7 @@
       </c>
       <c r="H19" s="342" t="inlineStr">
         <is>
-          <t>E3: re-dimensionar los préstamos CP (Ej_Flujo fila 8) hasta que el saldo no sea negativo.</t>
+          <t>E3: re-dimensionar los préstamos CP (Ej_Flujo fila 8) hasta que el saldo no sea negativo. Es normal que siga en REVISAR hasta terminar la fase E: la fase B lo empeora.</t>
         </is>
       </c>
       <c r="I19" s="342"/>
@@ -44094,11 +44094,11 @@
       </c>
       <c r="D20" s="342" t="inlineStr">
         <is>
-          <t>Totales anuales de Ej_Flujo fila 8 − fila 16 (2027-2035)</t>
+          <t>Ej_Flujo fila 8 − fila 16, 2026-2035 (sin L16, que es la devolución a CIE S.A.)</t>
         </is>
       </c>
       <c r="E20" s="350">
-        <f>ROUND(('Ej_Flujo'!AB8+'Ej_Flujo'!AO8+'Ej_Flujo'!BB8+'Ej_Flujo'!BO8+'Ej_Flujo'!CB8+'Ej_Flujo'!CO8+'Ej_Flujo'!DB8+'Ej_Flujo'!DO8+'Ej_Flujo'!EB8)-('Ej_Flujo'!AB16+'Ej_Flujo'!AO16+'Ej_Flujo'!BB16+'Ej_Flujo'!BO16+'Ej_Flujo'!CB16+'Ej_Flujo'!CO16+'Ej_Flujo'!DB16+'Ej_Flujo'!DO16+'Ej_Flujo'!EB16),2)</f>
+        <f>ROUND(('Ej_Flujo'!O8+'Ej_Flujo'!AB8+'Ej_Flujo'!AO8+'Ej_Flujo'!BB8+'Ej_Flujo'!BO8+'Ej_Flujo'!CB8+'Ej_Flujo'!CO8+'Ej_Flujo'!DB8+'Ej_Flujo'!DO8+'Ej_Flujo'!EB8)-(SUM('Ej_Flujo'!C16:K16)+SUM('Ej_Flujo'!M16:N16)+'Ej_Flujo'!AB16+'Ej_Flujo'!AO16+'Ej_Flujo'!BB16+'Ej_Flujo'!BO16+'Ej_Flujo'!CB16+'Ej_Flujo'!CO16+'Ej_Flujo'!DB16+'Ej_Flujo'!DO16+'Ej_Flujo'!EB16),2)</f>
         <v>0.0</v>
       </c>
       <c r="F20" s="344" t="inlineStr">
@@ -44374,11 +44374,11 @@
       </c>
       <c r="D27" s="342" t="inlineStr">
         <is>
-          <t>¿Dashboard!C12 es número (no texto)?</t>
+          <t>¿Dashboard!C12 es fórmula y da un número?</t>
         </is>
       </c>
       <c r="E27" s="344" t="b">
-        <f>ISNUMBER('Dashboard'!C12)</f>
+        <f>AND(_xlfn.ISFORMULA('Dashboard'!C12),ISNUMBER('Dashboard'!C12))</f>
         <v>0</v>
       </c>
       <c r="F27" s="344" t="inlineStr">
@@ -44563,162 +44563,164 @@
       <c r="N31" s="342"/>
       <c r="O31" s="342"/>
     </row>
-    <row r="33">
-      <c r="C33" s="343" t="inlineStr">
+    <row r="32" ht="43.6" customHeight="1">
+      <c r="B32" s="344">
+        <v>26</v>
+      </c>
+      <c r="C32" s="343" t="inlineStr">
+        <is>
+          <t>Egresos operativos 2028-2035 del flujo = Costos (USD)</t>
+        </is>
+      </c>
+      <c r="D32" s="342" t="inlineStr">
+        <is>
+          <t>Ej_Flujo filas 13, 19, 21 y 22 (totales 2028-2035) − Costos!F:M filas 7-16 y 20-27</t>
+        </is>
+      </c>
+      <c r="E32" s="350">
+        <f>ROUND(('Ej_Flujo'!AO13+'Ej_Flujo'!AO19+'Ej_Flujo'!AO21+'Ej_Flujo'!AO22+'Ej_Flujo'!BB13+'Ej_Flujo'!BB19+'Ej_Flujo'!BB21+'Ej_Flujo'!BB22+'Ej_Flujo'!BO13+'Ej_Flujo'!BO19+'Ej_Flujo'!BO21+'Ej_Flujo'!BO22+'Ej_Flujo'!CB13+'Ej_Flujo'!CB19+'Ej_Flujo'!CB21+'Ej_Flujo'!CB22+'Ej_Flujo'!CO13+'Ej_Flujo'!CO19+'Ej_Flujo'!CO21+'Ej_Flujo'!CO22+'Ej_Flujo'!DB13+'Ej_Flujo'!DB19+'Ej_Flujo'!DB21+'Ej_Flujo'!DB22+'Ej_Flujo'!DO13+'Ej_Flujo'!DO19+'Ej_Flujo'!DO21+'Ej_Flujo'!DO22+'Ej_Flujo'!EB13+'Ej_Flujo'!EB19+'Ej_Flujo'!EB21+'Ej_Flujo'!EB22)-(SUM('Costos'!F7:M16)+SUM('Costos'!F20:M27)),2)</f>
+        <v>-1617237.59</v>
+      </c>
+      <c r="F32" s="344" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G32" s="344" t="str">
+        <f>IF(ABS(E32)&lt;1,"OK","REVISAR")</f>
+        <v>REVISAR</v>
+      </c>
+      <c r="H32" s="342" t="inlineStr">
+        <is>
+          <t>B8: vincular Ej_Flujo filas 13, 19, 21 y 22 de 2028-2035 a la hoja Costos (hoy son valores pegados).</t>
+        </is>
+      </c>
+      <c r="I32" s="342"/>
+      <c r="J32" s="342"/>
+      <c r="K32" s="342"/>
+      <c r="L32" s="342"/>
+      <c r="M32" s="342"/>
+      <c r="N32" s="342"/>
+      <c r="O32" s="342"/>
+    </row>
+    <row r="34">
+      <c r="C34" s="343" t="inlineStr">
         <is>
           <t>Resumen de controles</t>
         </is>
       </c>
-      <c r="D33" s="343" t="str">
-        <f>COUNTIF(G7:G31,"OK")&amp;" de "&amp;ROWS(G7:G31)&amp;" en OK"</f>
-        <v>18 de 25 en OK</v>
-      </c>
-      <c r="E33" s="349" t="inlineStr">
-        <is>
-          <t>Con el libro tal como llegó (09/06/2026), los controles en REVISAR señalan las correcciones de la fase B.</t>
-        </is>
-      </c>
-      <c r="F33" s="349"/>
-      <c r="G33" s="349"/>
-      <c r="H33" s="349"/>
-      <c r="I33" s="349"/>
-      <c r="J33" s="349"/>
-      <c r="K33" s="349"/>
-      <c r="L33" s="349"/>
-      <c r="M33" s="349"/>
-      <c r="N33" s="349"/>
-      <c r="O33" s="349"/>
-    </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="B35" s="339" t="inlineStr">
+      <c r="D34" s="343" t="str">
+        <f>COUNTIF(G7:G32,"OK")&amp;" de "&amp;ROWS(G7:G32)&amp;" en OK"</f>
+        <v>18 de 26 en OK</v>
+      </c>
+      <c r="E34" s="349" t="inlineStr">
+        <is>
+          <t>Con el libro tal como llegó (09/06/2026) hay 8 controles en REVISAR: el 9, 11, 12, 17, 21, 22 y 26 se corrigen en la fase B (verificado: después de B1-B8 quedan 25 de 26 en OK); el 13 (caja) se corrige en E3 y E5, y empeora con la fase B.</t>
+        </is>
+      </c>
+      <c r="F34" s="349"/>
+      <c r="G34" s="349"/>
+      <c r="H34" s="349"/>
+      <c r="I34" s="349"/>
+      <c r="J34" s="349"/>
+      <c r="K34" s="349"/>
+      <c r="L34" s="349"/>
+      <c r="M34" s="349"/>
+      <c r="N34" s="349"/>
+      <c r="O34" s="349"/>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="B36" s="339" t="inlineStr">
         <is>
           <t>2. INDICADORES PARA EL POWERPOINT (tablas y textos)</t>
         </is>
       </c>
-      <c r="C35" s="339"/>
-      <c r="D35" s="339"/>
-      <c r="E35" s="339"/>
-      <c r="F35" s="339"/>
-      <c r="G35" s="339"/>
-      <c r="H35" s="339"/>
-      <c r="I35" s="339"/>
-      <c r="J35" s="339"/>
-      <c r="K35" s="339"/>
-      <c r="L35" s="339"/>
-      <c r="M35" s="339"/>
-      <c r="N35" s="339"/>
-      <c r="O35" s="339"/>
-    </row>
-    <row r="36" ht="28" customHeight="1">
-      <c r="B36" s="340" t="inlineStr">
+      <c r="C36" s="339"/>
+      <c r="D36" s="339"/>
+      <c r="E36" s="339"/>
+      <c r="F36" s="339"/>
+      <c r="G36" s="339"/>
+      <c r="H36" s="339"/>
+      <c r="I36" s="339"/>
+      <c r="J36" s="339"/>
+      <c r="K36" s="339"/>
+      <c r="L36" s="339"/>
+      <c r="M36" s="339"/>
+      <c r="N36" s="339"/>
+      <c r="O36" s="339"/>
+    </row>
+    <row r="37" ht="28" customHeight="1">
+      <c r="B37" s="340" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C36" s="340" t="inlineStr">
+      <c r="C37" s="340" t="inlineStr">
         <is>
           <t>Dato</t>
         </is>
       </c>
-      <c r="D36" s="340" t="inlineStr">
+      <c r="D37" s="340" t="inlineStr">
         <is>
           <t>Celda o cálculo de origen</t>
         </is>
       </c>
-      <c r="E36" s="340" t="inlineStr">
+      <c r="E37" s="340" t="inlineStr">
         <is>
           <t>Libro (vivo)</t>
         </is>
       </c>
-      <c r="F36" s="340" t="inlineStr">
+      <c r="F37" s="340" t="inlineStr">
         <is>
           <t>PPT jun-2026</t>
         </is>
       </c>
-      <c r="G36" s="340" t="inlineStr">
+      <c r="G37" s="340" t="inlineStr">
         <is>
           <t>Diferencia</t>
         </is>
       </c>
-      <c r="H36" s="341" t="inlineStr">
+      <c r="H37" s="341" t="inlineStr">
         <is>
           <t>Diapositivas y observaciones</t>
         </is>
       </c>
-      <c r="I36" s="341"/>
-      <c r="J36" s="341"/>
-      <c r="K36" s="341"/>
-      <c r="L36" s="341"/>
-      <c r="M36" s="341"/>
-      <c r="N36" s="341"/>
-      <c r="O36" s="341"/>
-    </row>
-    <row r="37" ht="17.2" customHeight="1">
-      <c r="B37" s="344">
+      <c r="I37" s="341"/>
+      <c r="J37" s="341"/>
+      <c r="K37" s="341"/>
+      <c r="L37" s="341"/>
+      <c r="M37" s="341"/>
+      <c r="N37" s="341"/>
+      <c r="O37" s="341"/>
+    </row>
+    <row r="38" ht="17.2" customHeight="1">
+      <c r="B38" s="344">
         <v>1</v>
       </c>
-      <c r="C37" s="343" t="inlineStr">
+      <c r="C38" s="343" t="inlineStr">
         <is>
           <t>Inversión total (USD)</t>
         </is>
       </c>
-      <c r="D37" s="342" t="inlineStr">
+      <c r="D38" s="342" t="inlineStr">
         <is>
           <t>Inversión!C7</t>
         </is>
       </c>
-      <c r="E37" s="350">
+      <c r="E38" s="350">
         <f>'Inversión'!C7</f>
         <v>5074594</v>
       </c>
-      <c r="F37" s="352">
+      <c r="F38" s="352">
         <v>5074594</v>
-      </c>
-      <c r="G37" s="350">
-        <f>IF(ISNUMBER(E37),E37-F37,"")</f>
-        <v>0</v>
-      </c>
-      <c r="H37" s="342" t="inlineStr">
-        <is>
-          <t>Diap. 3. Igual en plan y actualizado.</t>
-        </is>
-      </c>
-      <c r="I37" s="342"/>
-      <c r="J37" s="342"/>
-      <c r="K37" s="342"/>
-      <c r="L37" s="342"/>
-      <c r="M37" s="342"/>
-      <c r="N37" s="342"/>
-      <c r="O37" s="342"/>
-    </row>
-    <row r="38" ht="17.2" customHeight="1">
-      <c r="B38" s="344">
-        <v>2</v>
-      </c>
-      <c r="C38" s="343" t="inlineStr">
-        <is>
-          <t>VAN con financiamiento (USD)</t>
-        </is>
-      </c>
-      <c r="D38" s="342" t="inlineStr">
-        <is>
-          <t>VAN-TIR!C24</t>
-        </is>
-      </c>
-      <c r="E38" s="350">
-        <f>'VAN-TIR'!C24</f>
-        <v>2844947.7596976636</v>
-      </c>
-      <c r="F38" s="352">
-        <v>2844948</v>
       </c>
       <c r="G38" s="350">
         <f>IF(ISNUMBER(E38),E38-F38,"")</f>
-        <v>-0.24030233640223742</v>
+        <v>0</v>
       </c>
       <c r="H38" s="342" t="inlineStr">
         <is>
-          <t>Diap. 2, 3, 9 y 13.</t>
+          <t>Diap. 3. Igual en plan y actualizado.</t>
         </is>
       </c>
       <c r="I38" s="342"/>
@@ -44731,32 +44733,32 @@
     </row>
     <row r="39" ht="17.2" customHeight="1">
       <c r="B39" s="344">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C39" s="343" t="inlineStr">
         <is>
-          <t>TIR con financiamiento</t>
+          <t>VAN con financiamiento (USD)</t>
         </is>
       </c>
       <c r="D39" s="342" t="inlineStr">
         <is>
-          <t>VAN-TIR!C23</t>
-        </is>
-      </c>
-      <c r="E39" s="357">
-        <f>'VAN-TIR'!C23</f>
-        <v>0.1491544557454163</v>
-      </c>
-      <c r="F39" s="353">
-        <v>0.149</v>
-      </c>
-      <c r="G39" s="357">
+          <t>VAN-TIR!C24</t>
+        </is>
+      </c>
+      <c r="E39" s="350">
+        <f>'VAN-TIR'!C24</f>
+        <v>2844947.7596976636</v>
+      </c>
+      <c r="F39" s="352">
+        <v>2844948</v>
+      </c>
+      <c r="G39" s="350">
         <f>IF(ISNUMBER(E39),E39-F39,"")</f>
-        <v>0.0001544557454163098</v>
+        <v>-0.24030233640223742</v>
       </c>
       <c r="H39" s="342" t="inlineStr">
         <is>
-          <t>Diap. 2, 3, 9 y 13. Mostrar con 1 decimal (14,9%).</t>
+          <t>Diap. 2, 3, 9 y 13.</t>
         </is>
       </c>
       <c r="I39" s="342"/>
@@ -44769,32 +44771,32 @@
     </row>
     <row r="40" ht="17.2" customHeight="1">
       <c r="B40" s="344">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C40" s="343" t="inlineStr">
         <is>
-          <t>WACC</t>
+          <t>TIR con financiamiento</t>
         </is>
       </c>
       <c r="D40" s="342" t="inlineStr">
         <is>
-          <t>VAN-TIR!C22</t>
+          <t>VAN-TIR!C23</t>
         </is>
       </c>
       <c r="E40" s="357">
-        <f>'VAN-TIR'!C22</f>
-        <v>0.09874142837830967</v>
+        <f>'VAN-TIR'!C23</f>
+        <v>0.1491544557454163</v>
       </c>
       <c r="F40" s="353">
-        <v>0.0987</v>
+        <v>0.149</v>
       </c>
       <c r="G40" s="357">
         <f>IF(ISNUMBER(E40),E40-F40,"")</f>
-        <v>4.142837830967139e-05</v>
+        <v>0.0001544557454163098</v>
       </c>
       <c r="H40" s="342" t="inlineStr">
         <is>
-          <t>Diap. 3, 9 y 13. No cambia si no cambia el financiamiento.</t>
+          <t>Diap. 2, 3, 9 y 13. Mostrar con 1 decimal (14,9%).</t>
         </is>
       </c>
       <c r="I40" s="342"/>
@@ -44807,32 +44809,32 @@
     </row>
     <row r="41" ht="17.2" customHeight="1">
       <c r="B41" s="344">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C41" s="343" t="inlineStr">
         <is>
-          <t>Spread TIR − WACC (puntos porcentuales)</t>
+          <t>WACC</t>
         </is>
       </c>
       <c r="D41" s="342" t="inlineStr">
         <is>
-          <t>VAN-TIR!C23 − C22</t>
+          <t>VAN-TIR!C22</t>
         </is>
       </c>
       <c r="E41" s="357">
-        <f>'VAN-TIR'!C23-'VAN-TIR'!C22</f>
-        <v>0.050413027367106636</v>
+        <f>'VAN-TIR'!C22</f>
+        <v>0.09874142837830967</v>
       </c>
       <c r="F41" s="353">
-        <v>0.05</v>
+        <v>0.0987</v>
       </c>
       <c r="G41" s="357">
         <f>IF(ISNUMBER(E41),E41-F41,"")</f>
-        <v>0.0004130273671066331</v>
+        <v>4.142837830967139e-05</v>
       </c>
       <c r="H41" s="342" t="inlineStr">
         <is>
-          <t>Diap. 9 y 13 («5,0 pp»). Plan: 5,3 pp.</t>
+          <t>Diap. 3, 9 y 13. No cambia si no cambia el financiamiento.</t>
         </is>
       </c>
       <c r="I41" s="342"/>
@@ -44845,32 +44847,32 @@
     </row>
     <row r="42" ht="17.2" customHeight="1">
       <c r="B42" s="344">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C42" s="343" t="inlineStr">
         <is>
-          <t>VAN actualizado − VAN plan (USD)</t>
+          <t>Spread TIR − WACC (puntos porcentuales)</t>
         </is>
       </c>
       <c r="D42" s="342" t="inlineStr">
         <is>
-          <t>VAN-TIR!C24 − VAN plan (sección 4)</t>
-        </is>
-      </c>
-      <c r="E42" s="350">
-        <f>'VAN-TIR'!C24-E102</f>
-        <v>1419.7596976635978</v>
-      </c>
-      <c r="F42" s="352">
-        <v>1400</v>
-      </c>
-      <c r="G42" s="350">
+          <t>VAN-TIR!C23 − C22</t>
+        </is>
+      </c>
+      <c r="E42" s="357">
+        <f>'VAN-TIR'!C23-'VAN-TIR'!C22</f>
+        <v>0.050413027367106636</v>
+      </c>
+      <c r="F42" s="353">
+        <v>0.05</v>
+      </c>
+      <c r="G42" s="357">
         <f>IF(ISNUMBER(E42),E42-F42,"")</f>
-        <v>19.759697663597763</v>
+        <v>0.0004130273671066331</v>
       </c>
       <c r="H42" s="342" t="inlineStr">
         <is>
-          <t>Diap. 9 («Mejora VAN +USD 1,4K»).</t>
+          <t>Diap. 9 y 13 («5,0 pp»). Plan: 5,3 pp.</t>
         </is>
       </c>
       <c r="I42" s="342"/>
@@ -44883,32 +44885,32 @@
     </row>
     <row r="43" ht="17.2" customHeight="1">
       <c r="B43" s="344">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C43" s="343" t="inlineStr">
         <is>
-          <t>VAN actualizado vs plan (%)</t>
+          <t>VAN actualizado − VAN plan (USD)</t>
         </is>
       </c>
       <c r="D43" s="342" t="inlineStr">
         <is>
-          <t>VAN-TIR!C24 / VAN plan − 1</t>
-        </is>
-      </c>
-      <c r="E43" s="357">
-        <f>'VAN-TIR'!C24/E102-1</f>
-        <v>0.0004992951353612884</v>
-      </c>
-      <c r="F43" s="353">
-        <v>0.0005</v>
-      </c>
-      <c r="G43" s="357">
+          <t>VAN-TIR!C24 − VAN plan (sección 4)</t>
+        </is>
+      </c>
+      <c r="E43" s="350">
+        <f>'VAN-TIR'!C24-E103</f>
+        <v>1419.7596976635978</v>
+      </c>
+      <c r="F43" s="352">
+        <v>1400</v>
+      </c>
+      <c r="G43" s="350">
         <f>IF(ISNUMBER(E43),E43-F43,"")</f>
-        <v>-7.048646387115658e-07</v>
+        <v>19.759697663597763</v>
       </c>
       <c r="H43" s="342" t="inlineStr">
         <is>
-          <t>Diap. 2, 3, 9 y 13 («+0,05%»).</t>
+          <t>Diap. 9 («Mejora VAN +USD 1,4K»).</t>
         </is>
       </c>
       <c r="I43" s="342"/>
@@ -44921,32 +44923,32 @@
     </row>
     <row r="44" ht="17.2" customHeight="1">
       <c r="B44" s="344">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C44" s="343" t="inlineStr">
         <is>
-          <t>TIR actualizada − TIR plan (pp)</t>
+          <t>VAN actualizado vs plan (%)</t>
         </is>
       </c>
       <c r="D44" s="342" t="inlineStr">
         <is>
-          <t>VAN-TIR!C23 − TIR plan (sección 4)</t>
+          <t>VAN-TIR!C24 / VAN plan − 1</t>
         </is>
       </c>
       <c r="E44" s="357">
-        <f>'VAN-TIR'!C23-E103</f>
-        <v>-0.002745544254583704</v>
+        <f>'VAN-TIR'!C24/E103-1</f>
+        <v>0.0004992951353612884</v>
       </c>
       <c r="F44" s="353">
-        <v>-0.0029</v>
+        <v>0.0005</v>
       </c>
       <c r="G44" s="357">
         <f>IF(ISNUMBER(E44),E44-F44,"")</f>
-        <v>0.00015445574541629592</v>
+        <v>-7.048646387115658e-07</v>
       </c>
       <c r="H44" s="342" t="inlineStr">
         <is>
-          <t>Diap. 3, 9 y 13. Hoy −0,27 pp (el PPT dice −0,29).</t>
+          <t>Diap. 2, 3, 9 y 13 («+0,05%»).</t>
         </is>
       </c>
       <c r="I44" s="342"/>
@@ -44959,32 +44961,32 @@
     </row>
     <row r="45" ht="17.2" customHeight="1">
       <c r="B45" s="344">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C45" s="343" t="inlineStr">
         <is>
-          <t>Producción año 1 (Tn)</t>
+          <t>TIR actualizada − TIR plan (pp)</t>
         </is>
       </c>
       <c r="D45" s="342" t="inlineStr">
         <is>
-          <t>Ej_Producción!O33</t>
-        </is>
-      </c>
-      <c r="E45" s="350">
-        <f>'Ej_Producción'!O33</f>
-        <v>4315.166</v>
-      </c>
-      <c r="F45" s="352">
-        <v>4315</v>
-      </c>
-      <c r="G45" s="350">
+          <t>VAN-TIR!C23 − TIR plan (sección 4)</t>
+        </is>
+      </c>
+      <c r="E45" s="357">
+        <f>'VAN-TIR'!C23-E104</f>
+        <v>-0.002745544254583704</v>
+      </c>
+      <c r="F45" s="353">
+        <v>-0.0029</v>
+      </c>
+      <c r="G45" s="357">
         <f>IF(ISNUMBER(E45),E45-F45,"")</f>
-        <v>0.16600000000016735</v>
+        <v>0.00015445574541629592</v>
       </c>
       <c r="H45" s="342" t="inlineStr">
         <is>
-          <t>Diap. 2 y 4. Es real hasta el corte + proyección: rotularlo así.</t>
+          <t>Diap. 3, 9 y 13. Hoy −0,27 pp (el PPT dice −0,29).</t>
         </is>
       </c>
       <c r="I45" s="342"/>
@@ -44997,32 +44999,32 @@
     </row>
     <row r="46" ht="17.2" customHeight="1">
       <c r="B46" s="344">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C46" s="343" t="inlineStr">
         <is>
-          <t>Producción año 1 / plan</t>
+          <t>Producción año 1 (Tn)</t>
         </is>
       </c>
       <c r="D46" s="342" t="inlineStr">
         <is>
-          <t>Ej_Producción!P33</t>
-        </is>
-      </c>
-      <c r="E46" s="355">
-        <f>'Ej_Producción'!P33</f>
-        <v>0.3892095246685307</v>
-      </c>
-      <c r="F46" s="353">
-        <v>0.39</v>
-      </c>
-      <c r="G46" s="357">
+          <t>Producción!D28</t>
+        </is>
+      </c>
+      <c r="E46" s="350">
+        <f>'Producción'!D28</f>
+        <v>4315.166</v>
+      </c>
+      <c r="F46" s="352">
+        <v>4315</v>
+      </c>
+      <c r="G46" s="350">
         <f>IF(ISNUMBER(E46),E46-F46,"")</f>
-        <v>-0.0007904753314693092</v>
+        <v>0.16600000000016735</v>
       </c>
       <c r="H46" s="342" t="inlineStr">
         <is>
-          <t>Diap. 2 y 4 («39% del Plan»).</t>
+          <t>Diap. 2 y 4. Es real hasta el corte + proyección: rotularlo así.</t>
         </is>
       </c>
       <c r="I46" s="342"/>
@@ -45035,32 +45037,32 @@
     </row>
     <row r="47" ht="17.2" customHeight="1">
       <c r="B47" s="344">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C47" s="343" t="inlineStr">
         <is>
-          <t>Utilidad neta año 1 (USD)</t>
+          <t>Producción año 1 / plan</t>
         </is>
       </c>
       <c r="D47" s="342" t="inlineStr">
         <is>
-          <t>Resultados!C14</t>
-        </is>
-      </c>
-      <c r="E47" s="350">
-        <f>'Resultados'!C14</f>
-        <v>-334777.752861543</v>
-      </c>
-      <c r="F47" s="352">
-        <v>-335000</v>
-      </c>
-      <c r="G47" s="350">
+          <t>Ej_Producción!P33</t>
+        </is>
+      </c>
+      <c r="E47" s="355">
+        <f>'Ej_Producción'!P33</f>
+        <v>0.3892095246685307</v>
+      </c>
+      <c r="F47" s="353">
+        <v>0.39</v>
+      </c>
+      <c r="G47" s="357">
         <f>IF(ISNUMBER(E47),E47-F47,"")</f>
-        <v>222.24713845702354</v>
+        <v>-0.0007904753314693092</v>
       </c>
       <c r="H47" s="342" t="inlineStr">
         <is>
-          <t>Diap. 7 y 13 («pérdida de USD 335K»).</t>
+          <t>Diap. 2 y 4 («39% del Plan»).</t>
         </is>
       </c>
       <c r="I47" s="342"/>
@@ -45073,32 +45075,32 @@
     </row>
     <row r="48" ht="17.2" customHeight="1">
       <c r="B48" s="344">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C48" s="343" t="inlineStr">
         <is>
-          <t>Producción acumulada 10 años (Tn)</t>
+          <t>Utilidad neta año 1 (USD)</t>
         </is>
       </c>
       <c r="D48" s="342" t="inlineStr">
         <is>
-          <t>SUMA(Producción!D28:M28)</t>
+          <t>Resultados!C14</t>
         </is>
       </c>
       <c r="E48" s="350">
-        <f>SUM('Producción'!D28:M28)</f>
-        <v>161292.166</v>
+        <f>'Resultados'!C14</f>
+        <v>-334777.752861543</v>
       </c>
       <c r="F48" s="352">
-        <v>161000</v>
+        <v>-335000</v>
       </c>
       <c r="G48" s="350">
         <f>IF(ISNUMBER(E48),E48-F48,"")</f>
-        <v>292.16599999999744</v>
+        <v>222.24713845702354</v>
       </c>
       <c r="H48" s="342" t="inlineStr">
         <is>
-          <t>Diap. 3 y 4.</t>
+          <t>Diap. 7 y 13 («pérdida de USD 335K»).</t>
         </is>
       </c>
       <c r="I48" s="342"/>
@@ -45111,32 +45113,32 @@
     </row>
     <row r="49" ht="17.2" customHeight="1">
       <c r="B49" s="344">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C49" s="343" t="inlineStr">
         <is>
-          <t>Producción acumulada vs plan</t>
+          <t>Producción acumulada 10 años (Tn)</t>
         </is>
       </c>
       <c r="D49" s="342" t="inlineStr">
         <is>
-          <t>Acumulado / suma serie plan − 1</t>
-        </is>
-      </c>
-      <c r="E49" s="355">
-        <f>O80/O81-1</f>
-        <v>0.07617792160133452</v>
-      </c>
-      <c r="F49" s="353">
-        <v>0.07</v>
-      </c>
-      <c r="G49" s="357">
+          <t>SUMA(Producción!D28:M28)</t>
+        </is>
+      </c>
+      <c r="E49" s="350">
+        <f>SUM('Producción'!D28:M28)</f>
+        <v>161292.166</v>
+      </c>
+      <c r="F49" s="352">
+        <v>161000</v>
+      </c>
+      <c r="G49" s="350">
         <f>IF(ISNUMBER(E49),E49-F49,"")</f>
-        <v>0.006177921601334513</v>
+        <v>292.16599999999744</v>
       </c>
       <c r="H49" s="342" t="inlineStr">
         <is>
-          <t>Diap. 3, 4 y 13. Hoy +7,6% (el PPT dice +7%).</t>
+          <t>Diap. 3 y 4.</t>
         </is>
       </c>
       <c r="I49" s="342"/>
@@ -45147,34 +45149,34 @@
       <c r="N49" s="342"/>
       <c r="O49" s="342"/>
     </row>
-    <row r="50" ht="17.2" customHeight="1">
+    <row r="50" ht="30.4" customHeight="1">
       <c r="B50" s="344">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C50" s="343" t="inlineStr">
         <is>
-          <t>Ingresos acumulados 10 años (USD)</t>
+          <t>Producción acumulada vs plan</t>
         </is>
       </c>
       <c r="D50" s="342" t="inlineStr">
         <is>
-          <t>SUMA(Ingresos!D28:M28)</t>
-        </is>
-      </c>
-      <c r="E50" s="350">
-        <f>SUM('Ingresos'!D28:M28)</f>
-        <v>215640953.40509626</v>
-      </c>
-      <c r="F50" s="352">
-        <v>217000000</v>
-      </c>
-      <c r="G50" s="350">
+          <t>Acumulado / rótulo plan del PPT (150K Tn) − 1</t>
+        </is>
+      </c>
+      <c r="E50" s="355">
+        <f>O81/E107-1</f>
+        <v>0.07528110666666654</v>
+      </c>
+      <c r="F50" s="353">
+        <v>0.07</v>
+      </c>
+      <c r="G50" s="357">
         <f>IF(ISNUMBER(E50),E50-F50,"")</f>
-        <v>-1359046.5949037373</v>
+        <v>0.005281106666666535</v>
       </c>
       <c r="H50" s="342" t="inlineStr">
         <is>
-          <t>Diap. 3 y 5. El PPT de junio dice 217M; el libro da 215,6M.</t>
+          <t>Diap. 3, 4 y 13. Hoy +7,5% (el PPT dice +7%). Contra la suma de la serie plan del gráfico (149.875 Tn) daría +7,6%: ver sección 4.</t>
         </is>
       </c>
       <c r="I50" s="342"/>
@@ -45187,32 +45189,32 @@
     </row>
     <row r="51" ht="17.2" customHeight="1">
       <c r="B51" s="344">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C51" s="343" t="inlineStr">
         <is>
-          <t>Ingresos acumulados vs plan</t>
+          <t>Ingresos acumulados 10 años (USD)</t>
         </is>
       </c>
       <c r="D51" s="342" t="inlineStr">
         <is>
-          <t>Acumulado / suma serie plan − 1</t>
-        </is>
-      </c>
-      <c r="E51" s="355">
-        <f>O83/O84-1</f>
-        <v>0.20321428540196051</v>
-      </c>
-      <c r="F51" s="353">
-        <v>0.21</v>
-      </c>
-      <c r="G51" s="357">
+          <t>SUMA(Ingresos!D28:M28)</t>
+        </is>
+      </c>
+      <c r="E51" s="350">
+        <f>SUM('Ingresos'!D28:M28)</f>
+        <v>215640953.40509626</v>
+      </c>
+      <c r="F51" s="352">
+        <v>217000000</v>
+      </c>
+      <c r="G51" s="350">
         <f>IF(ISNUMBER(E51),E51-F51,"")</f>
-        <v>-0.006785714598039477</v>
+        <v>-1359046.5949037373</v>
       </c>
       <c r="H51" s="342" t="inlineStr">
         <is>
-          <t>Diap. 3, 5, 9 y 13. Hoy +20,3% (el PPT dice +21%).</t>
+          <t>Diap. 3 y 5. El PPT de junio dice 217M; el libro da 215,6M.</t>
         </is>
       </c>
       <c r="I51" s="342"/>
@@ -45223,34 +45225,34 @@
       <c r="N51" s="342"/>
       <c r="O51" s="342"/>
     </row>
-    <row r="52" ht="17.2" customHeight="1">
+    <row r="52" ht="30.4" customHeight="1">
       <c r="B52" s="344">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C52" s="343" t="inlineStr">
         <is>
-          <t>EBITDA acumulado 10 años (USD)</t>
+          <t>Ingresos acumulados vs plan</t>
         </is>
       </c>
       <c r="D52" s="342" t="inlineStr">
         <is>
-          <t>SUMA(Resultados!C9:L9)</t>
-        </is>
-      </c>
-      <c r="E52" s="350">
-        <f>SUM('Resultados'!C9:L9)</f>
-        <v>25409763.624551408</v>
-      </c>
-      <c r="F52" s="352">
-        <v>26400000</v>
-      </c>
-      <c r="G52" s="350">
+          <t>Acumulado / rótulo plan del PPT (USD 180M) − 1</t>
+        </is>
+      </c>
+      <c r="E52" s="355">
+        <f>O84/E108-1</f>
+        <v>0.19800529669497924</v>
+      </c>
+      <c r="F52" s="353">
+        <v>0.21</v>
+      </c>
+      <c r="G52" s="357">
         <f>IF(ISNUMBER(E52),E52-F52,"")</f>
-        <v>-990236.375448592</v>
+        <v>-0.011994703305020754</v>
       </c>
       <c r="H52" s="342" t="inlineStr">
         <is>
-          <t>Diap. 3, 7 y 13. El PPT de junio dice 26,4M; el libro da 25,4M.</t>
+          <t>Diap. 3, 5, 9 y 13. Hoy +19,8% (el PPT dice +21%). Contra la serie plan del gráfico (179,2M) daría +20,3%.</t>
         </is>
       </c>
       <c r="I52" s="342"/>
@@ -45263,32 +45265,32 @@
     </row>
     <row r="53" ht="17.2" customHeight="1">
       <c r="B53" s="344">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C53" s="343" t="inlineStr">
         <is>
-          <t>EBITDA acumulado vs plan</t>
+          <t>EBITDA acumulado 10 años (USD)</t>
         </is>
       </c>
       <c r="D53" s="342" t="inlineStr">
         <is>
-          <t>Acumulado / suma serie plan − 1</t>
-        </is>
-      </c>
-      <c r="E53" s="355">
-        <f>O87/O88-1</f>
-        <v>0.1752717210736232</v>
-      </c>
-      <c r="F53" s="353">
-        <v>0.25</v>
-      </c>
-      <c r="G53" s="357">
+          <t>SUMA(Resultados!C9:L9)</t>
+        </is>
+      </c>
+      <c r="E53" s="350">
+        <f>SUM('Resultados'!C9:L9)</f>
+        <v>25409763.624551408</v>
+      </c>
+      <c r="F53" s="352">
+        <v>26400000</v>
+      </c>
+      <c r="G53" s="350">
         <f>IF(ISNUMBER(E53),E53-F53,"")</f>
-        <v>-0.07472827892637679</v>
+        <v>-990236.375448592</v>
       </c>
       <c r="H53" s="342" t="inlineStr">
         <is>
-          <t>Diap. 3, 7, 9 y 13. Hoy +17,5% contra la serie plan del gráfico (el PPT dice +25%).</t>
+          <t>Diap. 3, 7 y 13. El PPT de junio dice 26,4M; el libro da 25,4M.</t>
         </is>
       </c>
       <c r="I53" s="342"/>
@@ -45299,34 +45301,34 @@
       <c r="N53" s="342"/>
       <c r="O53" s="342"/>
     </row>
-    <row r="54" ht="17.2" customHeight="1">
+    <row r="54" ht="30.4" customHeight="1">
       <c r="B54" s="344">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C54" s="343" t="inlineStr">
         <is>
-          <t>Utilidad neta acumulada 10 años (USD)</t>
+          <t>EBITDA acumulado vs plan</t>
         </is>
       </c>
       <c r="D54" s="342" t="inlineStr">
         <is>
-          <t>SUMA(Resultados!C14:L14)</t>
-        </is>
-      </c>
-      <c r="E54" s="350">
-        <f>SUM('Resultados'!C14:L14)</f>
-        <v>18029154.14481669</v>
-      </c>
-      <c r="F54" s="352">
-        <v>19600000</v>
-      </c>
-      <c r="G54" s="350">
+          <t>Acumulado / rótulo plan del PPT (USD 21,1M) − 1</t>
+        </is>
+      </c>
+      <c r="E54" s="355">
+        <f>O88/E109-1</f>
+        <v>0.20425420021570662</v>
+      </c>
+      <c r="F54" s="353">
+        <v>0.25</v>
+      </c>
+      <c r="G54" s="357">
         <f>IF(ISNUMBER(E54),E54-F54,"")</f>
-        <v>-1570845.8551833108</v>
+        <v>-0.045745799784293384</v>
       </c>
       <c r="H54" s="342" t="inlineStr">
         <is>
-          <t>Diap. 3. El PPT de junio dice 19,6M; el libro da 18,0M.</t>
+          <t>Diap. 3, 7, 9 y 13. Hoy +20,4% (el PPT dice +25%). Contra la serie plan del gráfico (21,6M) daría +17,5%: ver sección 4.</t>
         </is>
       </c>
       <c r="I54" s="342"/>
@@ -45337,34 +45339,34 @@
       <c r="N54" s="342"/>
       <c r="O54" s="342"/>
     </row>
-    <row r="55" ht="30.4" customHeight="1">
+    <row r="55" ht="17.2" customHeight="1">
       <c r="B55" s="344">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C55" s="343" t="inlineStr">
         <is>
-          <t>Utilidad neta acumulada vs plan (base 17,8M)</t>
+          <t>Utilidad neta acumulada 10 años (USD)</t>
         </is>
       </c>
       <c r="D55" s="342" t="inlineStr">
         <is>
-          <t>Acumulado / 17,8M − 1</t>
-        </is>
-      </c>
-      <c r="E55" s="355">
-        <f>O89/E109-1</f>
-        <v>0.012873828360488115</v>
-      </c>
-      <c r="F55" s="353">
-        <v>0.1</v>
-      </c>
-      <c r="G55" s="357">
+          <t>SUMA(Resultados!C14:L14)</t>
+        </is>
+      </c>
+      <c r="E55" s="350">
+        <f>SUM('Resultados'!C14:L14)</f>
+        <v>18029154.14481669</v>
+      </c>
+      <c r="F55" s="352">
+        <v>19600000</v>
+      </c>
+      <c r="G55" s="350">
         <f>IF(ISNUMBER(E55),E55-F55,"")</f>
-        <v>-0.08712617163951189</v>
+        <v>-1570845.8551833108</v>
       </c>
       <c r="H55" s="342" t="inlineStr">
         <is>
-          <t>Diap. 3. Hoy +1,3% (el PPT dice +10%). No hay serie anual del plan.</t>
+          <t>Diap. 3. El PPT de junio dice 19,6M; el libro da 18,0M.</t>
         </is>
       </c>
       <c r="I55" s="342"/>
@@ -45375,34 +45377,34 @@
       <c r="N55" s="342"/>
       <c r="O55" s="342"/>
     </row>
-    <row r="56" ht="17.2" customHeight="1">
+    <row r="56" ht="30.4" customHeight="1">
       <c r="B56" s="344">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C56" s="343" t="inlineStr">
         <is>
-          <t>Materia prima acumulada 10 años (USD)</t>
+          <t>Utilidad neta acumulada vs plan (base 17,8M)</t>
         </is>
       </c>
       <c r="D56" s="342" t="inlineStr">
         <is>
-          <t>SUMA(Costos!D6:M6)</t>
-        </is>
-      </c>
-      <c r="E56" s="350">
-        <f>SUM('Costos'!D6:M6)</f>
-        <v>181094065.8413827</v>
-      </c>
-      <c r="F56" s="352">
-        <v>183000000</v>
-      </c>
-      <c r="G56" s="350">
+          <t>Acumulado / 17,8M − 1</t>
+        </is>
+      </c>
+      <c r="E56" s="355">
+        <f>O90/E110-1</f>
+        <v>0.012873828360488115</v>
+      </c>
+      <c r="F56" s="353">
+        <v>0.1</v>
+      </c>
+      <c r="G56" s="357">
         <f>IF(ISNUMBER(E56),E56-F56,"")</f>
-        <v>-1905934.1586172879</v>
+        <v>-0.08712617163951189</v>
       </c>
       <c r="H56" s="342" t="inlineStr">
         <is>
-          <t>Diap. 6. El PPT dice 183M; el libro da 181,1M.</t>
+          <t>Diap. 3. Hoy +1,3% (el PPT dice +10%). No hay serie anual del plan.</t>
         </is>
       </c>
       <c r="I56" s="342"/>
@@ -45415,32 +45417,32 @@
     </row>
     <row r="57" ht="17.2" customHeight="1">
       <c r="B57" s="344">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C57" s="343" t="inlineStr">
         <is>
-          <t>Materia prima año 2 (USD)</t>
+          <t>Materia prima acumulada 10 años (USD)</t>
         </is>
       </c>
       <c r="D57" s="342" t="inlineStr">
         <is>
-          <t>Costos!E6</t>
+          <t>SUMA(Costos!D6:M6)</t>
         </is>
       </c>
       <c r="E57" s="350">
-        <f>'Costos'!E6</f>
-        <v>14101733.588170895</v>
+        <f>SUM('Costos'!D6:M6)</f>
+        <v>181094065.8413827</v>
       </c>
       <c r="F57" s="352">
-        <v>14100000</v>
+        <v>183000000</v>
       </c>
       <c r="G57" s="350">
         <f>IF(ISNUMBER(E57),E57-F57,"")</f>
-        <v>1733.588170895353</v>
+        <v>-1905934.1586172879</v>
       </c>
       <c r="H57" s="342" t="inlineStr">
         <is>
-          <t>Diap. 6 («14,1M»). Plan año 2 = Ej_Costos!AE22 (11,1M).</t>
+          <t>Diap. 6. El PPT dice 183M; el libro da 181,1M.</t>
         </is>
       </c>
       <c r="I57" s="342"/>
@@ -45453,32 +45455,32 @@
     </row>
     <row r="58" ht="17.2" customHeight="1">
       <c r="B58" s="344">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C58" s="343" t="inlineStr">
         <is>
-          <t>Materia prima / costo de producción año 2</t>
+          <t>Materia prima año 2 (USD)</t>
         </is>
       </c>
       <c r="D58" s="342" t="inlineStr">
         <is>
-          <t>Costos!E6 / Costos!E17</t>
-        </is>
-      </c>
-      <c r="E58" s="355">
-        <f>'Costos'!E6/'Costos'!E17</f>
-        <v>0.9613831886330262</v>
-      </c>
-      <c r="F58" s="353">
-        <v>0.961</v>
-      </c>
-      <c r="G58" s="357">
+          <t>Costos!E6</t>
+        </is>
+      </c>
+      <c r="E58" s="350">
+        <f>'Costos'!E6</f>
+        <v>14101733.588170895</v>
+      </c>
+      <c r="F58" s="352">
+        <v>14100000</v>
+      </c>
+      <c r="G58" s="350">
         <f>IF(ISNUMBER(E58),E58-F58,"")</f>
-        <v>0.0003831886330262213</v>
+        <v>1733.588170895353</v>
       </c>
       <c r="H58" s="342" t="inlineStr">
         <is>
-          <t>Diap. 6. Plan en el libro: Ej_Costos!AE22/AE44 = 96,45% (el PPT dice 95,3%).</t>
+          <t>Diap. 6 («14,1M»). Plan año 2 = Ej_Costos!AE22 (11,1M).</t>
         </is>
       </c>
       <c r="I58" s="342"/>
@@ -45491,32 +45493,32 @@
     </row>
     <row r="59" ht="17.2" customHeight="1">
       <c r="B59" s="344">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C59" s="343" t="inlineStr">
         <is>
-          <t>Desvío costo MP/Tn año 2 vs plan — mínimo</t>
+          <t>Materia prima / costo de producción año 2</t>
         </is>
       </c>
       <c r="D59" s="342" t="inlineStr">
         <is>
-          <t>MÍN(Ej_Costos!AF9:AF11; AF13:AF19)</t>
+          <t>Costos!E6 / Costos!E17</t>
         </is>
       </c>
       <c r="E59" s="355">
-        <f>MIN('Ej_Costos'!AF9:AF11,'Ej_Costos'!AF13:AF19)</f>
-        <v>0.026610462000214583</v>
+        <f>'Costos'!E6/'Costos'!E17</f>
+        <v>0.9613831886330262</v>
       </c>
       <c r="F59" s="353">
-        <v>0.06</v>
+        <v>0.961</v>
       </c>
       <c r="G59" s="357">
         <f>IF(ISNUMBER(E59),E59-F59,"")</f>
-        <v>-0.03338953799978542</v>
+        <v>0.0003831886330262213</v>
       </c>
       <c r="H59" s="342" t="inlineStr">
         <is>
-          <t>Diap. 2, 6, 11 y 13 («6-16%»). Hoy 2,7% (Accesorios); sin Accesorios 5,9%.</t>
+          <t>Diap. 6. Plan en el libro: Ej_Costos!AE22/AE44 = 96,45% (el PPT dice 95,3%).</t>
         </is>
       </c>
       <c r="I59" s="342"/>
@@ -45529,32 +45531,32 @@
     </row>
     <row r="60" ht="17.2" customHeight="1">
       <c r="B60" s="344">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C60" s="343" t="inlineStr">
         <is>
-          <t>Desvío costo MP/Tn año 2 vs plan — máximo</t>
+          <t>Desvío costo MP/Tn año 2 vs plan — mínimo</t>
         </is>
       </c>
       <c r="D60" s="342" t="inlineStr">
         <is>
-          <t>MÁX(Ej_Costos!AF9:AF11; AF13:AF19)</t>
+          <t>MÍN(Ej_Costos!AF9:AF11; AF13:AF19)</t>
         </is>
       </c>
       <c r="E60" s="355">
-        <f>MAX('Ej_Costos'!AF9:AF11,'Ej_Costos'!AF13:AF19)</f>
-        <v>0.15778067896859566</v>
+        <f>MIN('Ej_Costos'!AF9:AF11,'Ej_Costos'!AF13:AF19)</f>
+        <v>0.026610462000214583</v>
       </c>
       <c r="F60" s="353">
-        <v>0.16</v>
+        <v>0.06</v>
       </c>
       <c r="G60" s="357">
         <f>IF(ISNUMBER(E60),E60-F60,"")</f>
-        <v>-0.0022193210314043477</v>
+        <v>-0.03338953799978542</v>
       </c>
       <c r="H60" s="342" t="inlineStr">
         <is>
-          <t>Idem. El producto 4 (AF12) no tiene plan.</t>
+          <t>Diap. 2, 6, 11 y 13 («6-16%»). Hoy 2,7% (Accesorios); sin Accesorios 5,9%.</t>
         </is>
       </c>
       <c r="I60" s="342"/>
@@ -45567,32 +45569,32 @@
     </row>
     <row r="61" ht="17.2" customHeight="1">
       <c r="B61" s="344">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C61" s="343" t="inlineStr">
         <is>
-          <t>Precio promedio año 2 (USD/Tn)</t>
+          <t>Desvío costo MP/Tn año 2 vs plan — máximo</t>
         </is>
       </c>
       <c r="D61" s="342" t="inlineStr">
         <is>
-          <t>Ingresos!E29</t>
-        </is>
-      </c>
-      <c r="E61" s="350">
-        <f>'Ingresos'!E29</f>
-        <v>1219.2023182297155</v>
-      </c>
-      <c r="F61" s="352">
-        <v>1219</v>
-      </c>
-      <c r="G61" s="350">
+          <t>MÁX(Ej_Costos!AF9:AF11; AF13:AF19)</t>
+        </is>
+      </c>
+      <c r="E61" s="355">
+        <f>MAX('Ej_Costos'!AF9:AF11,'Ej_Costos'!AF13:AF19)</f>
+        <v>0.15778067896859566</v>
+      </c>
+      <c r="F61" s="353">
+        <v>0.16</v>
+      </c>
+      <c r="G61" s="357">
         <f>IF(ISNUMBER(E61),E61-F61,"")</f>
-        <v>0.20231822971550173</v>
+        <v>-0.0022193210314043477</v>
       </c>
       <c r="H61" s="342" t="inlineStr">
         <is>
-          <t>Diap. 5.</t>
+          <t>Idem. El producto 4 (AF12) no tiene plan.</t>
         </is>
       </c>
       <c r="I61" s="342"/>
@@ -45605,32 +45607,32 @@
     </row>
     <row r="62" ht="17.2" customHeight="1">
       <c r="B62" s="344">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C62" s="343" t="inlineStr">
         <is>
-          <t>Precio promedio plan año 2 (USD/Tn)</t>
+          <t>Precio promedio año 2 (USD/Tn)</t>
         </is>
       </c>
       <c r="D62" s="342" t="inlineStr">
         <is>
-          <t>Ej_Ingresos!AE34 / Ej_Producción!AE48</t>
+          <t>Ingresos!E29</t>
         </is>
       </c>
       <c r="E62" s="350">
-        <f>'Ej_Ingresos'!AE34/'Ej_Producción'!AE48</f>
-        <v>1096.3244333306445</v>
+        <f>'Ingresos'!E29</f>
+        <v>1219.2023182297155</v>
       </c>
       <c r="F62" s="352">
-        <v>1096</v>
+        <v>1219</v>
       </c>
       <c r="G62" s="350">
         <f>IF(ISNUMBER(E62),E62-F62,"")</f>
-        <v>0.3244333306445242</v>
+        <v>0.20231822971550173</v>
       </c>
       <c r="H62" s="342" t="inlineStr">
         <is>
-          <t>Diap. 5. Es plan: no debería cambiar.</t>
+          <t>Diap. 5.</t>
         </is>
       </c>
       <c r="I62" s="342"/>
@@ -45641,34 +45643,34 @@
       <c r="N62" s="342"/>
       <c r="O62" s="342"/>
     </row>
-    <row r="63" ht="30.4" customHeight="1">
+    <row r="63" ht="17.2" customHeight="1">
       <c r="B63" s="344">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C63" s="343" t="inlineStr">
         <is>
-          <t>Precio Accesorios Metálicos año 2 (USD/Tn)</t>
+          <t>Precio promedio plan año 2 (USD/Tn)</t>
         </is>
       </c>
       <c r="D63" s="342" t="inlineStr">
         <is>
-          <t>Ingresos!E26</t>
+          <t>Ej_Ingresos!AE34 / Ej_Producción!AE48</t>
         </is>
       </c>
       <c r="E63" s="350">
-        <f>'Ingresos'!E26</f>
-        <v>5202</v>
+        <f>'Ej_Ingresos'!AE34/'Ej_Producción'!AE48</f>
+        <v>1096.3244333306445</v>
       </c>
       <c r="F63" s="352">
-        <v>5202</v>
+        <v>1096</v>
       </c>
       <c r="G63" s="350">
         <f>IF(ISNUMBER(E63),E63-F63,"")</f>
-        <v>0</v>
+        <v>0.3244333306445242</v>
       </c>
       <c r="H63" s="342" t="inlineStr">
         <is>
-          <t>Diap. 5.</t>
+          <t>Diap. 5. Es plan: no debería cambiar.</t>
         </is>
       </c>
       <c r="I63" s="342"/>
@@ -45679,34 +45681,34 @@
       <c r="N63" s="342"/>
       <c r="O63" s="342"/>
     </row>
-    <row r="64" ht="17.2" customHeight="1">
+    <row r="64" ht="30.4" customHeight="1">
       <c r="B64" s="344">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C64" s="343" t="inlineStr">
         <is>
-          <t>Capital de trabajo neto año 1 (USD)</t>
+          <t>Precio Accesorios Metálicos año 2 (USD/Tn)</t>
         </is>
       </c>
       <c r="D64" s="342" t="inlineStr">
         <is>
-          <t>Capital Trabajo!C18</t>
+          <t>Ingresos!E26</t>
         </is>
       </c>
       <c r="E64" s="350">
-        <f>'Capital Trabajo'!C18</f>
-        <v>1541094.4312681279</v>
+        <f>'Ingresos'!E26</f>
+        <v>5202</v>
       </c>
       <c r="F64" s="352">
-        <v>1540000</v>
+        <v>5202</v>
       </c>
       <c r="G64" s="350">
         <f>IF(ISNUMBER(E64),E64-F64,"")</f>
-        <v>1094.431268127868</v>
+        <v>0</v>
       </c>
       <c r="H64" s="342" t="inlineStr">
         <is>
-          <t>Diap. 8.</t>
+          <t>Diap. 5.</t>
         </is>
       </c>
       <c r="I64" s="342"/>
@@ -45719,28 +45721,28 @@
     </row>
     <row r="65" ht="17.2" customHeight="1">
       <c r="B65" s="344">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C65" s="343" t="inlineStr">
         <is>
-          <t>Capital de trabajo neto año 2 (USD)</t>
+          <t>Capital de trabajo neto año 1 (USD)</t>
         </is>
       </c>
       <c r="D65" s="342" t="inlineStr">
         <is>
-          <t>Capital Trabajo!D18</t>
+          <t>Capital Trabajo!C18</t>
         </is>
       </c>
       <c r="E65" s="350">
-        <f>'Capital Trabajo'!D18</f>
-        <v>6115600.303155011</v>
+        <f>'Capital Trabajo'!C18</f>
+        <v>1541094.4312681279</v>
       </c>
       <c r="F65" s="352">
-        <v>6120000</v>
+        <v>1540000</v>
       </c>
       <c r="G65" s="350">
         <f>IF(ISNUMBER(E65),E65-F65,"")</f>
-        <v>-4399.696844989434</v>
+        <v>1094.431268127868</v>
       </c>
       <c r="H65" s="342" t="inlineStr">
         <is>
@@ -45757,28 +45759,28 @@
     </row>
     <row r="66" ht="17.2" customHeight="1">
       <c r="B66" s="344">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C66" s="343" t="inlineStr">
         <is>
-          <t>Capital de trabajo neto año 10 (USD)</t>
+          <t>Capital de trabajo neto año 2 (USD)</t>
         </is>
       </c>
       <c r="D66" s="342" t="inlineStr">
         <is>
-          <t>Capital Trabajo!L18</t>
+          <t>Capital Trabajo!D18</t>
         </is>
       </c>
       <c r="E66" s="350">
-        <f>'Capital Trabajo'!L18</f>
-        <v>10928040.580366578</v>
+        <f>'Capital Trabajo'!D18</f>
+        <v>6115600.303155011</v>
       </c>
       <c r="F66" s="352">
-        <v>10930000</v>
+        <v>6120000</v>
       </c>
       <c r="G66" s="350">
         <f>IF(ISNUMBER(E66),E66-F66,"")</f>
-        <v>-1959.419633422047</v>
+        <v>-4399.696844989434</v>
       </c>
       <c r="H66" s="342" t="inlineStr">
         <is>
@@ -45795,28 +45797,28 @@
     </row>
     <row r="67" ht="17.2" customHeight="1">
       <c r="B67" s="344">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C67" s="343" t="inlineStr">
         <is>
-          <t>Ventas a crédito año 2 (USD)</t>
+          <t>Capital de trabajo neto año 10 (USD)</t>
         </is>
       </c>
       <c r="D67" s="342" t="inlineStr">
         <is>
-          <t>Capital Trabajo!D9</t>
+          <t>Capital Trabajo!L18</t>
         </is>
       </c>
       <c r="E67" s="350">
-        <f>'Capital Trabajo'!D9</f>
-        <v>4279400.136986301</v>
+        <f>'Capital Trabajo'!L18</f>
+        <v>10928040.580366578</v>
       </c>
       <c r="F67" s="352">
-        <v>4280000</v>
+        <v>10930000</v>
       </c>
       <c r="G67" s="350">
         <f>IF(ISNUMBER(E67),E67-F67,"")</f>
-        <v>-599.8630136987194</v>
+        <v>-1959.419633422047</v>
       </c>
       <c r="H67" s="342" t="inlineStr">
         <is>
@@ -45833,32 +45835,32 @@
     </row>
     <row r="68" ht="17.2" customHeight="1">
       <c r="B68" s="344">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C68" s="343" t="inlineStr">
         <is>
-          <t>Cuentas por cobrar año 10 (USD)</t>
+          <t>Ventas a crédito año 2 (USD)</t>
         </is>
       </c>
       <c r="D68" s="342" t="inlineStr">
         <is>
-          <t>Capital Trabajo!L9</t>
+          <t>Capital Trabajo!D9</t>
         </is>
       </c>
       <c r="E68" s="350">
-        <f>'Capital Trabajo'!L9</f>
-        <v>7509783.1482635895</v>
+        <f>'Capital Trabajo'!D9</f>
+        <v>4279400.136986301</v>
       </c>
       <c r="F68" s="352">
-        <v>7500000</v>
+        <v>4280000</v>
       </c>
       <c r="G68" s="350">
         <f>IF(ISNUMBER(E68),E68-F68,"")</f>
-        <v>9783.148263589479</v>
+        <v>-599.8630136987194</v>
       </c>
       <c r="H68" s="342" t="inlineStr">
         <is>
-          <t>Diap. 8.</t>
+          <t>Diap. 8 y 13 («USD 4-7M adicionales»).</t>
         </is>
       </c>
       <c r="I68" s="342"/>
@@ -45869,34 +45871,34 @@
       <c r="N68" s="342"/>
       <c r="O68" s="342"/>
     </row>
-    <row r="69" ht="30.4" customHeight="1">
+    <row r="69" ht="17.2" customHeight="1">
       <c r="B69" s="344">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C69" s="343" t="inlineStr">
         <is>
-          <t>Préstamos CP por año, años 2-10 — mínimo (USD)</t>
+          <t>Cuentas por cobrar año 10 (USD)</t>
         </is>
       </c>
       <c r="D69" s="342" t="inlineStr">
         <is>
-          <t>MÍN de la serie «Préstamos CP» (sección 3)</t>
+          <t>Capital Trabajo!L9</t>
         </is>
       </c>
       <c r="E69" s="350">
-        <f>MIN(F94:N94)</f>
-        <v>4000000</v>
+        <f>'Capital Trabajo'!L9</f>
+        <v>7509783.1482635895</v>
       </c>
       <c r="F69" s="352">
-        <v>5000000</v>
+        <v>7500000</v>
       </c>
       <c r="G69" s="350">
         <f>IF(ISNUMBER(E69),E69-F69,"")</f>
-        <v>-1000000</v>
+        <v>9783.148263589479</v>
       </c>
       <c r="H69" s="342" t="inlineStr">
         <is>
-          <t>Diap. 8, 11 y 13 («USD 5-11,9M/año»). Hoy el año 7 es 4,0M.</t>
+          <t>Diap. 8 y 13.</t>
         </is>
       </c>
       <c r="I69" s="342"/>
@@ -45909,32 +45911,32 @@
     </row>
     <row r="70" ht="30.4" customHeight="1">
       <c r="B70" s="344">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C70" s="343" t="inlineStr">
         <is>
-          <t>Préstamos CP por año, años 2-10 — máximo (USD)</t>
+          <t>Préstamos CP por año, años 2-10 — mínimo (USD)</t>
         </is>
       </c>
       <c r="D70" s="342" t="inlineStr">
         <is>
-          <t>MÁX de la serie «Préstamos CP» (sección 3)</t>
+          <t>MÍN de la serie «Préstamos CP» (sección 3)</t>
         </is>
       </c>
       <c r="E70" s="350">
-        <f>MAX(F94:N94)</f>
-        <v>11900000</v>
+        <f>MIN(F95:N95)</f>
+        <v>4000000</v>
       </c>
       <c r="F70" s="352">
-        <v>11900000</v>
+        <v>5000000</v>
       </c>
       <c r="G70" s="350">
         <f>IF(ISNUMBER(E70),E70-F70,"")</f>
-        <v>0</v>
+        <v>-1000000</v>
       </c>
       <c r="H70" s="342" t="inlineStr">
         <is>
-          <t>Idem.</t>
+          <t>Diap. 8, 11 y 13 («USD 5-11,9M/año»). Hoy el año 7 es 4,0M.</t>
         </is>
       </c>
       <c r="I70" s="342"/>
@@ -45947,32 +45949,32 @@
     </row>
     <row r="71" ht="30.4" customHeight="1">
       <c r="B71" s="344">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C71" s="343" t="inlineStr">
         <is>
-          <t>Margen de seguridad años 2-10 — mínimo</t>
+          <t>Préstamos CP por año, años 2-10 — máximo (USD)</t>
         </is>
       </c>
       <c r="D71" s="342" t="inlineStr">
         <is>
-          <t>MÍN de la serie «Margen de seguridad» (sección 3)</t>
-        </is>
-      </c>
-      <c r="E71" s="355">
-        <f>MIN(F93:N93)</f>
-        <v>0.5039954967106854</v>
-      </c>
-      <c r="F71" s="353">
-        <v>0.52</v>
-      </c>
-      <c r="G71" s="357">
+          <t>MÁX de la serie «Préstamos CP» (sección 3)</t>
+        </is>
+      </c>
+      <c r="E71" s="350">
+        <f>MAX(F95:N95)</f>
+        <v>11900000</v>
+      </c>
+      <c r="F71" s="352">
+        <v>11900000</v>
+      </c>
+      <c r="G71" s="350">
         <f>IF(ISNUMBER(E71),E71-F71,"")</f>
-        <v>-0.016004503289314576</v>
+        <v>0</v>
       </c>
       <c r="H71" s="342" t="inlineStr">
         <is>
-          <t>Diap. 10 («52-69%»). Hoy el año 3 da 50,4%.</t>
+          <t>Idem.</t>
         </is>
       </c>
       <c r="I71" s="342"/>
@@ -45985,32 +45987,32 @@
     </row>
     <row r="72" ht="30.4" customHeight="1">
       <c r="B72" s="344">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C72" s="343" t="inlineStr">
         <is>
-          <t>Margen de seguridad años 2-10 — máximo</t>
+          <t>Margen de seguridad años 2-10 — mínimo</t>
         </is>
       </c>
       <c r="D72" s="342" t="inlineStr">
         <is>
-          <t>MÁX de la serie «Margen de seguridad» (sección 3)</t>
+          <t>MÍN de la serie «Margen de seguridad» (sección 3)</t>
         </is>
       </c>
       <c r="E72" s="355">
-        <f>MAX(F93:N93)</f>
-        <v>0.6931320917474184</v>
+        <f>MIN(F94:N94)</f>
+        <v>0.5039954967106854</v>
       </c>
       <c r="F72" s="353">
-        <v>0.69</v>
+        <v>0.52</v>
       </c>
       <c r="G72" s="357">
         <f>IF(ISNUMBER(E72),E72-F72,"")</f>
-        <v>0.003132091747418464</v>
+        <v>-0.016004503289314576</v>
       </c>
       <c r="H72" s="342" t="inlineStr">
         <is>
-          <t>Idem.</t>
+          <t>Diap. 10 («52-69%»). Hoy el año 3 da 50,4%.</t>
         </is>
       </c>
       <c r="I72" s="342"/>
@@ -46023,32 +46025,32 @@
     </row>
     <row r="73" ht="30.4" customHeight="1">
       <c r="B73" s="344">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C73" s="343" t="inlineStr">
         <is>
-          <t>Concentración Slitter DW 0,43/0,48 (año 2, % de Tn)</t>
+          <t>Margen de seguridad años 2-10 — máximo</t>
         </is>
       </c>
       <c r="D73" s="342" t="inlineStr">
         <is>
-          <t>Producción!E8 / Producción!E28</t>
+          <t>MÁX de la serie «Margen de seguridad» (sección 3)</t>
         </is>
       </c>
       <c r="E73" s="355">
-        <f>'Producción'!E8/'Producción'!E28</f>
-        <v>0.3350895679662803</v>
+        <f>MAX(F94:N94)</f>
+        <v>0.6931320917474184</v>
       </c>
       <c r="F73" s="353">
-        <v>0.33</v>
+        <v>0.69</v>
       </c>
       <c r="G73" s="357">
         <f>IF(ISNUMBER(E73),E73-F73,"")</f>
-        <v>0.005089567966280295</v>
+        <v>0.003132091747418464</v>
       </c>
       <c r="H73" s="342" t="inlineStr">
         <is>
-          <t>Diap. 11.</t>
+          <t>Idem.</t>
         </is>
       </c>
       <c r="I73" s="342"/>
@@ -46061,32 +46063,32 @@
     </row>
     <row r="74" ht="30.4" customHeight="1">
       <c r="B74" s="344">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C74" s="343" t="inlineStr">
         <is>
-          <t>Payback inversión propia (años, calculado)</t>
+          <t>Concentración Slitter DW 0,43/0,48 (año 2, % de Tn)</t>
         </is>
       </c>
       <c r="D74" s="342" t="inlineStr">
         <is>
-          <t>Payback filas 6-7 (dividendos descontados a Ke)</t>
-        </is>
-      </c>
-      <c r="E74" s="358">
-        <f>IFERROR(COUNTIF('Payback'!D7:M7,"&lt;0")+(-INDEX('Payback'!C7:M7,COUNTIF('Payback'!C7:M7,"&lt;0")))/INDEX('Payback'!C6:M6,COUNTIF('Payback'!C7:M7,"&lt;0")+1),"No recupera en 10 años")</f>
-        <v>6.3809271306571045</v>
-      </c>
-      <c r="F74" s="352">
-        <v>6</v>
-      </c>
-      <c r="G74" s="358">
+          <t>Producción!E8 / Producción!E28</t>
+        </is>
+      </c>
+      <c r="E74" s="355">
+        <f>'Producción'!E8/'Producción'!E28</f>
+        <v>0.3350895679662803</v>
+      </c>
+      <c r="F74" s="353">
+        <v>0.33</v>
+      </c>
+      <c r="G74" s="357">
         <f>IF(ISNUMBER(E74),E74-F74,"")</f>
-        <v>0.3809271306571045</v>
+        <v>0.005089567966280295</v>
       </c>
       <c r="H74" s="342" t="inlineStr">
         <is>
-          <t>Diap. 9 («Actual: 6 Años»). Se recupera durante el año 7 (6,4 años).</t>
+          <t>Diap. 11.</t>
         </is>
       </c>
       <c r="I74" s="342"/>
@@ -46099,27 +46101,32 @@
     </row>
     <row r="75" ht="30.4" customHeight="1">
       <c r="B75" s="344">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C75" s="343" t="inlineStr">
         <is>
-          <t>Payback inversión total (años, calculado)</t>
+          <t>Payback inversión propia (años, calculado)</t>
         </is>
       </c>
       <c r="D75" s="342" t="inlineStr">
         <is>
-          <t>Payback filas 11-12 (flujo sin financiamiento a Ke)</t>
+          <t>Payback filas 6-7 (dividendos descontados a Ke)</t>
         </is>
       </c>
       <c r="E75" s="358">
-        <f>IFERROR(COUNTIF('Payback'!D12:M12,"&lt;0")+(-INDEX('Payback'!C12:M12,COUNTIF('Payback'!C12:M12,"&lt;0")))/INDEX('Payback'!C11:M11,COUNTIF('Payback'!C12:M12,"&lt;0")+1),"No recupera en 10 años")</f>
-        <v>5.02442781532552</v>
-      </c>
-      <c r="F75" s="342"/>
-      <c r="G75" s="342"/>
+        <f>IFERROR(COUNTIF('Payback'!D7:M7,"&lt;0")+(-INDEX('Payback'!C7:M7,COUNTIF('Payback'!C7:M7,"&lt;0")))/INDEX('Payback'!C6:M6,COUNTIF('Payback'!C7:M7,"&lt;0")+1),"No recupera en 10 años")</f>
+        <v>6.3809271306571045</v>
+      </c>
+      <c r="F75" s="352">
+        <v>6</v>
+      </c>
+      <c r="G75" s="358">
+        <f>IF(ISNUMBER(E75),E75-F75,"")</f>
+        <v>0.3809271306571045</v>
+      </c>
       <c r="H75" s="342" t="inlineStr">
         <is>
-          <t>No está en el PPT. Hoy 5,0 por el error de exponentes; corregido (paso B6) ≈ 8,1.</t>
+          <t>Diap. 9 («Actual: 6 Años»). Se recupera durante el año 7 (6,4 años).</t>
         </is>
       </c>
       <c r="I75" s="342"/>
@@ -46130,29 +46137,29 @@
       <c r="N75" s="342"/>
       <c r="O75" s="342"/>
     </row>
-    <row r="76" ht="17.2" customHeight="1">
+    <row r="76" ht="30.4" customHeight="1">
       <c r="B76" s="344">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C76" s="343" t="inlineStr">
         <is>
-          <t>Payback tipeado en el Dashboard</t>
+          <t>Payback inversión total (años, calculado)</t>
         </is>
       </c>
       <c r="D76" s="342" t="inlineStr">
         <is>
-          <t>Dashboard!C12 (texto)</t>
-        </is>
-      </c>
-      <c r="E76" s="344" t="str">
-        <f>'Dashboard'!C12</f>
-        <v>4 Años</v>
+          <t>Payback filas 11-12 (flujo sin financiamiento a Ke)</t>
+        </is>
+      </c>
+      <c r="E76" s="358">
+        <f>IFERROR(COUNTIF('Payback'!D12:M12,"&lt;0")+(-INDEX('Payback'!C12:M12,COUNTIF('Payback'!C12:M12,"&lt;0")))/INDEX('Payback'!C11:M11,COUNTIF('Payback'!C12:M12,"&lt;0")+1),"No recupera en 10 años")</f>
+        <v>5.02442781532552</v>
       </c>
       <c r="F76" s="342"/>
       <c r="G76" s="342"/>
       <c r="H76" s="342" t="inlineStr">
         <is>
-          <t>Hoy «4 Años» en INFORME2 («6 Años» en ORIGINAL). Reemplazar por fórmula (paso B7).</t>
+          <t>No está en el PPT. Hoy 5,0 por el error de exponentes; corregido (paso B6) ≈ 8,1.</t>
         </is>
       </c>
       <c r="I76" s="342"/>
@@ -46163,1272 +46170,1273 @@
       <c r="N76" s="342"/>
       <c r="O76" s="342"/>
     </row>
-    <row r="78" ht="20" customHeight="1">
-      <c r="B78" s="339" t="inlineStr">
+    <row r="77" ht="17.2" customHeight="1">
+      <c r="B77" s="344">
+        <v>40</v>
+      </c>
+      <c r="C77" s="343" t="inlineStr">
+        <is>
+          <t>Payback tipeado en el Dashboard</t>
+        </is>
+      </c>
+      <c r="D77" s="342" t="inlineStr">
+        <is>
+          <t>Dashboard!C12 (texto)</t>
+        </is>
+      </c>
+      <c r="E77" s="344" t="str">
+        <f>'Dashboard'!C12</f>
+        <v>4 Años</v>
+      </c>
+      <c r="F77" s="342"/>
+      <c r="G77" s="342"/>
+      <c r="H77" s="342" t="inlineStr">
+        <is>
+          <t>Hoy «4 Años» en INFORME2 («6 Años» en ORIGINAL). Reemplazar por fórmula (paso B7).</t>
+        </is>
+      </c>
+      <c r="I77" s="342"/>
+      <c r="J77" s="342"/>
+      <c r="K77" s="342"/>
+      <c r="L77" s="342"/>
+      <c r="M77" s="342"/>
+      <c r="N77" s="342"/>
+      <c r="O77" s="342"/>
+    </row>
+    <row r="79" ht="20" customHeight="1">
+      <c r="B79" s="339" t="inlineStr">
         <is>
           <t>3. SERIES ANUALES PARA LOS GRÁFICOS (clic derecho en el gráfico &gt; Editar datos &gt; pegar la fila «Actualizado»)</t>
         </is>
       </c>
-      <c r="C78" s="339"/>
-      <c r="D78" s="339"/>
-      <c r="E78" s="339"/>
-      <c r="F78" s="339"/>
-      <c r="G78" s="339"/>
-      <c r="H78" s="339"/>
-      <c r="I78" s="339"/>
-      <c r="J78" s="339"/>
-      <c r="K78" s="339"/>
-      <c r="L78" s="339"/>
-      <c r="M78" s="339"/>
-      <c r="N78" s="339"/>
-      <c r="O78" s="339"/>
-    </row>
-    <row r="79" ht="28" customHeight="1">
-      <c r="B79" s="340" t="inlineStr">
+      <c r="C79" s="339"/>
+      <c r="D79" s="339"/>
+      <c r="E79" s="339"/>
+      <c r="F79" s="339"/>
+      <c r="G79" s="339"/>
+      <c r="H79" s="339"/>
+      <c r="I79" s="339"/>
+      <c r="J79" s="339"/>
+      <c r="K79" s="339"/>
+      <c r="L79" s="339"/>
+      <c r="M79" s="339"/>
+      <c r="N79" s="339"/>
+      <c r="O79" s="339"/>
+    </row>
+    <row r="80" ht="28" customHeight="1">
+      <c r="B80" s="340" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C79" s="340" t="inlineStr">
+      <c r="C80" s="340" t="inlineStr">
         <is>
           <t>Serie</t>
         </is>
       </c>
-      <c r="D79" s="340" t="inlineStr">
+      <c r="D80" s="340" t="inlineStr">
         <is>
           <t>Origen</t>
         </is>
       </c>
-      <c r="E79" s="340" t="inlineStr">
+      <c r="E80" s="340" t="inlineStr">
         <is>
           <t xml:space="preserve">Año 1
 2026</t>
         </is>
       </c>
-      <c r="F79" s="340" t="inlineStr">
+      <c r="F80" s="340" t="inlineStr">
         <is>
           <t xml:space="preserve">Año 2
 2027</t>
         </is>
       </c>
-      <c r="G79" s="340" t="inlineStr">
+      <c r="G80" s="340" t="inlineStr">
         <is>
           <t xml:space="preserve">Año 3
 2028</t>
         </is>
       </c>
-      <c r="H79" s="340" t="inlineStr">
+      <c r="H80" s="340" t="inlineStr">
         <is>
           <t xml:space="preserve">Año 4
 2029</t>
         </is>
       </c>
-      <c r="I79" s="340" t="inlineStr">
+      <c r="I80" s="340" t="inlineStr">
         <is>
           <t xml:space="preserve">Año 5
 2030</t>
         </is>
       </c>
-      <c r="J79" s="340" t="inlineStr">
+      <c r="J80" s="340" t="inlineStr">
         <is>
           <t xml:space="preserve">Año 6
 2031</t>
         </is>
       </c>
-      <c r="K79" s="340" t="inlineStr">
+      <c r="K80" s="340" t="inlineStr">
         <is>
           <t xml:space="preserve">Año 7
 2032</t>
         </is>
       </c>
-      <c r="L79" s="340" t="inlineStr">
+      <c r="L80" s="340" t="inlineStr">
         <is>
           <t xml:space="preserve">Año 8
 2033</t>
         </is>
       </c>
-      <c r="M79" s="340" t="inlineStr">
+      <c r="M80" s="340" t="inlineStr">
         <is>
           <t xml:space="preserve">Año 9
 2034</t>
         </is>
       </c>
-      <c r="N79" s="340" t="inlineStr">
+      <c r="N80" s="340" t="inlineStr">
         <is>
           <t xml:space="preserve">Año 10
 2035</t>
         </is>
       </c>
-      <c r="O79" s="340" t="inlineStr">
+      <c r="O80" s="340" t="inlineStr">
         <is>
           <t>Total 10 años</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="17.2" customHeight="1">
-      <c r="B80" s="344">
+    <row r="81" ht="17.2" customHeight="1">
+      <c r="B81" s="344">
         <v>1</v>
       </c>
-      <c r="C80" s="343" t="inlineStr">
+      <c r="C81" s="343" t="inlineStr">
         <is>
           <t>Producción (Tn) — Actualizado</t>
         </is>
       </c>
-      <c r="D80" s="342" t="inlineStr">
+      <c r="D81" s="342" t="inlineStr">
         <is>
           <t>Producción!D28:M28</t>
         </is>
       </c>
-      <c r="E80" s="350">
+      <c r="E81" s="350">
         <f>'Producción'!D28</f>
         <v>4315.166</v>
       </c>
-      <c r="F80" s="350">
+      <c r="F81" s="350">
         <f>'Producción'!E28</f>
         <v>14235</v>
       </c>
-      <c r="G80" s="350">
+      <c r="G81" s="350">
         <f>'Producción'!F28</f>
         <v>14950</v>
       </c>
-      <c r="H80" s="350">
+      <c r="H81" s="350">
         <f>'Producción'!G28</f>
         <v>15698</v>
       </c>
-      <c r="I80" s="350">
+      <c r="I81" s="350">
         <f>'Producción'!H28</f>
         <v>16482</v>
       </c>
-      <c r="J80" s="350">
+      <c r="J81" s="350">
         <f>'Producción'!I28</f>
         <v>17306</v>
       </c>
-      <c r="K80" s="350">
+      <c r="K81" s="350">
         <f>'Producción'!J28</f>
         <v>18170</v>
       </c>
-      <c r="L80" s="350">
+      <c r="L81" s="350">
         <f>'Producción'!K28</f>
         <v>19076</v>
       </c>
-      <c r="M80" s="350">
+      <c r="M81" s="350">
         <f>'Producción'!L28</f>
         <v>20030</v>
       </c>
-      <c r="N80" s="350">
+      <c r="N81" s="350">
         <f>'Producción'!M28</f>
         <v>21030</v>
       </c>
-      <c r="O80" s="351">
-        <f>SUM(E80:N80)</f>
-        <v>161292.166</v>
-      </c>
-    </row>
-    <row r="81" ht="17.2" customHeight="1">
-      <c r="B81" s="344">
-        <v>2</v>
-      </c>
-      <c r="C81" s="343" t="inlineStr">
-        <is>
-          <t>Producción (Tn) — Plan original</t>
-        </is>
-      </c>
-      <c r="D81" s="342" t="inlineStr">
-        <is>
-          <t>PPT jun-2026 (fijo)</t>
-        </is>
-      </c>
-      <c r="E81" s="352">
-        <v>11087</v>
-      </c>
-      <c r="F81" s="352">
-        <v>12587</v>
-      </c>
-      <c r="G81" s="352">
-        <v>13216</v>
-      </c>
-      <c r="H81" s="352">
-        <v>13876</v>
-      </c>
-      <c r="I81" s="352">
-        <v>14570</v>
-      </c>
-      <c r="J81" s="352">
-        <v>15299</v>
-      </c>
-      <c r="K81" s="352">
-        <v>16065</v>
-      </c>
-      <c r="L81" s="352">
-        <v>16868</v>
-      </c>
-      <c r="M81" s="352">
-        <v>17711</v>
-      </c>
-      <c r="N81" s="352">
-        <v>18596</v>
-      </c>
       <c r="O81" s="351">
         <f>SUM(E81:N81)</f>
-        <v>149875</v>
+        <v>161292.166</v>
       </c>
     </row>
     <row r="82" ht="17.2" customHeight="1">
       <c r="B82" s="344">
+        <v>2</v>
+      </c>
+      <c r="C82" s="343" t="inlineStr">
+        <is>
+          <t>Producción (Tn) — Plan original</t>
+        </is>
+      </c>
+      <c r="D82" s="342" t="inlineStr">
+        <is>
+          <t>PPT jun-2026 (fijo)</t>
+        </is>
+      </c>
+      <c r="E82" s="352">
+        <v>11087</v>
+      </c>
+      <c r="F82" s="352">
+        <v>12587</v>
+      </c>
+      <c r="G82" s="352">
+        <v>13216</v>
+      </c>
+      <c r="H82" s="352">
+        <v>13876</v>
+      </c>
+      <c r="I82" s="352">
+        <v>14570</v>
+      </c>
+      <c r="J82" s="352">
+        <v>15299</v>
+      </c>
+      <c r="K82" s="352">
+        <v>16065</v>
+      </c>
+      <c r="L82" s="352">
+        <v>16868</v>
+      </c>
+      <c r="M82" s="352">
+        <v>17711</v>
+      </c>
+      <c r="N82" s="352">
+        <v>18596</v>
+      </c>
+      <c r="O82" s="351">
+        <f>SUM(E82:N82)</f>
+        <v>149875</v>
+      </c>
+    </row>
+    <row r="83" ht="17.2" customHeight="1">
+      <c r="B83" s="344">
         <v>3</v>
       </c>
-      <c r="C82" s="343" t="inlineStr">
+      <c r="C83" s="343" t="inlineStr">
         <is>
           <t>Ventas (Tn) — Actualizado</t>
         </is>
       </c>
-      <c r="D82" s="342" t="inlineStr">
+      <c r="D83" s="342" t="inlineStr">
         <is>
           <t>Producción!D29:M29</t>
         </is>
       </c>
-      <c r="E82" s="350">
+      <c r="E83" s="350">
         <f>'Producción'!D29</f>
         <v>4195.166</v>
       </c>
-      <c r="F82" s="350">
+      <c r="F83" s="350">
         <f>'Producción'!E29</f>
         <v>14235</v>
       </c>
-      <c r="G82" s="350">
+      <c r="G83" s="350">
         <f>'Producción'!F29</f>
         <v>14726</v>
       </c>
-      <c r="H82" s="350">
+      <c r="H83" s="350">
         <f>'Producción'!G29</f>
         <v>15464</v>
       </c>
-      <c r="I82" s="350">
+      <c r="I83" s="350">
         <f>'Producción'!H29</f>
         <v>16235</v>
       </c>
-      <c r="J82" s="350">
+      <c r="J83" s="350">
         <f>'Producción'!I29</f>
         <v>17046</v>
       </c>
-      <c r="K82" s="350">
+      <c r="K83" s="350">
         <f>'Producción'!J29</f>
         <v>17897</v>
       </c>
-      <c r="L82" s="350">
+      <c r="L83" s="350">
         <f>'Producción'!K29</f>
         <v>18789</v>
       </c>
-      <c r="M82" s="350">
+      <c r="M83" s="350">
         <f>'Producción'!L29</f>
         <v>19728</v>
       </c>
-      <c r="N82" s="350">
+      <c r="N83" s="350">
         <f>'Producción'!M29</f>
         <v>20713</v>
       </c>
-      <c r="O82" s="351">
-        <f>SUM(E82:N82)</f>
+      <c r="O83" s="351">
+        <f>SUM(E83:N83)</f>
         <v>159028.166</v>
       </c>
     </row>
-    <row r="83" ht="17.2" customHeight="1">
-      <c r="B83" s="344">
+    <row r="84" ht="17.2" customHeight="1">
+      <c r="B84" s="344">
         <v>4</v>
       </c>
-      <c r="C83" s="343" t="inlineStr">
+      <c r="C84" s="343" t="inlineStr">
         <is>
           <t>Ingresos (USD) — Actualizado</t>
         </is>
       </c>
-      <c r="D83" s="342" t="inlineStr">
+      <c r="D84" s="342" t="inlineStr">
         <is>
           <t>Ingresos!D28:M28</t>
         </is>
       </c>
-      <c r="E83" s="350">
+      <c r="E84" s="350">
         <f>'Ingresos'!D28</f>
         <v>4208607.23095</v>
       </c>
-      <c r="F83" s="350">
+      <c r="F84" s="350">
         <f>'Ingresos'!E28</f>
         <v>17355345</v>
       </c>
-      <c r="G83" s="350">
+      <c r="G84" s="350">
         <f>'Ingresos'!F28</f>
         <v>18854496.150000002</v>
       </c>
-      <c r="H83" s="350">
+      <c r="H84" s="350">
         <f>'Ingresos'!G28</f>
         <v>20195139.069</v>
       </c>
-      <c r="I83" s="350">
+      <c r="I84" s="350">
         <f>'Ingresos'!H28</f>
         <v>21621692.26224</v>
       </c>
-      <c r="J83" s="350">
+      <c r="J84" s="350">
         <f>'Ingresos'!I28</f>
         <v>23156432.836210802</v>
       </c>
-      <c r="K83" s="350">
+      <c r="K84" s="350">
         <f>'Ingresos'!J28</f>
         <v>24800444.267548323</v>
       </c>
-      <c r="L83" s="350">
+      <c r="L84" s="350">
         <f>'Ingresos'!K28</f>
         <v>26553500.487099838</v>
       </c>
-      <c r="M83" s="350">
+      <c r="M84" s="350">
         <f>'Ingresos'!L28</f>
         <v>28438953.334089424</v>
       </c>
-      <c r="N83" s="350">
+      <c r="N84" s="350">
         <f>'Ingresos'!M28</f>
         <v>30456342.76795789</v>
       </c>
-      <c r="O83" s="351">
-        <f>SUM(E83:N83)</f>
-        <v>215640953.40509626</v>
-      </c>
-    </row>
-    <row r="84" ht="17.2" customHeight="1">
-      <c r="B84" s="344">
-        <v>5</v>
-      </c>
-      <c r="C84" s="343" t="inlineStr">
-        <is>
-          <t>Ingresos (USD) — Plan original</t>
-        </is>
-      </c>
-      <c r="D84" s="342" t="inlineStr">
-        <is>
-          <t>PPT jun-2026 (fijo)</t>
-        </is>
-      </c>
-      <c r="E84" s="352">
-        <v>10820400</v>
-      </c>
-      <c r="F84" s="352">
-        <v>13591134</v>
-      </c>
-      <c r="G84" s="352">
-        <v>14986567</v>
-      </c>
-      <c r="H84" s="352">
-        <v>16104783</v>
-      </c>
-      <c r="I84" s="352">
-        <v>17250523</v>
-      </c>
-      <c r="J84" s="352">
-        <v>18474024</v>
-      </c>
-      <c r="K84" s="352">
-        <v>19789483</v>
-      </c>
-      <c r="L84" s="352">
-        <v>21195174</v>
-      </c>
-      <c r="M84" s="352">
-        <v>22699886</v>
-      </c>
-      <c r="N84" s="352">
-        <v>24308765</v>
-      </c>
       <c r="O84" s="351">
         <f>SUM(E84:N84)</f>
-        <v>179220739</v>
+        <v>215640953.40509626</v>
       </c>
     </row>
     <row r="85" ht="17.2" customHeight="1">
       <c r="B85" s="344">
+        <v>5</v>
+      </c>
+      <c r="C85" s="343" t="inlineStr">
+        <is>
+          <t>Ingresos (USD) — Plan original</t>
+        </is>
+      </c>
+      <c r="D85" s="342" t="inlineStr">
+        <is>
+          <t>PPT jun-2026 (fijo)</t>
+        </is>
+      </c>
+      <c r="E85" s="352">
+        <v>10820400</v>
+      </c>
+      <c r="F85" s="352">
+        <v>13591134</v>
+      </c>
+      <c r="G85" s="352">
+        <v>14986567</v>
+      </c>
+      <c r="H85" s="352">
+        <v>16104783</v>
+      </c>
+      <c r="I85" s="352">
+        <v>17250523</v>
+      </c>
+      <c r="J85" s="352">
+        <v>18474024</v>
+      </c>
+      <c r="K85" s="352">
+        <v>19789483</v>
+      </c>
+      <c r="L85" s="352">
+        <v>21195174</v>
+      </c>
+      <c r="M85" s="352">
+        <v>22699886</v>
+      </c>
+      <c r="N85" s="352">
+        <v>24308765</v>
+      </c>
+      <c r="O85" s="351">
+        <f>SUM(E85:N85)</f>
+        <v>179220739</v>
+      </c>
+    </row>
+    <row r="86" ht="17.2" customHeight="1">
+      <c r="B86" s="344">
         <v>6</v>
       </c>
-      <c r="C85" s="343" t="inlineStr">
+      <c r="C86" s="343" t="inlineStr">
         <is>
           <t>Costos de producción (USD) — Actualizado</t>
         </is>
       </c>
-      <c r="D85" s="342" t="inlineStr">
+      <c r="D86" s="342" t="inlineStr">
         <is>
           <t>Resultados!C6:L6</t>
         </is>
       </c>
-      <c r="E85" s="350">
+      <c r="E86" s="350">
         <f>'Resultados'!C6</f>
         <v>4032136.443023058</v>
       </c>
-      <c r="F85" s="350">
+      <c r="F86" s="350">
         <f>'Resultados'!D6</f>
         <v>14668171.60410502</v>
       </c>
-      <c r="G85" s="350">
+      <c r="G86" s="350">
         <f>'Resultados'!E6</f>
         <v>15861608.209453648</v>
       </c>
-      <c r="H85" s="350">
+      <c r="H86" s="350">
         <f>'Resultados'!F6</f>
         <v>17138115.4123965</v>
       </c>
-      <c r="I85" s="350">
+      <c r="I86" s="350">
         <f>'Resultados'!G6</f>
         <v>18516472.728581738</v>
       </c>
-      <c r="J85" s="350">
+      <c r="J86" s="350">
         <f>'Resultados'!H6</f>
         <v>20007681.209758777</v>
       </c>
-      <c r="K85" s="350">
+      <c r="K86" s="350">
         <f>'Resultados'!I6</f>
         <v>21618460.33938418</v>
       </c>
-      <c r="L85" s="350">
+      <c r="L86" s="350">
         <f>'Resultados'!J6</f>
         <v>23358574.7747177</v>
       </c>
-      <c r="M85" s="350">
+      <c r="M86" s="350">
         <f>'Resultados'!K6</f>
         <v>25243293.25831479</v>
       </c>
-      <c r="N85" s="350">
+      <c r="N86" s="350">
         <f>'Resultados'!L6</f>
         <v>27278714.81756568</v>
       </c>
-      <c r="O85" s="351">
-        <f>SUM(E85:N85)</f>
-        <v>187723228.79730108</v>
-      </c>
-    </row>
-    <row r="86" ht="30.4" customHeight="1">
-      <c r="B86" s="344">
-        <v>7</v>
-      </c>
-      <c r="C86" s="343" t="inlineStr">
-        <is>
-          <t>Costos de producción (USD) — Plan original</t>
-        </is>
-      </c>
-      <c r="D86" s="342" t="inlineStr">
-        <is>
-          <t>PPT jun-2026 (fijo)</t>
-        </is>
-      </c>
-      <c r="E86" s="352">
-        <v>9852158</v>
-      </c>
-      <c r="F86" s="352">
-        <v>11621795</v>
-      </c>
-      <c r="G86" s="352">
-        <v>12557052</v>
-      </c>
-      <c r="H86" s="352">
-        <v>13563820</v>
-      </c>
-      <c r="I86" s="352">
-        <v>14652622</v>
-      </c>
-      <c r="J86" s="352">
-        <v>15829707</v>
-      </c>
-      <c r="K86" s="352">
-        <v>17102792</v>
-      </c>
-      <c r="L86" s="352">
-        <v>18477528</v>
-      </c>
-      <c r="M86" s="352">
-        <v>19963439</v>
-      </c>
-      <c r="N86" s="352">
-        <v>21569494</v>
-      </c>
       <c r="O86" s="351">
         <f>SUM(E86:N86)</f>
+        <v>187723228.79730108</v>
+      </c>
+    </row>
+    <row r="87" ht="30.4" customHeight="1">
+      <c r="B87" s="344">
+        <v>7</v>
+      </c>
+      <c r="C87" s="343" t="inlineStr">
+        <is>
+          <t>Costos de producción (USD) — Plan original</t>
+        </is>
+      </c>
+      <c r="D87" s="342" t="inlineStr">
+        <is>
+          <t>PPT jun-2026 (fijo)</t>
+        </is>
+      </c>
+      <c r="E87" s="352">
+        <v>9852158</v>
+      </c>
+      <c r="F87" s="352">
+        <v>11621795</v>
+      </c>
+      <c r="G87" s="352">
+        <v>12557052</v>
+      </c>
+      <c r="H87" s="352">
+        <v>13563820</v>
+      </c>
+      <c r="I87" s="352">
+        <v>14652622</v>
+      </c>
+      <c r="J87" s="352">
+        <v>15829707</v>
+      </c>
+      <c r="K87" s="352">
+        <v>17102792</v>
+      </c>
+      <c r="L87" s="352">
+        <v>18477528</v>
+      </c>
+      <c r="M87" s="352">
+        <v>19963439</v>
+      </c>
+      <c r="N87" s="352">
+        <v>21569494</v>
+      </c>
+      <c r="O87" s="351">
+        <f>SUM(E87:N87)</f>
         <v>155190407</v>
       </c>
     </row>
-    <row r="87" ht="17.2" customHeight="1">
-      <c r="B87" s="344">
+    <row r="88" ht="17.2" customHeight="1">
+      <c r="B88" s="344">
         <v>8</v>
       </c>
-      <c r="C87" s="343" t="inlineStr">
+      <c r="C88" s="343" t="inlineStr">
         <is>
           <t>EBITDA (USD) — Actualizado</t>
         </is>
       </c>
-      <c r="D87" s="342" t="inlineStr">
+      <c r="D88" s="342" t="inlineStr">
         <is>
           <t>Resultados!C9:L9</t>
         </is>
       </c>
-      <c r="E87" s="350">
+      <c r="E88" s="350">
         <f>'Resultados'!C9</f>
         <v>-23859.585545666167</v>
       </c>
-      <c r="F87" s="350">
+      <c r="F88" s="350">
         <f>'Resultados'!D9</f>
         <v>2449376.1146034813</v>
       </c>
-      <c r="G87" s="350">
+      <c r="G88" s="350">
         <f>'Resultados'!E9</f>
         <v>2750225.2471809983</v>
       </c>
-      <c r="H87" s="350">
+      <c r="H88" s="350">
         <f>'Resultados'!F9</f>
         <v>2810091.8644371796</v>
       </c>
-      <c r="I87" s="350">
+      <c r="I88" s="350">
         <f>'Resultados'!G9</f>
         <v>2853865.5314269564</v>
       </c>
-      <c r="J87" s="350">
+      <c r="J88" s="350">
         <f>'Resultados'!H9</f>
         <v>2892816.4576387797</v>
       </c>
-      <c r="K87" s="350">
+      <c r="K88" s="350">
         <f>'Resultados'!I9</f>
         <v>2921302.5530457506</v>
       </c>
-      <c r="L87" s="350">
+      <c r="L88" s="350">
         <f>'Resultados'!J9</f>
         <v>2929326.759807406</v>
       </c>
-      <c r="M87" s="350">
+      <c r="M88" s="350">
         <f>'Resultados'!K9</f>
         <v>2924965.5842097355</v>
       </c>
-      <c r="N87" s="350">
+      <c r="N88" s="350">
         <f>'Resultados'!L9</f>
         <v>2901653.097746788</v>
       </c>
-      <c r="O87" s="351">
-        <f>SUM(E87:N87)</f>
-        <v>25409763.624551408</v>
-      </c>
-    </row>
-    <row r="88" ht="17.2" customHeight="1">
-      <c r="B88" s="344">
-        <v>9</v>
-      </c>
-      <c r="C88" s="343" t="inlineStr">
-        <is>
-          <t>EBITDA (USD) — Plan original</t>
-        </is>
-      </c>
-      <c r="D88" s="342" t="inlineStr">
-        <is>
-          <t>PPT jun-2026 (fijo)</t>
-        </is>
-      </c>
-      <c r="E88" s="352">
-        <v>732980</v>
-      </c>
-      <c r="F88" s="352">
-        <v>1734077</v>
-      </c>
-      <c r="G88" s="352">
-        <v>2192768</v>
-      </c>
-      <c r="H88" s="352">
-        <v>2302686</v>
-      </c>
-      <c r="I88" s="352">
-        <v>2358049</v>
-      </c>
-      <c r="J88" s="352">
-        <v>2402842</v>
-      </c>
-      <c r="K88" s="352">
-        <v>2443544</v>
-      </c>
-      <c r="L88" s="352">
-        <v>2472777</v>
-      </c>
-      <c r="M88" s="352">
-        <v>2489805</v>
-      </c>
-      <c r="N88" s="352">
-        <v>2490803</v>
-      </c>
       <c r="O88" s="351">
         <f>SUM(E88:N88)</f>
-        <v>21620331</v>
+        <v>25409763.624551408</v>
       </c>
     </row>
     <row r="89" ht="17.2" customHeight="1">
       <c r="B89" s="344">
+        <v>9</v>
+      </c>
+      <c r="C89" s="343" t="inlineStr">
+        <is>
+          <t>EBITDA (USD) — Plan original</t>
+        </is>
+      </c>
+      <c r="D89" s="342" t="inlineStr">
+        <is>
+          <t>PPT jun-2026 (fijo)</t>
+        </is>
+      </c>
+      <c r="E89" s="352">
+        <v>732980</v>
+      </c>
+      <c r="F89" s="352">
+        <v>1734077</v>
+      </c>
+      <c r="G89" s="352">
+        <v>2192768</v>
+      </c>
+      <c r="H89" s="352">
+        <v>2302686</v>
+      </c>
+      <c r="I89" s="352">
+        <v>2358049</v>
+      </c>
+      <c r="J89" s="352">
+        <v>2402842</v>
+      </c>
+      <c r="K89" s="352">
+        <v>2443544</v>
+      </c>
+      <c r="L89" s="352">
+        <v>2472777</v>
+      </c>
+      <c r="M89" s="352">
+        <v>2489805</v>
+      </c>
+      <c r="N89" s="352">
+        <v>2490803</v>
+      </c>
+      <c r="O89" s="351">
+        <f>SUM(E89:N89)</f>
+        <v>21620331</v>
+      </c>
+    </row>
+    <row r="90" ht="17.2" customHeight="1">
+      <c r="B90" s="344">
         <v>10</v>
       </c>
-      <c r="C89" s="343" t="inlineStr">
+      <c r="C90" s="343" t="inlineStr">
         <is>
           <t>Utilidad neta (USD) — Actualizado</t>
         </is>
       </c>
-      <c r="D89" s="342" t="inlineStr">
+      <c r="D90" s="342" t="inlineStr">
         <is>
           <t>Resultados!C14:L14</t>
         </is>
       </c>
-      <c r="E89" s="350">
+      <c r="E90" s="350">
         <f>'Resultados'!C14</f>
         <v>-334777.752861543</v>
       </c>
-      <c r="F89" s="350">
+      <c r="F90" s="350">
         <f>'Resultados'!D14</f>
         <v>1480799.445797248</v>
       </c>
-      <c r="G89" s="350">
+      <c r="G90" s="350">
         <f>'Resultados'!E14</f>
         <v>1582364.1727693735</v>
       </c>
-      <c r="H89" s="350">
+      <c r="H90" s="350">
         <f>'Resultados'!F14</f>
         <v>1957769.1648346798</v>
       </c>
-      <c r="I89" s="350">
+      <c r="I90" s="350">
         <f>'Resultados'!G14</f>
         <v>2059600.387129505</v>
       </c>
-      <c r="J89" s="350">
+      <c r="J90" s="350">
         <f>'Resultados'!H14</f>
         <v>2108638.0888499077</v>
       </c>
-      <c r="K89" s="350">
+      <c r="K90" s="350">
         <f>'Resultados'!I14</f>
         <v>2403682.9350278014</v>
       </c>
-      <c r="L89" s="350">
+      <c r="L90" s="350">
         <f>'Resultados'!J14</f>
         <v>2348149.1823336678</v>
       </c>
-      <c r="M89" s="350">
+      <c r="M90" s="350">
         <f>'Resultados'!K14</f>
         <v>2282851.2864852794</v>
       </c>
-      <c r="N89" s="350">
+      <c r="N90" s="350">
         <f>'Resultados'!L14</f>
         <v>2140077.2344507705</v>
       </c>
-      <c r="O89" s="351">
-        <f>SUM(E89:N89)</f>
+      <c r="O90" s="351">
+        <f>SUM(E90:N90)</f>
         <v>18029154.14481669</v>
       </c>
     </row>
-    <row r="90" ht="17.2" customHeight="1">
-      <c r="B90" s="344">
+    <row r="91" ht="17.2" customHeight="1">
+      <c r="B91" s="344">
         <v>11</v>
       </c>
-      <c r="C90" s="343" t="inlineStr">
+      <c r="C91" s="343" t="inlineStr">
         <is>
           <t>Margen EBITDA — Actualizado</t>
         </is>
       </c>
-      <c r="D90" s="342" t="inlineStr">
+      <c r="D91" s="342" t="inlineStr">
         <is>
           <t>EBITDA / Ingresos</t>
         </is>
       </c>
-      <c r="E90" s="355">
+      <c r="E91" s="355">
         <f>IF('Ingresos'!D28=0,0,'Resultados'!C9/'Ingresos'!D28)</f>
         <v>-0.005669235506274696</v>
       </c>
-      <c r="F90" s="355">
+      <c r="F91" s="355">
         <f>IF('Ingresos'!E28=0,0,'Resultados'!D9/'Ingresos'!E28)</f>
         <v>0.14113093773724933</v>
       </c>
-      <c r="G90" s="355">
+      <c r="G91" s="355">
         <f>IF('Ingresos'!F28=0,0,'Resultados'!E9/'Ingresos'!F28)</f>
         <v>0.14586575134658256</v>
       </c>
-      <c r="H90" s="355">
+      <c r="H91" s="355">
         <f>IF('Ingresos'!G28=0,0,'Resultados'!F9/'Ingresos'!G28)</f>
         <v>0.13914694297652722</v>
       </c>
-      <c r="I90" s="355">
+      <c r="I91" s="355">
         <f>IF('Ingresos'!H28=0,0,'Resultados'!G9/'Ingresos'!H28)</f>
         <v>0.13199084959741708</v>
       </c>
-      <c r="J90" s="355">
+      <c r="J91" s="355">
         <f>IF('Ingresos'!I28=0,0,'Resultados'!H9/'Ingresos'!I28)</f>
         <v>0.12492496051097933</v>
       </c>
-      <c r="K90" s="355">
+      <c r="K91" s="355">
         <f>IF('Ingresos'!J28=0,0,'Resultados'!I9/'Ingresos'!J28)</f>
         <v>0.11779234765033261</v>
       </c>
-      <c r="L90" s="355">
+      <c r="L91" s="355">
         <f>IF('Ingresos'!K28=0,0,'Resultados'!J9/'Ingresos'!K28)</f>
         <v>0.11031791312149315</v>
       </c>
-      <c r="M90" s="355">
+      <c r="M91" s="355">
         <f>IF('Ingresos'!L28=0,0,'Resultados'!K9/'Ingresos'!L28)</f>
         <v>0.10285067631879459</v>
       </c>
-      <c r="N90" s="355">
+      <c r="N91" s="355">
         <f>IF('Ingresos'!M28=0,0,'Resultados'!L9/'Ingresos'!M28)</f>
         <v>0.09527253878950698</v>
       </c>
-      <c r="O90" s="356">
-        <f>IF(O83=0,0,O87/O83)</f>
+      <c r="O91" s="356">
+        <f>IF(O84=0,0,O88/O84)</f>
         <v>0.11783366389044585</v>
       </c>
     </row>
-    <row r="91" ht="17.2" customHeight="1">
-      <c r="B91" s="344">
+    <row r="92" ht="17.2" customHeight="1">
+      <c r="B92" s="344">
         <v>12</v>
       </c>
-      <c r="C91" s="343" t="inlineStr">
+      <c r="C92" s="343" t="inlineStr">
         <is>
           <t>Margen neto — Actualizado</t>
         </is>
       </c>
-      <c r="D91" s="342" t="inlineStr">
+      <c r="D92" s="342" t="inlineStr">
         <is>
           <t>Utilidad neta / Ingresos</t>
         </is>
       </c>
-      <c r="E91" s="355">
+      <c r="E92" s="355">
         <f>IF('Ingresos'!D28=0,0,'Resultados'!C14/'Ingresos'!D28)</f>
         <v>-0.07954597197847192</v>
       </c>
-      <c r="F91" s="355">
+      <c r="F92" s="355">
         <f>IF('Ingresos'!E28=0,0,'Resultados'!D14/'Ingresos'!E28)</f>
         <v>0.08532238603134931</v>
       </c>
-      <c r="G91" s="355">
+      <c r="G92" s="355">
         <f>IF('Ingresos'!F28=0,0,'Resultados'!E14/'Ingresos'!F28)</f>
         <v>0.08392503094119401</v>
       </c>
-      <c r="H91" s="355">
+      <c r="H92" s="355">
         <f>IF('Ingresos'!G28=0,0,'Resultados'!F14/'Ingresos'!G28)</f>
         <v>0.09694259386606059</v>
       </c>
-      <c r="I91" s="355">
+      <c r="I92" s="355">
         <f>IF('Ingresos'!H28=0,0,'Resultados'!G14/'Ingresos'!H28)</f>
         <v>0.09525620669046239</v>
       </c>
-      <c r="J91" s="355">
+      <c r="J92" s="355">
         <f>IF('Ingresos'!I28=0,0,'Resultados'!H14/'Ingresos'!I28)</f>
         <v>0.09106057499290354</v>
       </c>
-      <c r="K91" s="355">
+      <c r="K92" s="355">
         <f>IF('Ingresos'!J28=0,0,'Resultados'!I14/'Ingresos'!J28)</f>
         <v>0.09692096274956853</v>
       </c>
-      <c r="L91" s="355">
+      <c r="L92" s="355">
         <f>IF('Ingresos'!K28=0,0,'Resultados'!J14/'Ingresos'!K28)</f>
         <v>0.0884308712320035</v>
       </c>
-      <c r="M91" s="355">
+      <c r="M92" s="355">
         <f>IF('Ingresos'!L28=0,0,'Resultados'!K14/'Ingresos'!L28)</f>
         <v>0.0802719867945651</v>
       </c>
-      <c r="N91" s="355">
+      <c r="N92" s="355">
         <f>IF('Ingresos'!M28=0,0,'Resultados'!L14/'Ingresos'!M28)</f>
         <v>0.07026704587466999</v>
       </c>
-      <c r="O91" s="356">
-        <f>IF(O83=0,0,O89/O83)</f>
+      <c r="O92" s="356">
+        <f>IF(O84=0,0,O90/O84)</f>
         <v>0.08360728266187774</v>
       </c>
     </row>
-    <row r="92" ht="17.2" customHeight="1">
-      <c r="B92" s="344">
+    <row r="93" ht="17.2" customHeight="1">
+      <c r="B93" s="344">
         <v>13</v>
       </c>
-      <c r="C92" s="343" t="inlineStr">
+      <c r="C93" s="343" t="inlineStr">
         <is>
           <t>Punto de equilibrio (Tn) — Actualizado</t>
         </is>
       </c>
-      <c r="D92" s="342" t="inlineStr">
+      <c r="D93" s="342" t="inlineStr">
         <is>
           <t>Pto Equilibrio!C14:L14</t>
         </is>
       </c>
-      <c r="E92" s="350">
+      <c r="E93" s="350">
         <f>'Pto Equilibrio'!C14</f>
         <v>8239.515130848906</v>
       </c>
-      <c r="F92" s="350">
+      <c r="F93" s="350">
         <f>'Pto Equilibrio'!D14</f>
         <v>6815.949572386749</v>
       </c>
-      <c r="G92" s="350">
+      <c r="G93" s="350">
         <f>'Pto Equilibrio'!E14</f>
         <v>7304.162315438446</v>
       </c>
-      <c r="H92" s="350">
+      <c r="H93" s="350">
         <f>'Pto Equilibrio'!F14</f>
         <v>6201.196467253019</v>
       </c>
-      <c r="I92" s="350">
+      <c r="I93" s="350">
         <f>'Pto Equilibrio'!G14</f>
         <v>6204.048889092515</v>
       </c>
-      <c r="J92" s="350">
+      <c r="J93" s="350">
         <f>'Pto Equilibrio'!H14</f>
         <v>6432.656678767174</v>
       </c>
-      <c r="K92" s="350">
+      <c r="K93" s="350">
         <f>'Pto Equilibrio'!I14</f>
         <v>5492.014953996452</v>
       </c>
-      <c r="L92" s="350">
+      <c r="L93" s="350">
         <f>'Pto Equilibrio'!J14</f>
         <v>6115.221619788001</v>
       </c>
-      <c r="M92" s="350">
+      <c r="M93" s="350">
         <f>'Pto Equilibrio'!K14</f>
         <v>6789.379819778335</v>
       </c>
-      <c r="N92" s="350">
+      <c r="N93" s="350">
         <f>'Pto Equilibrio'!L14</f>
         <v>7854.421027770492</v>
       </c>
-      <c r="O92" s="342"/>
-    </row>
-    <row r="93" ht="17.2" customHeight="1">
-      <c r="B93" s="344">
-        <v>14</v>
-      </c>
-      <c r="C93" s="343" t="inlineStr">
-        <is>
-          <t>Margen de seguridad — Actualizado</t>
-        </is>
-      </c>
-      <c r="D93" s="342" t="inlineStr">
-        <is>
-          <t>1 − punto de equilibrio / ventas (Tn)</t>
-        </is>
-      </c>
-      <c r="E93" s="355">
-        <f>IF(E82=0,0,1-E92/E82)</f>
-        <v>-0.9640498447138697</v>
-      </c>
-      <c r="F93" s="355">
-        <f>IF(F82=0,0,1-F92/F82)</f>
-        <v>0.5211837321821743</v>
-      </c>
-      <c r="G93" s="355">
-        <f>IF(G82=0,0,1-G92/G82)</f>
-        <v>0.5039954967106854</v>
-      </c>
-      <c r="H93" s="355">
-        <f>IF(H82=0,0,1-H92/H82)</f>
-        <v>0.598991433829991</v>
-      </c>
-      <c r="I93" s="355">
-        <f>IF(I82=0,0,1-I92/I82)</f>
-        <v>0.6178596310999375</v>
-      </c>
-      <c r="J93" s="355">
-        <f>IF(J82=0,0,1-J92/J82)</f>
-        <v>0.6226295507000368</v>
-      </c>
-      <c r="K93" s="355">
-        <f>IF(K82=0,0,1-K92/K82)</f>
-        <v>0.6931320917474184</v>
-      </c>
-      <c r="L93" s="355">
-        <f>IF(L82=0,0,1-L92/L82)</f>
-        <v>0.6745318207574644</v>
-      </c>
-      <c r="M93" s="355">
-        <f>IF(M82=0,0,1-M92/M82)</f>
-        <v>0.6558505768563293</v>
-      </c>
-      <c r="N93" s="355">
-        <f>IF(N82=0,0,1-N92/N82)</f>
-        <v>0.6207975171259358</v>
-      </c>
       <c r="O93" s="342"/>
     </row>
     <row r="94" ht="17.2" customHeight="1">
       <c r="B94" s="344">
+        <v>14</v>
+      </c>
+      <c r="C94" s="343" t="inlineStr">
+        <is>
+          <t>Margen de seguridad — Actualizado</t>
+        </is>
+      </c>
+      <c r="D94" s="342" t="inlineStr">
+        <is>
+          <t>1 − punto de equilibrio / ventas (Tn)</t>
+        </is>
+      </c>
+      <c r="E94" s="355">
+        <f>IF(E83=0,0,1-E93/E83)</f>
+        <v>-0.9640498447138697</v>
+      </c>
+      <c r="F94" s="355">
+        <f>IF(F83=0,0,1-F93/F83)</f>
+        <v>0.5211837321821743</v>
+      </c>
+      <c r="G94" s="355">
+        <f>IF(G83=0,0,1-G93/G83)</f>
+        <v>0.5039954967106854</v>
+      </c>
+      <c r="H94" s="355">
+        <f>IF(H83=0,0,1-H93/H83)</f>
+        <v>0.598991433829991</v>
+      </c>
+      <c r="I94" s="355">
+        <f>IF(I83=0,0,1-I93/I83)</f>
+        <v>0.6178596310999375</v>
+      </c>
+      <c r="J94" s="355">
+        <f>IF(J83=0,0,1-J93/J83)</f>
+        <v>0.6226295507000368</v>
+      </c>
+      <c r="K94" s="355">
+        <f>IF(K83=0,0,1-K93/K83)</f>
+        <v>0.6931320917474184</v>
+      </c>
+      <c r="L94" s="355">
+        <f>IF(L83=0,0,1-L93/L83)</f>
+        <v>0.6745318207574644</v>
+      </c>
+      <c r="M94" s="355">
+        <f>IF(M83=0,0,1-M93/M83)</f>
+        <v>0.6558505768563293</v>
+      </c>
+      <c r="N94" s="355">
+        <f>IF(N83=0,0,1-N93/N83)</f>
+        <v>0.6207975171259358</v>
+      </c>
+      <c r="O94" s="342"/>
+    </row>
+    <row r="95" ht="17.2" customHeight="1">
+      <c r="B95" s="344">
         <v>15</v>
       </c>
-      <c r="C94" s="343" t="inlineStr">
+      <c r="C95" s="343" t="inlineStr">
         <is>
           <t>Préstamos CP para chapas (USD/año)</t>
         </is>
       </c>
-      <c r="D94" s="342" t="inlineStr">
+      <c r="D95" s="342" t="inlineStr">
         <is>
           <t>Ej_Flujo!O8, AB8, AO8 … EB8</t>
         </is>
       </c>
-      <c r="E94" s="350">
+      <c r="E95" s="350">
         <f>'Ej_Flujo'!O8</f>
         <v>0</v>
       </c>
-      <c r="F94" s="350">
+      <c r="F95" s="350">
         <f>'Ej_Flujo'!AB8</f>
         <v>10900000</v>
       </c>
-      <c r="G94" s="350">
+      <c r="G95" s="350">
         <f>'Ej_Flujo'!AO8</f>
         <v>11900000</v>
       </c>
-      <c r="H94" s="350">
+      <c r="H95" s="350">
         <f>'Ej_Flujo'!BB8</f>
         <v>5000000</v>
       </c>
-      <c r="I94" s="350">
+      <c r="I95" s="350">
         <f>'Ej_Flujo'!BO8</f>
         <v>6200000</v>
       </c>
-      <c r="J94" s="350">
+      <c r="J95" s="350">
         <f>'Ej_Flujo'!CB8</f>
         <v>6000000</v>
       </c>
-      <c r="K94" s="350">
+      <c r="K95" s="350">
         <f>'Ej_Flujo'!CO8</f>
         <v>4000000</v>
       </c>
-      <c r="L94" s="350">
+      <c r="L95" s="350">
         <f>'Ej_Flujo'!DB8</f>
         <v>5300000</v>
       </c>
-      <c r="M94" s="350">
+      <c r="M95" s="350">
         <f>'Ej_Flujo'!DO8</f>
         <v>5300000</v>
       </c>
-      <c r="N94" s="350">
+      <c r="N95" s="350">
         <f>'Ej_Flujo'!EB8</f>
         <v>7000000</v>
       </c>
-      <c r="O94" s="351">
-        <f>SUM(E94:N94)</f>
+      <c r="O95" s="351">
+        <f>SUM(E95:N95)</f>
         <v>61600000</v>
       </c>
     </row>
-    <row r="95" ht="17.2" customHeight="1">
-      <c r="B95" s="344">
+    <row r="96" ht="17.2" customHeight="1">
+      <c r="B96" s="344">
         <v>16</v>
       </c>
-      <c r="C95" s="343" t="inlineStr">
+      <c r="C96" s="343" t="inlineStr">
         <is>
           <t>Capital de trabajo neto (USD)</t>
         </is>
       </c>
-      <c r="D95" s="342" t="inlineStr">
+      <c r="D96" s="342" t="inlineStr">
         <is>
           <t>Capital Trabajo!C18:L18</t>
         </is>
       </c>
-      <c r="E95" s="350">
+      <c r="E96" s="350">
         <f>'Capital Trabajo'!C18</f>
         <v>1541094.4312681279</v>
       </c>
-      <c r="F95" s="350">
+      <c r="F96" s="350">
         <f>'Capital Trabajo'!D18</f>
         <v>6115600.303155011</v>
       </c>
-      <c r="G95" s="350">
+      <c r="G96" s="350">
         <f>'Capital Trabajo'!E18</f>
         <v>6634952.553563189</v>
       </c>
-      <c r="H95" s="350">
+      <c r="H96" s="350">
         <f>'Capital Trabajo'!F18</f>
         <v>7125811.3987322375</v>
       </c>
-      <c r="I95" s="350">
+      <c r="I96" s="350">
         <f>'Capital Trabajo'!G18</f>
         <v>7650561.367870811</v>
       </c>
-      <c r="J95" s="350">
+      <c r="J96" s="350">
         <f>'Capital Trabajo'!H18</f>
         <v>8216141.11296786</v>
       </c>
-      <c r="K95" s="350">
+      <c r="K96" s="350">
         <f>'Capital Trabajo'!I18</f>
         <v>8823630.459126458</v>
       </c>
-      <c r="L95" s="350">
+      <c r="L96" s="350">
         <f>'Capital Trabajo'!J18</f>
         <v>9474146.132618628</v>
       </c>
-      <c r="M95" s="350">
+      <c r="M96" s="350">
         <f>'Capital Trabajo'!K18</f>
         <v>10175411.345889574</v>
       </c>
-      <c r="N95" s="350">
+      <c r="N96" s="350">
         <f>'Capital Trabajo'!L18</f>
         <v>10928040.580366578</v>
       </c>
-      <c r="O95" s="342"/>
-    </row>
-    <row r="96" ht="17.2" customHeight="1">
-      <c r="B96" s="344">
+      <c r="O96" s="342"/>
+    </row>
+    <row r="97" ht="17.2" customHeight="1">
+      <c r="B97" s="344">
         <v>17</v>
       </c>
-      <c r="C96" s="343" t="inlineStr">
+      <c r="C97" s="343" t="inlineStr">
         <is>
           <t>Cuentas por cobrar (USD)</t>
         </is>
       </c>
-      <c r="D96" s="342" t="inlineStr">
+      <c r="D97" s="342" t="inlineStr">
         <is>
           <t>Capital Trabajo!C9:L9</t>
         </is>
       </c>
-      <c r="E96" s="350">
+      <c r="E97" s="350">
         <f>'Capital Trabajo'!C9</f>
         <v>1037738.7692753423</v>
       </c>
-      <c r="F96" s="350">
+      <c r="F97" s="350">
         <f>'Capital Trabajo'!D9</f>
         <v>4279400.136986301</v>
       </c>
-      <c r="G96" s="350">
+      <c r="G97" s="350">
         <f>'Capital Trabajo'!E9</f>
         <v>4649053.84520548</v>
       </c>
-      <c r="H96" s="350">
+      <c r="H97" s="350">
         <f>'Capital Trabajo'!F9</f>
         <v>4979623.3320821915</v>
       </c>
-      <c r="I96" s="350">
+      <c r="I97" s="350">
         <f>'Capital Trabajo'!G9</f>
         <v>5331376.1742509585</v>
       </c>
-      <c r="J96" s="350">
+      <c r="J97" s="350">
         <f>'Capital Trabajo'!H9</f>
         <v>5709805.356873896</v>
       </c>
-      <c r="K96" s="350">
+      <c r="K97" s="350">
         <f>'Capital Trabajo'!I9</f>
         <v>6115178.038573558</v>
       </c>
-      <c r="L96" s="350">
+      <c r="L97" s="350">
         <f>'Capital Trabajo'!J9</f>
         <v>6547438.476271193</v>
       </c>
-      <c r="M96" s="350">
+      <c r="M97" s="350">
         <f>'Capital Trabajo'!K9</f>
         <v>7012344.657720679</v>
       </c>
-      <c r="N96" s="350">
+      <c r="N97" s="350">
         <f>'Capital Trabajo'!L9</f>
         <v>7509783.1482635895</v>
       </c>
-      <c r="O96" s="342"/>
-    </row>
-    <row r="97" ht="17.2" customHeight="1">
-      <c r="B97" s="344">
+      <c r="O97" s="342"/>
+    </row>
+    <row r="98" ht="17.2" customHeight="1">
+      <c r="B98" s="344">
         <v>18</v>
       </c>
-      <c r="C97" s="343" t="inlineStr">
+      <c r="C98" s="343" t="inlineStr">
         <is>
           <t>Gastos financieros LP + CP (USD)</t>
         </is>
       </c>
-      <c r="D97" s="342" t="inlineStr">
+      <c r="D98" s="342" t="inlineStr">
         <is>
           <t>Resultados!C11:L11</t>
         </is>
       </c>
-      <c r="E97" s="350">
+      <c r="E98" s="350">
         <f>'Resultados'!C11</f>
         <v>229420.38749922696</v>
       </c>
-      <c r="F97" s="350">
+      <c r="F98" s="350">
         <f>'Resultados'!D11</f>
         <v>699654.618806233</v>
       </c>
-      <c r="G97" s="350">
+      <c r="G98" s="350">
         <f>'Resultados'!E11</f>
         <v>883947.5129116247</v>
       </c>
-      <c r="H97" s="350">
+      <c r="H98" s="350">
         <f>'Resultados'!F11</f>
         <v>555002.7089125</v>
       </c>
-      <c r="I97" s="350">
+      <c r="I98" s="350">
         <f>'Resultados'!G11</f>
         <v>482679.6216750512</v>
       </c>
-      <c r="J97" s="350">
+      <c r="J98" s="350">
         <f>'Resultados'!H11</f>
         <v>457245.44042676385</v>
       </c>
-      <c r="K97" s="350">
+      <c r="K98" s="350">
         <f>'Resultados'!I11</f>
         <v>174246.57534246577</v>
       </c>
-      <c r="L97" s="350">
+      <c r="L98" s="350">
         <f>'Resultados'!J11</f>
         <v>220273.97260273976</v>
       </c>
-      <c r="M97" s="350">
+      <c r="M98" s="350">
         <f>'Resultados'!K11</f>
         <v>262356.16438356164</v>
       </c>
-      <c r="N97" s="350">
+      <c r="N98" s="350">
         <f>'Resultados'!L11</f>
         <v>361643.8356164384</v>
       </c>
-      <c r="O97" s="351">
-        <f>SUM(E97:N97)</f>
+      <c r="O98" s="351">
+        <f>SUM(E98:N98)</f>
         <v>4326470.838176605</v>
       </c>
     </row>
-    <row r="98" ht="17.2" customHeight="1">
-      <c r="B98" s="344">
+    <row r="99" ht="17.2" customHeight="1">
+      <c r="B99" s="344">
         <v>19</v>
       </c>
-      <c r="C98" s="343" t="inlineStr">
+      <c r="C99" s="343" t="inlineStr">
         <is>
           <t>Materia prima (USD)</t>
         </is>
       </c>
-      <c r="D98" s="342" t="inlineStr">
+      <c r="D99" s="342" t="inlineStr">
         <is>
           <t>Costos!D6:M6</t>
         </is>
       </c>
-      <c r="E98" s="350">
+      <c r="E99" s="350">
         <f>'Costos'!D6</f>
         <v>3876548.1750011332</v>
       </c>
-      <c r="F98" s="350">
+      <c r="F99" s="350">
         <f>'Costos'!E6</f>
         <v>14101733.588170895</v>
       </c>
-      <c r="G98" s="350">
+      <c r="G99" s="350">
         <f>'Costos'!F6</f>
         <v>15254335.845277237</v>
       </c>
-      <c r="H98" s="350">
+      <c r="H99" s="350">
         <f>'Costos'!G6</f>
         <v>16498216.667481313</v>
       </c>
-      <c r="I98" s="350">
+      <c r="I99" s="350">
         <f>'Costos'!H6</f>
         <v>17841772.2833685</v>
       </c>
-      <c r="J98" s="350">
+      <c r="J99" s="350">
         <f>'Costos'!I6</f>
         <v>19295790.55297855</v>
       </c>
-      <c r="K98" s="350">
+      <c r="K99" s="350">
         <f>'Costos'!J6</f>
         <v>20866848.258718</v>
       </c>
-      <c r="L98" s="350">
+      <c r="L99" s="350">
         <f>'Costos'!K6</f>
         <v>22564513.049915385</v>
       </c>
-      <c r="M98" s="350">
+      <c r="M99" s="350">
         <f>'Costos'!L6</f>
         <v>24403760.19800815</v>
       </c>
-      <c r="N98" s="350">
+      <c r="N99" s="350">
         <f>'Costos'!M6</f>
         <v>26390547.22246354</v>
       </c>
-      <c r="O98" s="351">
-        <f>SUM(E98:N98)</f>
+      <c r="O99" s="351">
+        <f>SUM(E99:N99)</f>
         <v>181094065.8413827</v>
       </c>
     </row>
-    <row r="100" ht="20" customHeight="1">
-      <c r="B100" s="339" t="inlineStr">
+    <row r="101" ht="20" customHeight="1">
+      <c r="B101" s="339" t="inlineStr">
         <is>
           <t>4. PLAN ORIGINAL — VALORES DE REFERENCIA (fijos; no están en el Excel: vienen del PPT de junio 2026)</t>
         </is>
       </c>
-      <c r="C100" s="339"/>
-      <c r="D100" s="339"/>
-      <c r="E100" s="339"/>
-      <c r="F100" s="339"/>
-      <c r="G100" s="339"/>
-      <c r="H100" s="339"/>
-      <c r="I100" s="339"/>
-      <c r="J100" s="339"/>
-      <c r="K100" s="339"/>
-      <c r="L100" s="339"/>
-      <c r="M100" s="339"/>
-      <c r="N100" s="339"/>
-      <c r="O100" s="339"/>
-    </row>
-    <row r="101" ht="20" customHeight="1">
-      <c r="B101" s="340" t="inlineStr">
+      <c r="C101" s="339"/>
+      <c r="D101" s="339"/>
+      <c r="E101" s="339"/>
+      <c r="F101" s="339"/>
+      <c r="G101" s="339"/>
+      <c r="H101" s="339"/>
+      <c r="I101" s="339"/>
+      <c r="J101" s="339"/>
+      <c r="K101" s="339"/>
+      <c r="L101" s="339"/>
+      <c r="M101" s="339"/>
+      <c r="N101" s="339"/>
+      <c r="O101" s="339"/>
+    </row>
+    <row r="102" ht="20" customHeight="1">
+      <c r="B102" s="340" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C101" s="340" t="inlineStr">
+      <c r="C102" s="340" t="inlineStr">
         <is>
           <t>Dato</t>
         </is>
       </c>
-      <c r="D101" s="340" t="inlineStr">
+      <c r="D102" s="340" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="E101" s="340" t="inlineStr">
+      <c r="E102" s="340" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
       </c>
-      <c r="F101" s="341" t="inlineStr">
+      <c r="F102" s="341" t="inlineStr">
         <is>
           <t>Observación</t>
         </is>
       </c>
-      <c r="G101" s="341"/>
-      <c r="H101" s="341"/>
-      <c r="I101" s="341"/>
-      <c r="J101" s="341"/>
-      <c r="K101" s="341"/>
-      <c r="L101" s="341"/>
-      <c r="M101" s="341"/>
-      <c r="N101" s="341"/>
-      <c r="O101" s="341"/>
-    </row>
-    <row r="102" ht="17.2" customHeight="1">
-      <c r="B102" s="344">
-        <v>1</v>
-      </c>
-      <c r="C102" s="343" t="inlineStr">
-        <is>
-          <t>VAN con financiamiento — plan</t>
-        </is>
-      </c>
-      <c r="D102" s="342" t="inlineStr">
-        <is>
-          <t>PPT «Plan vs Actualizado 10 años», jun-2026</t>
-        </is>
-      </c>
-      <c r="E102" s="350">
-        <v>2843528</v>
-      </c>
-      <c r="F102" s="342" t="inlineStr">
-        <is>
-          <t>PPT jun-2026. No está en ningún Excel (plan de negocio original, PDF ene-2026).</t>
-        </is>
-      </c>
-      <c r="G102" s="342"/>
-      <c r="H102" s="342"/>
-      <c r="I102" s="342"/>
-      <c r="J102" s="342"/>
-      <c r="K102" s="342"/>
-      <c r="L102" s="342"/>
-      <c r="M102" s="342"/>
-      <c r="N102" s="342"/>
-      <c r="O102" s="342"/>
+      <c r="G102" s="341"/>
+      <c r="H102" s="341"/>
+      <c r="I102" s="341"/>
+      <c r="J102" s="341"/>
+      <c r="K102" s="341"/>
+      <c r="L102" s="341"/>
+      <c r="M102" s="341"/>
+      <c r="N102" s="341"/>
+      <c r="O102" s="341"/>
     </row>
     <row r="103" ht="17.2" customHeight="1">
       <c r="B103" s="344">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C103" s="343" t="inlineStr">
         <is>
-          <t>TIR con financiamiento — plan</t>
+          <t>VAN con financiamiento — plan</t>
         </is>
       </c>
       <c r="D103" s="342" t="inlineStr">
@@ -47436,12 +47444,12 @@
           <t>PPT «Plan vs Actualizado 10 años», jun-2026</t>
         </is>
       </c>
-      <c r="E103" s="353">
-        <v>0.1519</v>
+      <c r="E103" s="350">
+        <v>2843528</v>
       </c>
       <c r="F103" s="342" t="inlineStr">
         <is>
-          <t>Idem.</t>
+          <t>PPT jun-2026. No está en ningún Excel (plan de negocio original, PDF ene-2026).</t>
         </is>
       </c>
       <c r="G103" s="342"/>
@@ -47456,11 +47464,11 @@
     </row>
     <row r="104" ht="17.2" customHeight="1">
       <c r="B104" s="344">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C104" s="343" t="inlineStr">
         <is>
-          <t>WACC — plan</t>
+          <t>TIR con financiamiento — plan</t>
         </is>
       </c>
       <c r="D104" s="342" t="inlineStr">
@@ -47469,11 +47477,11 @@
         </is>
       </c>
       <c r="E104" s="353">
-        <v>0.0987</v>
+        <v>0.1519</v>
       </c>
       <c r="F104" s="342" t="inlineStr">
         <is>
-          <t>Igual al actual (VAN-TIR!C22).</t>
+          <t>Idem.</t>
         </is>
       </c>
       <c r="G104" s="342"/>
@@ -47488,11 +47496,11 @@
     </row>
     <row r="105" ht="17.2" customHeight="1">
       <c r="B105" s="344">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C105" s="343" t="inlineStr">
         <is>
-          <t>Payback inversión propia — plan (años)</t>
+          <t>WACC — plan</t>
         </is>
       </c>
       <c r="D105" s="342" t="inlineStr">
@@ -47500,12 +47508,12 @@
           <t>PPT «Plan vs Actualizado 10 años», jun-2026</t>
         </is>
       </c>
-      <c r="E105" s="352">
-        <v>3</v>
+      <c r="E105" s="353">
+        <v>0.0987</v>
       </c>
       <c r="F105" s="342" t="inlineStr">
         <is>
-          <t>PPT jun-2026. Sin cálculo de respaldo en el libro.</t>
+          <t>Igual al actual (VAN-TIR!C22).</t>
         </is>
       </c>
       <c r="G105" s="342"/>
@@ -47518,13 +47526,13 @@
       <c r="N105" s="342"/>
       <c r="O105" s="342"/>
     </row>
-    <row r="106" ht="30.4" customHeight="1">
+    <row r="106" ht="17.2" customHeight="1">
       <c r="B106" s="344">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C106" s="343" t="inlineStr">
         <is>
-          <t>Producción acumulada — plan (rótulo PPT, Tn)</t>
+          <t>Payback inversión propia — plan (años)</t>
         </is>
       </c>
       <c r="D106" s="342" t="inlineStr">
@@ -47533,11 +47541,11 @@
         </is>
       </c>
       <c r="E106" s="352">
-        <v>150000</v>
+        <v>3</v>
       </c>
       <c r="F106" s="342" t="inlineStr">
         <is>
-          <t>La serie plan del gráfico suma 149.875 Tn (sección 3).</t>
+          <t>PPT jun-2026. Sin cálculo de respaldo en el libro.</t>
         </is>
       </c>
       <c r="G106" s="342"/>
@@ -47552,11 +47560,11 @@
     </row>
     <row r="107" ht="30.4" customHeight="1">
       <c r="B107" s="344">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C107" s="343" t="inlineStr">
         <is>
-          <t>Ingresos acumulados — plan (rótulo PPT, USD)</t>
+          <t>Producción acumulada — plan (rótulo PPT, Tn)</t>
         </is>
       </c>
       <c r="D107" s="342" t="inlineStr">
@@ -47565,11 +47573,11 @@
         </is>
       </c>
       <c r="E107" s="352">
-        <v>180000000</v>
+        <v>150000</v>
       </c>
       <c r="F107" s="342" t="inlineStr">
         <is>
-          <t>La serie plan del gráfico suma 179.220.739.</t>
+          <t>Base del indicador 13, con el mismo criterio que el PPT de junio. La serie plan del gráfico suma 149.875 Tn (sección 3).</t>
         </is>
       </c>
       <c r="G107" s="342"/>
@@ -47582,13 +47590,13 @@
       <c r="N107" s="342"/>
       <c r="O107" s="342"/>
     </row>
-    <row r="108" ht="17.2" customHeight="1">
+    <row r="108" ht="30.4" customHeight="1">
       <c r="B108" s="344">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C108" s="343" t="inlineStr">
         <is>
-          <t>EBITDA acumulado — plan (rótulo PPT, USD)</t>
+          <t>Ingresos acumulados — plan (rótulo PPT, USD)</t>
         </is>
       </c>
       <c r="D108" s="342" t="inlineStr">
@@ -47597,11 +47605,11 @@
         </is>
       </c>
       <c r="E108" s="352">
-        <v>21100000</v>
+        <v>180000000</v>
       </c>
       <c r="F108" s="342" t="inlineStr">
         <is>
-          <t>La serie plan del gráfico suma 21.620.331. Elegir una base y documentarla.</t>
+          <t>Base del indicador 15. La serie plan del gráfico suma 179.220.739.</t>
         </is>
       </c>
       <c r="G108" s="342"/>
@@ -47614,13 +47622,13 @@
       <c r="N108" s="342"/>
       <c r="O108" s="342"/>
     </row>
-    <row r="109" ht="17.2" customHeight="1">
+    <row r="109" ht="30.4" customHeight="1">
       <c r="B109" s="344">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C109" s="343" t="inlineStr">
         <is>
-          <t>Utilidad neta acumulada — plan (USD)</t>
+          <t>EBITDA acumulado — plan (rótulo PPT, USD)</t>
         </is>
       </c>
       <c r="D109" s="342" t="inlineStr">
@@ -47629,11 +47637,11 @@
         </is>
       </c>
       <c r="E109" s="352">
-        <v>17800000</v>
+        <v>21100000</v>
       </c>
       <c r="F109" s="342" t="inlineStr">
         <is>
-          <t>Sin serie anual del plan.</t>
+          <t>Base del indicador 17. La serie plan del gráfico suma 21.620.331: si la Gerencia adopta la serie como plan oficial, cambiar este valor y el rótulo de las diap. 3, 7 y 13.</t>
         </is>
       </c>
       <c r="G109" s="342"/>
@@ -47648,11 +47656,11 @@
     </row>
     <row r="110" ht="17.2" customHeight="1">
       <c r="B110" s="344">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C110" s="343" t="inlineStr">
         <is>
-          <t>Materia prima acumulada — plan (USD)</t>
+          <t>Utilidad neta acumulada — plan (USD)</t>
         </is>
       </c>
       <c r="D110" s="342" t="inlineStr">
@@ -47661,11 +47669,11 @@
         </is>
       </c>
       <c r="E110" s="352">
-        <v>156000000</v>
+        <v>17800000</v>
       </c>
       <c r="F110" s="342" t="inlineStr">
         <is>
-          <t>Inconsistente: supera el costo de producción total del plan (155,2M).</t>
+          <t>Base del indicador 19. Sin serie anual del plan.</t>
         </is>
       </c>
       <c r="G110" s="342"/>
@@ -47678,13 +47686,13 @@
       <c r="N110" s="342"/>
       <c r="O110" s="342"/>
     </row>
-    <row r="111" ht="30.4" customHeight="1">
+    <row r="111" ht="17.2" customHeight="1">
       <c r="B111" s="344">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C111" s="343" t="inlineStr">
         <is>
-          <t>Utilidad neta plan año 1 / año 2 / año 10 (USD)</t>
+          <t>Materia prima acumulada — plan (USD)</t>
         </is>
       </c>
       <c r="D111" s="342" t="inlineStr">
@@ -47693,11 +47701,11 @@
         </is>
       </c>
       <c r="E111" s="352">
-        <v>253000</v>
+        <v>156000000</v>
       </c>
       <c r="F111" s="342" t="inlineStr">
         <is>
-          <t>PPT: 253K / 1.204K / 2.152K. El libro tiene 360.858 (Ej_Resultados!P20) y 1.243.444 (AE20) para los años 1 y 2.</t>
+          <t>Inconsistente: supera el costo de producción total del plan (155,2M).</t>
         </is>
       </c>
       <c r="G111" s="342"/>
@@ -47712,11 +47720,11 @@
     </row>
     <row r="112" ht="30.4" customHeight="1">
       <c r="B112" s="344">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C112" s="343" t="inlineStr">
         <is>
-          <t>Capital de trabajo neto plan año 1 / 2 / 10 (USD)</t>
+          <t>Utilidad neta plan año 1 / año 2 / año 10 (USD)</t>
         </is>
       </c>
       <c r="D112" s="342" t="inlineStr">
@@ -47725,11 +47733,11 @@
         </is>
       </c>
       <c r="E112" s="352">
-        <v>4040000</v>
+        <v>253000</v>
       </c>
       <c r="F112" s="342" t="inlineStr">
         <is>
-          <t>PPT: 4,04M / 4,75M / 8,82M. En el libro solo Inversión!C18 = 4.024.908 (capital operativo inicial).</t>
+          <t>PPT: 253K / 1.204K / 2.152K. El libro tiene 360.858 (Ej_Resultados!P20) y 1.243.444 (AE20) para los años 1 y 2.</t>
         </is>
       </c>
       <c r="G112" s="342"/>
@@ -47742,13 +47750,13 @@
       <c r="N112" s="342"/>
       <c r="O112" s="342"/>
     </row>
-    <row r="113" ht="17.2" customHeight="1">
+    <row r="113" ht="30.4" customHeight="1">
       <c r="B113" s="344">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C113" s="343" t="inlineStr">
         <is>
-          <t>EBITDA plan año 1 / año 2 (USD)</t>
+          <t>Capital de trabajo neto plan año 1 / 2 / 10 (USD)</t>
         </is>
       </c>
       <c r="D113" s="342" t="inlineStr">
@@ -47757,11 +47765,11 @@
         </is>
       </c>
       <c r="E113" s="352">
-        <v>732980</v>
+        <v>4040000</v>
       </c>
       <c r="F113" s="342" t="inlineStr">
         <is>
-          <t>PPT: 732.980 / 1.734.077. El libro tiene 841.163 (Ej_Resultados!P13) y 1.868.908 (AE13): definir la fuente oficial del plan.</t>
+          <t>PPT: 4,04M / 4,75M / 8,82M. En el libro solo Inversión!C18 = 4.024.908 (capital operativo inicial).</t>
         </is>
       </c>
       <c r="G113" s="342"/>
@@ -47774,28 +47782,60 @@
       <c r="N113" s="342"/>
       <c r="O113" s="342"/>
     </row>
-    <row r="115" ht="30.4" customHeight="1">
-      <c r="B115" s="349" t="inlineStr">
+    <row r="114" ht="17.2" customHeight="1">
+      <c r="B114" s="344">
+        <v>12</v>
+      </c>
+      <c r="C114" s="343" t="inlineStr">
+        <is>
+          <t>EBITDA plan año 1 / año 2 (USD)</t>
+        </is>
+      </c>
+      <c r="D114" s="342" t="inlineStr">
+        <is>
+          <t>PPT «Plan vs Actualizado 10 años», jun-2026</t>
+        </is>
+      </c>
+      <c r="E114" s="352">
+        <v>732980</v>
+      </c>
+      <c r="F114" s="342" t="inlineStr">
+        <is>
+          <t>PPT: 732.980 / 1.734.077. El libro tiene 841.163 (Ej_Resultados!P13) y 1.868.908 (AE13): definir la fuente oficial del plan.</t>
+        </is>
+      </c>
+      <c r="G114" s="342"/>
+      <c r="H114" s="342"/>
+      <c r="I114" s="342"/>
+      <c r="J114" s="342"/>
+      <c r="K114" s="342"/>
+      <c r="L114" s="342"/>
+      <c r="M114" s="342"/>
+      <c r="N114" s="342"/>
+      <c r="O114" s="342"/>
+    </row>
+    <row r="116" ht="30.4" customHeight="1">
+      <c r="B116" s="349" t="inlineStr">
         <is>
           <t>Las series «Plan original» de la sección 3 y los valores de esta sección se copiaron de los gráficos y tablas del PPT de junio 2026. Solo los años 1 y 2 de producción e ingresos coinciden con el libro (Ej_Producción!P18/AE18 y Ej_Ingresos!P34/AE34). Confirmar contra el plan de negocio original (PDF de enero 2026) y no modificarlos al actualizar la prospección.</t>
         </is>
       </c>
-      <c r="C115" s="349"/>
-      <c r="D115" s="349"/>
-      <c r="E115" s="349"/>
-      <c r="F115" s="349"/>
-      <c r="G115" s="349"/>
-      <c r="H115" s="349"/>
-      <c r="I115" s="349"/>
-      <c r="J115" s="349"/>
-      <c r="K115" s="349"/>
-      <c r="L115" s="349"/>
-      <c r="M115" s="349"/>
-      <c r="N115" s="349"/>
-      <c r="O115" s="349"/>
+      <c r="C116" s="349"/>
+      <c r="D116" s="349"/>
+      <c r="E116" s="349"/>
+      <c r="F116" s="349"/>
+      <c r="G116" s="349"/>
+      <c r="H116" s="349"/>
+      <c r="I116" s="349"/>
+      <c r="J116" s="349"/>
+      <c r="K116" s="349"/>
+      <c r="L116" s="349"/>
+      <c r="M116" s="349"/>
+      <c r="N116" s="349"/>
+      <c r="O116" s="349"/>
     </row>
   </sheetData>
-  <mergeCells count="88">
+  <mergeCells count="89">
     <mergeCell ref="B2:O2"/>
     <mergeCell ref="B3:O3"/>
     <mergeCell ref="B5:O5"/>
@@ -47825,9 +47865,9 @@
     <mergeCell ref="H29:O29"/>
     <mergeCell ref="H30:O30"/>
     <mergeCell ref="H31:O31"/>
-    <mergeCell ref="E33:O33"/>
-    <mergeCell ref="B35:O35"/>
-    <mergeCell ref="H36:O36"/>
+    <mergeCell ref="H32:O32"/>
+    <mergeCell ref="E34:O34"/>
+    <mergeCell ref="B36:O36"/>
     <mergeCell ref="H37:O37"/>
     <mergeCell ref="H38:O38"/>
     <mergeCell ref="H39:O39"/>
@@ -47868,9 +47908,9 @@
     <mergeCell ref="H74:O74"/>
     <mergeCell ref="H75:O75"/>
     <mergeCell ref="H76:O76"/>
-    <mergeCell ref="B78:O78"/>
-    <mergeCell ref="B100:O100"/>
-    <mergeCell ref="F101:O101"/>
+    <mergeCell ref="H77:O77"/>
+    <mergeCell ref="B79:O79"/>
+    <mergeCell ref="B101:O101"/>
     <mergeCell ref="F102:O102"/>
     <mergeCell ref="F103:O103"/>
     <mergeCell ref="F104:O104"/>
@@ -47883,14 +47923,15 @@
     <mergeCell ref="F111:O111"/>
     <mergeCell ref="F112:O112"/>
     <mergeCell ref="F113:O113"/>
-    <mergeCell ref="B115:O115"/>
+    <mergeCell ref="F114:O114"/>
+    <mergeCell ref="B116:O116"/>
   </mergeCells>
-  <conditionalFormatting sqref="G7:G31">
+  <conditionalFormatting sqref="G7:G32">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"REVISAR"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G7:G31">
+  <conditionalFormatting sqref="G7:G32">
     <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
@@ -47906,7 +47947,7 @@
     <tabColor rgb="FF1F4E79"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F99"/>
+  <dimension ref="A1:F100"/>
   <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -47950,7 +47991,7 @@
       <c r="E5" s="364"/>
       <c r="F5" s="364"/>
     </row>
-    <row r="6" ht="30.4" customHeight="1">
+    <row r="6" ht="43.6" customHeight="1">
       <c r="B6" s="369" t="inlineStr">
         <is>
           <t>•</t>
@@ -47958,7 +47999,7 @@
       </c>
       <c r="C6" s="367" t="inlineStr">
         <is>
-          <t>Seguir las fases en orden: A Preparar → B Correcciones únicas → C Ventas → D Costos → E Caja y préstamos CP → F Resultados y controles → G PowerPoint. Al terminar cada fase presionar F9 y revisar la hoja «CONTROLES Y PPT»: todos los controles deben quedar en OK.</t>
+          <t>Seguir las fases en orden: A Preparar → B Correcciones únicas → C Ventas → D Costos → E Caja y préstamos CP → F Resultados y controles → G PowerPoint. Al terminar cada fase presionar F9 y revisar en «CONTROLES Y PPT» los controles que indica cada paso (columna «Control / resultado esperado»). Los controles 13, 14 y 23 (caja, préstamos CP y dividendos) recién deben quedar en OK al terminar la fase E; en el paso F1, todos.</t>
         </is>
       </c>
       <c r="D6" s="367"/>
@@ -48010,7 +48051,7 @@
       <c r="E9" s="367"/>
       <c r="F9" s="367"/>
     </row>
-    <row r="10" ht="30.4" customHeight="1">
+    <row r="10" ht="43.6" customHeight="1">
       <c r="B10" s="369" t="inlineStr">
         <is>
           <t>•</t>
@@ -48018,7 +48059,7 @@
       </c>
       <c r="C10" s="367" t="inlineStr">
         <is>
-          <t>Escribir solo en las celdas indicadas. No escribir en columnas de total (O y AD de las hojas Ej_; O, AB, AO, BB, BO, CB, CO, DB, DO, EB y EF de Ej_Flujo) ni en el plan original (columnas P y AE de las hojas Ej_; columna E de Supuestos).</t>
+          <t>Escribir solo en las celdas indicadas. No escribir en columnas de total o promedio (O y AD de las hojas Ej_; O, AB, AO, BB, BO, CB, CO, DB, DO, EB y EF de Ej_Flujo), salvo las celdas que un paso indica expresamente: Ej_Producción!O31:O32 y O46:O47 (B4), Ej_Costos!O9:O19 y AD9:AD19 (B5), Ej_Costos!O1 (D2) y Ej_Flujo!O37 y O40 (E2). Tampoco en el plan original (columnas P y AE de las hojas Ej_; columna E de Supuestos).</t>
         </is>
       </c>
       <c r="D10" s="367"/>
@@ -48155,7 +48196,7 @@
       <c r="E19" s="367"/>
       <c r="F19" s="367"/>
     </row>
-    <row r="20" ht="30.4" customHeight="1">
+    <row r="20" ht="56.8" customHeight="1">
       <c r="B20" s="369">
         <v>6</v>
       </c>
@@ -48166,7 +48207,7 @@
       </c>
       <c r="D20" s="367" t="inlineStr">
         <is>
-          <t>Insumos, packaging, mantenimiento y movimiento de carga escalan con el volumen. Mano de obra y gastos fijos no: la MO crece 3% anual desde el año 3 (cargas 43,09%; en los años 1-2 el factor 1,42 está incluido).</t>
+          <t>Insumos, packaging, mantenimiento y movimiento de carga: en 2026, tarifa del plan por Tn × Tn del mes (el mantenimiento 2026 está tipeado); en 2027, plan × (2 − MP plan / MP proyectada), repartido por las Tn de cada mes. Años 3-10: insumos (Supuestos!B61 × Tn producidas), packaging (B62 × MP) y seguro caución (20% × 1,8% × MP) siguen al volumen; mantenimiento, movimiento de carga y energía crecen 10% anual fijo (Costos filas 11, 15 y 16) y no cambian con la prospección. Mano de obra y gastos fijos no siguen al volumen: la MO crece 3% anual desde el año 3 (cargas 43,09%; en los años 1-2 el factor 1,42 está incluido).</t>
         </is>
       </c>
       <c r="E20" s="367"/>
@@ -48539,7 +48580,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="70.0" customHeight="1">
+    <row r="40" ht="83.2" customHeight="1">
       <c r="B40" s="370" t="inlineStr">
         <is>
           <t>B3</t>
@@ -48557,7 +48598,7 @@
       </c>
       <c r="E40" s="367" t="inlineStr">
         <is>
-          <t>Opción exacta: AC23:AN23 =('Servicio Deuda'!$F$23+'Servicio Deuda'!$F$24+'Servicio Deuda'!$F$25)/12; AP23:BA23 igual con la columna G; BC23:BN23 con la H; BP23:BY23 =('Servicio Deuda'!$I$23+'Servicio Deuda'!$I$24+'Servicio Deuda'!$I$25)/10. Agrega unos USD 477.000 de egresos en jul-oct 2031: después hay que revisar los préstamos CP (paso E3).</t>
+          <t>Opción exacta: AC23:AN23 =('Servicio Deuda'!$F$23+'Servicio Deuda'!$F$24+'Servicio Deuda'!$F$25)/12; AP23:BA23 igual con la columna G; BC23:BN23 con la H; BP23:BY23 =('Servicio Deuda'!$I$23+'Servicio Deuda'!$I$24+'Servicio Deuda'!$I$25)/10. Agrega unos USD 464.000 de egresos en jul-oct 2031 (4 × 116.058) y, neto de la baja de las cuotas 2028-2030, unos USD 387.000 (= valor actual del control 17). Después hay que revisar los préstamos CP (paso E3).</t>
         </is>
       </c>
       <c r="F40" s="367" t="inlineStr">
@@ -48566,7 +48607,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="30.4" customHeight="1">
+    <row r="41" ht="83.2" customHeight="1">
       <c r="B41" s="370" t="inlineStr">
         <is>
           <t>B4</t>
@@ -48574,17 +48615,17 @@
       </c>
       <c r="C41" s="368" t="inlineStr">
         <is>
-          <t>Vincular la producción de Accesorios del año 1</t>
+          <t>Crear los totales 2026 de Steel Frame y Accesorios y vincular Producción!D26</t>
         </is>
       </c>
       <c r="D41" s="371" t="inlineStr">
         <is>
-          <t>Producción!D26</t>
+          <t>Ej_Producción!O31</t>
         </is>
       </c>
       <c r="E41" s="367" t="inlineStr">
         <is>
-          <t>Escribir =+Ej_Producción!O32. Hoy es un 0 tipeado: si Accesorios produce en 2026, su volumen no entra al total ni al costo de materia prima.</t>
+          <t>En Ej_Producción escribir O31 =SUMA(C31:N31) y copiarla a O32; escribir O46 =SUMA(C46:N46) y copiarla a O47 (hoy las cuatro están vacías, a diferencia de O30 y O45). Luego Producción!D26 =+Ej_Producción!O32 (hoy es un 0 tipeado; D24, D25 y D27 ya apuntan a O31, O46 y O47). Sin esto, si Steel Frame o Accesorios producen o venden en 2026, su volumen no llega al modelo anual: Tn, precio promedio (Ej_Ingresos!O17:O18) y costo/Tn (Ej_Costos!O18:O19) quedan en 0.</t>
         </is>
       </c>
       <c r="F41" s="367" t="inlineStr">
@@ -48674,1081 +48715,1099 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="20" customHeight="1">
-      <c r="B46" s="364" t="inlineStr">
+    <row r="45" ht="188.8" customHeight="1">
+      <c r="B45" s="370" t="inlineStr">
+        <is>
+          <t>B8</t>
+        </is>
+      </c>
+      <c r="C45" s="368" t="inlineStr">
+        <is>
+          <t>Vincular los demás egresos operativos 2028-2035 (hoy son valores pegados)</t>
+        </is>
+      </c>
+      <c r="D45" s="371" t="inlineStr">
+        <is>
+          <t>Ej_Flujo!AC13</t>
+        </is>
+      </c>
+      <c r="E45" s="367" t="inlineStr">
+        <is>
+          <t>Mismo mapeo que 2027, con el costo anual de la hoja Costos / 12. Para 2028: AC13:AN13 =(Costos!$F$10+Costos!$F$13+Costos!$F$27)/12 (insumos, packaging y honorarios); AC19:AN19 =(Costos!$F$7+Costos!$F$8+Costos!$F$14+Costos!$F$20+Costos!$F$21)/12 (nómina y alimentación); AC21:AN21 =(Costos!$F$16+Costos!$F$22+Costos!$F$23)/12 (energía, servicios y alquileres); AC22:AN22 =(Costos!$F$9+Costos!$F$11+Costos!$F$12+Costos!$F$15+Costos!$F$24+Costos!$F$25+Costos!$F$26)/12 (otros). Repetir con la columna G de Costos en AP:BA, H en BC:BN, I en BP:CA, J en CC:CN, K en CP:DA, L en DC:DN y M en DP:EA, sin escribir en las columnas de total. Hoy esas filas repiten los montos de 2027 y no siguen al volumen: el cambio agrega ≈ USD 1,62M de egresos en 2028-2035. Atención: la fila 25 («Inversiones / CAPEX») repite desde feb-2027 los servicios de terceros de Steel Frame que ya están en la fila 22 (USD 3.750/mes; 371.250 en 2027-2035). Confirmarlo con quien armó el modelo; si es una duplicación, dejar en 0 las columnas de mes de la fila 25 desde feb-2027 y anotarlo en el registro.</t>
+        </is>
+      </c>
+      <c r="F45" s="367" t="inlineStr">
+        <is>
+          <t>Control 26 en OK. Con B2, B3 y B8 la caja empeora: es esperable y se resuelve en E3 y E5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="B47" s="364" t="inlineStr">
         <is>
           <t>FASE C — CARGAR LA PROSPECCIÓN DE VENTAS</t>
         </is>
       </c>
-      <c r="C46" s="364"/>
-      <c r="D46" s="364"/>
-      <c r="E46" s="364"/>
-      <c r="F46" s="364"/>
-    </row>
-    <row r="47" ht="18" customHeight="1">
-      <c r="B47" s="365" t="inlineStr">
+      <c r="C47" s="364"/>
+      <c r="D47" s="364"/>
+      <c r="E47" s="364"/>
+      <c r="F47" s="364"/>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="B48" s="365" t="inlineStr">
         <is>
           <t>Paso</t>
         </is>
       </c>
-      <c r="C47" s="365" t="inlineStr">
+      <c r="C48" s="365" t="inlineStr">
         <is>
           <t>Qué hacer</t>
         </is>
       </c>
-      <c r="D47" s="365" t="inlineStr">
+      <c r="D48" s="365" t="inlineStr">
         <is>
           <t>Dónde</t>
         </is>
       </c>
-      <c r="E47" s="365" t="inlineStr">
+      <c r="E48" s="365" t="inlineStr">
         <is>
           <t>Cómo / criterio</t>
         </is>
       </c>
-      <c r="F47" s="365" t="inlineStr">
+      <c r="F48" s="365" t="inlineStr">
         <is>
           <t>Control / resultado esperado</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="109.6" customHeight="1">
-      <c r="B48" s="370" t="inlineStr">
+    <row r="49" ht="109.6" customHeight="1">
+      <c r="B49" s="370" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="C48" s="368" t="inlineStr">
+      <c r="C49" s="368" t="inlineStr">
         <is>
           <t>Actualizar los meses reales hasta el corte</t>
         </is>
       </c>
-      <c r="D48" s="371" t="inlineStr">
+      <c r="D49" s="371" t="inlineStr">
         <is>
           <t>Ej_Producción!H22</t>
         </is>
       </c>
-      <c r="E48" s="367" t="inlineStr">
+      <c r="E49" s="367" t="inlineStr">
         <is>
           <t>Rangos: Ej_Producción!H22:K32 (producción) y H37:K47 (ventas); Ej_Ingresos!G8:K18 (precio). Desde el primer mes no real hasta el corte (hoy: volumen desde junio, columna H; precio desde mayo, columna G). Producción en Tn producidas y ventas en Tn facturadas, por producto y mes. Precio = facturación del mes en USD sin IVA ÷ Tn vendidas del mismo producto (si se facturó en Gs, convertir con el TC del mes). Mes sin venta: Tn = 0. Pasar los meses reales a formato azul (Copiar formato desde C22 y C8) y actualizar los títulos B2 («…EJECUTADO A &lt;MES&gt;…») de Ej_Producción, Ej_Ingresos y Ej_Costos.</t>
         </is>
       </c>
-      <c r="F48" s="367" t="inlineStr">
+      <c r="F49" s="367" t="inlineStr">
         <is>
           <t>Controles 1 a 5 en OK; totales iguales a la facturación contable.</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="70.0" customHeight="1">
-      <c r="B49" s="370" t="inlineStr">
+    <row r="50" ht="96.4" customHeight="1">
+      <c r="B50" s="370" t="inlineStr">
         <is>
           <t>C2</t>
         </is>
       </c>
-      <c r="C49" s="368" t="inlineStr">
+      <c r="C50" s="368" t="inlineStr">
         <is>
           <t>Cargar la prospección del resto de 2026</t>
         </is>
       </c>
-      <c r="D49" s="371" t="inlineStr">
+      <c r="D50" s="371" t="inlineStr">
         <is>
           <t>Ej_Producción!L22</t>
         </is>
       </c>
-      <c r="E49" s="367" t="inlineStr">
-        <is>
-          <t>Rangos: Ej_Producción!L22:N32 y L37:N47; Ej_Ingresos!L8:N18. Meses posteriores al corte (con corte a setiembre: oct-dic, columnas L:N), en las celdas amarillas. Criterio: venta = producción × (1 − 1,5%), salvo un stock previsto y documentado; la venta acumulada no puede superar a la producción acumulada. Si hay Tn vendidas, el precio no puede quedar vacío.</t>
-        </is>
-      </c>
-      <c r="F49" s="367" t="inlineStr">
+      <c r="E50" s="367" t="inlineStr">
+        <is>
+          <t>Rangos: Ej_Producción!L22:N32 y L37:N47; Ej_Ingresos!L8:N18. Meses posteriores al corte (con corte a setiembre: oct-dic, columnas L:N), en las celdas amarillas. Criterio del modelo: Tn vendidas tipeadas según la prospección comercial (hoy sin merma en los años 1 y 2; la merma de 1,5% se aplica desde el año 3). Si se decide aplicar la merma también en 2026, anotarlo en el registro, igual que en C3 (b). La venta acumulada no puede superar a la producción acumulada más el stock inicial. Si hay Tn vendidas, el precio no puede quedar vacío.</t>
+        </is>
+      </c>
+      <c r="F50" s="367" t="inlineStr">
         <is>
           <t>Controles 5 y 7 en OK.</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="83.2" customHeight="1">
-      <c r="B50" s="370" t="inlineStr">
+    <row r="51" ht="83.2" customHeight="1">
+      <c r="B51" s="370" t="inlineStr">
         <is>
           <t>C3</t>
         </is>
       </c>
-      <c r="C50" s="368" t="inlineStr">
+      <c r="C51" s="368" t="inlineStr">
         <is>
           <t>Cargar 2027 mes a mes</t>
         </is>
       </c>
-      <c r="D50" s="371" t="inlineStr">
+      <c r="D51" s="371" t="inlineStr">
         <is>
           <t>Ej_Producción!R22</t>
         </is>
       </c>
-      <c r="E50" s="367" t="inlineStr">
+      <c r="E51" s="367" t="inlineStr">
         <is>
           <t>Rangos: Ej_Producción!R22:AC32 y R37:AC47; Ej_Ingresos!R8:AC18. Si la prospección trae un total anual por producto, repartirlo en 12 meses según la rampa comercial (o /12). El total (columna AD) y el precio promedio ponderado (Ej_Ingresos!AD8:AD18) son la base de los años 3-10. Decidir y anotar en el registro: (a) si el precio 2027 lleva +5% (el plan sí; la proyección actual no); (b) si la venta lleva la merma de 1,5% (hoy venta = producción). No tocar AD, AE ni AF.</t>
         </is>
       </c>
-      <c r="F50" s="367" t="inlineStr">
+      <c r="F51" s="367" t="inlineStr">
         <is>
           <t>Controles 2 a 5 en OK.</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="56.8" customHeight="1">
-      <c r="B51" s="370" t="inlineStr">
+    <row r="52" ht="56.8" customHeight="1">
+      <c r="B52" s="370" t="inlineStr">
         <is>
           <t>C4</t>
         </is>
       </c>
-      <c r="C51" s="368" t="inlineStr">
+      <c r="C52" s="368" t="inlineStr">
         <is>
           <t>Años 2028-2035, si la prospección viene como tasas</t>
         </is>
       </c>
-      <c r="D51" s="371" t="inlineStr">
+      <c r="D52" s="371" t="inlineStr">
         <is>
           <t>Supuestos!B11</t>
         </is>
       </c>
-      <c r="E51" s="367" t="inlineStr">
+      <c r="E52" s="367" t="inlineStr">
         <is>
           <t>Escribir la tasa como fracción (5% = 0,05): B11 crecimiento anual de la producción; B8 merma producción-venta; B14 aumento de precio del año 3; B15 aumento de precio de los años 4-10. Son iguales para los 11 productos. No modificar la columna E (ORIGINALES).</t>
         </is>
       </c>
-      <c r="F51" s="367" t="inlineStr">
+      <c r="F52" s="367" t="inlineStr">
         <is>
           <t>Producción!F6/E6 − 1 = B11 en cada producto.</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="83.2" customHeight="1">
-      <c r="B52" s="370" t="inlineStr">
+    <row r="53" ht="83.2" customHeight="1">
+      <c r="B53" s="370" t="inlineStr">
         <is>
           <t>C5</t>
         </is>
       </c>
-      <c r="C52" s="368" t="inlineStr">
+      <c r="C53" s="368" t="inlineStr">
         <is>
           <t>Años 2028-2035, si la prospección trae Tn por producto y año</t>
         </is>
       </c>
-      <c r="D52" s="371" t="inlineStr">
+      <c r="D53" s="371" t="inlineStr">
         <is>
           <t>Producción!F6</t>
         </is>
       </c>
-      <c r="E52" s="367" t="inlineStr">
+      <c r="E53" s="367" t="inlineStr">
         <is>
           <t>Crear una hoja «Prosp_Tn» con la misma grilla que Producción (rótulos en B:C, años en F:M). Cargar solo las Tn de PRODUCCIÓN que traiga la prospección y dejar vacío lo demás. En Producción!F6: =SI(ESNUMERO(Prosp_Tn!F6);Prosp_Tn!F6;REDONDEAR(E6*(1+Supuestos!$B$11);0)); copiar a G6:M6 y pegar solo fórmulas en las filas pares 8 a 26. Las filas impares (venta) no se tocan: siguen aplicando la merma. Si el dato viene en Tn vendidas, cargar =REDONDEAR(venta/(1-Supuestos!$B$8);0).</t>
         </is>
       </c>
-      <c r="F52" s="367" t="inlineStr">
+      <c r="F53" s="367" t="inlineStr">
         <is>
           <t>Las celdas con dato coinciden con Prosp_Tn; las vacías siguen la tasa B11.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="70.0" customHeight="1">
-      <c r="B53" s="370" t="inlineStr">
-        <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="C53" s="368" t="inlineStr">
-        <is>
-          <t>Precios por producto y año (opcional)</t>
-        </is>
-      </c>
-      <c r="D53" s="371" t="inlineStr">
-        <is>
-          <t>Ingresos!F6</t>
-        </is>
-      </c>
-      <c r="E53" s="367" t="inlineStr">
-        <is>
-          <t>Crear una hoja «Prosp_Precio» con la misma grilla que Ingresos. Ingresos!F6: =SI(ESNUMERO(Prosp_Precio!F6);Prosp_Precio!F6;E6*(1+Supuestos!$B$14)); Ingresos!G6: =SI(ESNUMERO(Prosp_Precio!G6);Prosp_Precio!G6;F6*(1+Supuestos!$B$15)), copiada a H6:M6. Repetir en las filas pares 8 a 26. No tocar las filas impares (ingreso = precio × venta) ni las filas 28-29.</t>
-        </is>
-      </c>
-      <c r="F53" s="367" t="inlineStr">
-        <is>
-          <t>Ingresos!F28:M28 cambia solo donde hay dato nuevo.</t>
         </is>
       </c>
     </row>
     <row r="54" ht="70.0" customHeight="1">
       <c r="B54" s="370" t="inlineStr">
         <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="C54" s="368" t="inlineStr">
+        <is>
+          <t>Precios por producto y año (opcional)</t>
+        </is>
+      </c>
+      <c r="D54" s="371" t="inlineStr">
+        <is>
+          <t>Ingresos!F6</t>
+        </is>
+      </c>
+      <c r="E54" s="367" t="inlineStr">
+        <is>
+          <t>Crear una hoja «Prosp_Precio» con la misma grilla que Ingresos. Ingresos!F6: =SI(ESNUMERO(Prosp_Precio!F6);Prosp_Precio!F6;E6*(1+Supuestos!$B$14)); Ingresos!G6: =SI(ESNUMERO(Prosp_Precio!G6);Prosp_Precio!G6;F6*(1+Supuestos!$B$15)), copiada a H6:M6. Repetir en las filas pares 8 a 26. No tocar las filas impares (ingreso = precio × venta) ni las filas 28-29.</t>
+        </is>
+      </c>
+      <c r="F54" s="367" t="inlineStr">
+        <is>
+          <t>Las celdas con dato coinciden con Prosp_Precio; los años vacíos siguen B14/B15 a partir del último precio cargado. Ingresos!F28:M28 cambia desde el primer año con dato nuevo en adelante.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="83.2" customHeight="1">
+      <c r="B55" s="370" t="inlineStr">
+        <is>
           <t>C7</t>
         </is>
       </c>
-      <c r="C54" s="368" t="inlineStr">
+      <c r="C55" s="368" t="inlineStr">
         <is>
           <t>Productos 10 y 11 en 2026, o productos que arrancan después de 2027</t>
         </is>
       </c>
-      <c r="D54" s="371" t="inlineStr">
+      <c r="D55" s="371" t="inlineStr">
         <is>
           <t>Ej_Producción!C31</t>
         </is>
       </c>
-      <c r="E54" s="367" t="inlineStr">
-        <is>
-          <t>Rangos: Ej_Producción!C31:N32 y C46:N47; Ej_Ingresos!C17:N18; Ej_Costos!C18:N19. Steel Frame y Accesorios Metálicos arrancan hoy en ene-2027. Si venden en 2026, cargar Tn, precio y costo de chapa en esas filas (requiere los pasos B4 y B5). Un producto con 2027 = 0 queda en 0 en los años 3-10: cargarlo con los pasos C5 y C6 y escribir su costo/Tn en su fila par de Materia Prima (columnas F:M).</t>
-        </is>
-      </c>
-      <c r="F54" s="367" t="inlineStr">
+      <c r="E55" s="367" t="inlineStr">
+        <is>
+          <t>Rangos: Ej_Producción!C31:N32 y C46:N47; Ej_Ingresos!C17:N18; Ej_Costos!C18:N19. Steel Frame y Accesorios Metálicos arrancan hoy en ene-2027. Si venden en 2026, primero aplicar B4 (crea los totales Ej_Producción!O31, O32, O46 y O47, hoy vacíos) y B5; después cargar Tn, precio y costo de chapa en esas filas. Un producto con 2027 = 0 queda en 0 en los años 3-10: cargarlo con los pasos C5 y C6 y escribir su costo/Tn en su fila par de Materia Prima (columnas F:M).</t>
+        </is>
+      </c>
+      <c r="F55" s="367" t="inlineStr">
         <is>
           <t>Controles 5, 6 y 9 en OK.</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="96.4" customHeight="1">
-      <c r="B55" s="370" t="inlineStr">
+    <row r="56" ht="96.4" customHeight="1">
+      <c r="B56" s="370" t="inlineStr">
         <is>
           <t>C8</t>
         </is>
       </c>
-      <c r="C55" s="368" t="inlineStr">
+      <c r="C56" s="368" t="inlineStr">
         <is>
           <t>Producto nuevo (12.°)</t>
         </is>
       </c>
-      <c r="D55" s="371" t="inlineStr">
+      <c r="D56" s="371" t="inlineStr">
         <is>
           <t>Producción!D28</t>
         </is>
       </c>
-      <c r="E55" s="367" t="inlineStr">
+      <c r="E56" s="367" t="inlineStr">
         <is>
           <t>Primero evaluar asimilarlo a la fila del producto más parecido en precio y costo (más simple y sin riesgo). Si se agrega: insertar filas dentro de cada bloque (Ej_Producción filas 17, 32 y 47; Ej_Ingresos 18 y 33; Ej_Costos 19 y 33; un par de filas antes de la 26 en Producción, Ingresos y Materia Prima), copiar las fórmulas de la fila vecina y sumar la fila nueva A MANO en Producción!D28:M28 y D29:M29, Ingresos!D28:M28 y Materia Prima!D28:M28: son sumas celda por celda, no SUMA de rango.</t>
         </is>
       </c>
-      <c r="F55" s="367" t="inlineStr">
+      <c r="F56" s="367" t="inlineStr">
         <is>
           <t>Controles 1 a 4 y 8 en OK.</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="20" customHeight="1">
-      <c r="B57" s="364" t="inlineStr">
+    <row r="58" ht="20" customHeight="1">
+      <c r="B58" s="364" t="inlineStr">
         <is>
           <t>FASE D — COSTOS QUE ACOMPAÑAN A LAS VENTAS</t>
         </is>
       </c>
-      <c r="C57" s="364"/>
-      <c r="D57" s="364"/>
-      <c r="E57" s="364"/>
-      <c r="F57" s="364"/>
-    </row>
-    <row r="58" ht="18" customHeight="1">
-      <c r="B58" s="365" t="inlineStr">
+      <c r="C58" s="364"/>
+      <c r="D58" s="364"/>
+      <c r="E58" s="364"/>
+      <c r="F58" s="364"/>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="B59" s="365" t="inlineStr">
         <is>
           <t>Paso</t>
         </is>
       </c>
-      <c r="C58" s="365" t="inlineStr">
+      <c r="C59" s="365" t="inlineStr">
         <is>
           <t>Qué hacer</t>
         </is>
       </c>
-      <c r="D58" s="365" t="inlineStr">
+      <c r="D59" s="365" t="inlineStr">
         <is>
           <t>Dónde</t>
         </is>
       </c>
-      <c r="E58" s="365" t="inlineStr">
+      <c r="E59" s="365" t="inlineStr">
         <is>
           <t>Cómo / criterio</t>
         </is>
       </c>
-      <c r="F58" s="365" t="inlineStr">
+      <c r="F59" s="365" t="inlineStr">
         <is>
           <t>Control / resultado esperado</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="30.4" customHeight="1">
-      <c r="B59" s="370" t="inlineStr">
+    <row r="60" ht="30.4" customHeight="1">
+      <c r="B60" s="370" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="C59" s="368" t="inlineStr">
+      <c r="C60" s="368" t="inlineStr">
         <is>
           <t>Confirmar que la producción está cargada</t>
         </is>
       </c>
-      <c r="D59" s="371" t="inlineStr">
+      <c r="D60" s="371" t="inlineStr">
         <is>
           <t>Ej_Producción!C22</t>
         </is>
       </c>
-      <c r="E59" s="367" t="inlineStr">
+      <c r="E60" s="367" t="inlineStr">
         <is>
           <t>El costo de chapa se calcula sobre Tn PRODUCIDAS, no vendidas: si solo se cargan ventas, el costo no cambia y el margen se infla.</t>
         </is>
       </c>
-      <c r="F59" s="367" t="inlineStr">
+      <c r="F60" s="367" t="inlineStr">
         <is>
           <t>Control 7 en OK (venta ≤ producción).</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="70.0" customHeight="1">
-      <c r="B60" s="370" t="inlineStr">
-        <is>
-          <t>D2</t>
-        </is>
-      </c>
-      <c r="C60" s="368" t="inlineStr">
-        <is>
-          <t>Tipo de cambio</t>
-        </is>
-      </c>
-      <c r="D60" s="371" t="inlineStr">
-        <is>
-          <t>Ej_Costos!O1</t>
-        </is>
-      </c>
-      <c r="E60" s="367" t="inlineStr">
-        <is>
-          <t>Ej_Costos!O1 (hoy 6.028,12, «TC cierre de mayo-2026») convierte los gastos reales cargados en Gs (fórmulas =MontoGs/USD). Cambiarlo solo con un nuevo cierre, y actualizar el rótulo P1: revalúa también los meses ya cerrados. Supuestos!B6 (6.145) es informativo: no recalcula nada. Los meses proyectados están en USD calculados a 6.145. No tocar Supuestos!E6 (7.800).</t>
-        </is>
-      </c>
-      <c r="F60" s="367" t="inlineStr">
-        <is>
-          <t>Un único TC de proyección, anotado en el registro.</t>
         </is>
       </c>
     </row>
     <row r="61" ht="70.0" customHeight="1">
       <c r="B61" s="370" t="inlineStr">
         <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="C61" s="368" t="inlineStr">
+        <is>
+          <t>Tipo de cambio</t>
+        </is>
+      </c>
+      <c r="D61" s="371" t="inlineStr">
+        <is>
+          <t>Ej_Costos!O1</t>
+        </is>
+      </c>
+      <c r="E61" s="367" t="inlineStr">
+        <is>
+          <t>Ej_Costos!O1 (hoy 6.028,12, «TC cierre de mayo-2026») convierte los gastos reales cargados en Gs (fórmulas =MontoGs/USD). Cambiarlo solo con un nuevo cierre, y actualizar el rótulo P1: revalúa también los meses ya cerrados. Supuestos!B6 (6.145) es informativo: no recalcula nada. Los meses proyectados están en USD calculados a 6.145. No tocar Supuestos!E6 (7.800).</t>
+        </is>
+      </c>
+      <c r="F61" s="367" t="inlineStr">
+        <is>
+          <t>Un único TC de proyección, anotado en el registro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="96.4" customHeight="1">
+      <c r="B62" s="370" t="inlineStr">
+        <is>
           <t>D3</t>
         </is>
       </c>
-      <c r="C61" s="368" t="inlineStr">
+      <c r="C62" s="368" t="inlineStr">
         <is>
           <t>Costo de chapa (USD/Tn) por producto y mes</t>
         </is>
       </c>
-      <c r="D61" s="371" t="inlineStr">
+      <c r="D62" s="371" t="inlineStr">
         <is>
           <t>Ej_Costos!G9</t>
         </is>
       </c>
-      <c r="E61" s="367" t="inlineStr">
-        <is>
-          <t>Rangos: G9:N19 (2026) y R9:AC19 (2027). USD/Tn sin IVA, una fila por producto (mismo orden que Ej_Producción 22-32). Criterio vigente para 2027: enero = dic-2026 y feb-dic = dic-2026 × 1,07, salvo una cotización nueva (documentarla). Todo mes con Tn producidas debe tener costo &gt; 0. No escribir en los promedios (O, AD) ni en el plan (P, AE). El promedio 2027 (AD9:AD19) es la base de los años 3-10.</t>
-        </is>
-      </c>
-      <c r="F61" s="367" t="inlineStr">
+      <c r="E62" s="367" t="inlineStr">
+        <is>
+          <t>Rangos: G9:N19 (2026) y R9:AC19 (2027). USD/Tn sin IVA, una fila por producto (mismo orden que Ej_Producción 22-32). Criterio vigente para 2027 (productos 2 a 9): enero = dic-2026 y feb-dic = dic-2026 × 1,07. Producto 1: todo 2027 = dic-2026 × 1,07. Productos 10 y 11: valor fijo todo el año (986,54 y 957,72), sin dato de 2026. Documentar toda cotización nueva. Todo mes con Tn producidas debe tener costo &gt; 0. No escribir en los promedios (O, AD), ya corregidos en B5, ni en el plan (P, AE). El promedio 2027 (AD9:AD19) es la base de los años 3-10.</t>
+        </is>
+      </c>
+      <c r="F62" s="367" t="inlineStr">
         <is>
           <t>Controles 6 y 8 en OK.</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="56.8" customHeight="1">
-      <c r="B62" s="370" t="inlineStr">
+    <row r="63" ht="56.8" customHeight="1">
+      <c r="B63" s="370" t="inlineStr">
         <is>
           <t>D4</t>
         </is>
       </c>
-      <c r="C62" s="368" t="inlineStr">
+      <c r="C63" s="368" t="inlineStr">
         <is>
           <t>Gastos reales de los meses cerrados</t>
         </is>
       </c>
-      <c r="D62" s="371" t="inlineStr">
+      <c r="D63" s="371" t="inlineStr">
         <is>
           <t>Ej_Costos!G34</t>
         </is>
       </c>
-      <c r="E62" s="367" t="inlineStr">
+      <c r="E63" s="367" t="inlineStr">
         <is>
           <t>Rango: G34:K54 (meses cerrados). Mismo criterio que ene-abr: los montos en Gs se cargan como =MontoGs/USD (p. ej. =29898626/USD), encima de la fórmula de proyección del mes. Los meses sin gasto, en 0. Las filas 35 y 48 quedan en 0 porque las cargas sociales ya están en las filas 34 y 47.</t>
         </is>
       </c>
-      <c r="F62" s="367" t="inlineStr">
+      <c r="F63" s="367" t="inlineStr">
         <is>
           <t>Ej_Costos!O65 cambia solo con lo cargado.</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="83.2" customHeight="1">
-      <c r="B63" s="370" t="inlineStr">
+    <row r="64" ht="109.6" customHeight="1">
+      <c r="B64" s="370" t="inlineStr">
         <is>
           <t>D5</t>
         </is>
       </c>
-      <c r="C63" s="368" t="inlineStr">
+      <c r="C64" s="368" t="inlineStr">
         <is>
           <t>Mano de obra según la dotación que requiere el nuevo volumen</t>
         </is>
       </c>
-      <c r="D63" s="371" t="inlineStr">
+      <c r="D64" s="371" t="inlineStr">
         <is>
           <t>Ej_Costos!R34</t>
         </is>
       </c>
-      <c r="E63" s="367" t="inlineStr">
-        <is>
-          <t>Rangos: G34:N34 y R34:AC34 (fábrica); G47:N47 y R47:AC47 (administración). USD/mes con cargas = salario Gs × 1,42 / TC × N.° de personas (auxiliar Ej_Costos!O88:P114). Reemplazar las constantes «+6702» de R34:T34 por el valor nuevo y actualizar las notas de ingreso de personal (filas 68-71). Desde 2028 la MO solo crece 3% (Supuestos!B21): si la dotación crece después, ajustarlo en Mano de Obra y documentarlo.</t>
-        </is>
-      </c>
-      <c r="F63" s="367" t="inlineStr">
+      <c r="E64" s="367" t="inlineStr">
+        <is>
+          <t>Rangos: G34:N34 y R34:AC34 (fábrica); G47:N47 y R47:AC47 (administración). USD/mes con cargas = salario Gs × 1,42 / TC × N.° de personas (auxiliar Ej_Costos!O88:P114). Recalcular todo R34:AC34: en R34:T34 cambiar la constante «+6702»; U34:AC34 son valores tipeados que repiten T34 (18.379,63 = 11.677,63 + 6.702): reemplazarlos también. Si cambia la administración, recalcular R47:AC47 (todo tipeado: R47:S47 = 7.304,97 y T47:AC47 = 8.228,97). Actualizar las notas de ingreso de personal (filas 68-71). Desde 2028 la MO solo crece 3% (Supuestos!B21): si la dotación crece después, ajustarlo en Mano de Obra y documentarlo.</t>
+        </is>
+      </c>
+      <c r="F64" s="367" t="inlineStr">
         <is>
           <t>MO año 2 → año 3 crece ≈ 3,8%.</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="56.8" customHeight="1">
-      <c r="B64" s="370" t="inlineStr">
+    <row r="65" ht="96.4" customHeight="1">
+      <c r="B65" s="370" t="inlineStr">
         <is>
           <t>D6</t>
         </is>
       </c>
-      <c r="C64" s="368" t="inlineStr">
+      <c r="C65" s="368" t="inlineStr">
         <is>
           <t>Insumos, packaging, mantenimiento y movimiento de carga (automáticos)</t>
         </is>
       </c>
-      <c r="D64" s="371" t="inlineStr">
+      <c r="D65" s="371" t="inlineStr">
         <is>
           <t>Ej_Costos!AJ37</t>
         </is>
       </c>
-      <c r="E64" s="367" t="inlineStr">
-        <is>
-          <t>No se cargan. En 2026: tarifa del plan por Tn × Tn del mes. En 2027: plan × (2 − MP plan / MP proyectada). Verificar que Ej_Costos!AM37/AE37 sea &gt; 0 y razonable frente a AD22/AE22; si la MP 2027 se aleja mucho del plan, revisar el criterio y documentarlo.</t>
-        </is>
-      </c>
-      <c r="F64" s="367" t="inlineStr">
+      <c r="E65" s="367" t="inlineStr">
+        <is>
+          <t>No se cargan. En 2026: tarifa del plan por Tn × Tn del mes (el mantenimiento 2026 está tipeado). En 2027: plan × (2 − MP plan / MP proyectada), repartido por las Tn de cada mes. Verificar que Ej_Costos!AM37/AE37 sea &gt; 0 y razonable frente a AD22/AE22; si la MP 2027 se aleja mucho del plan, revisar el criterio y documentarlo. En los años 3-10 solo insumos, packaging y seguro caución siguen al volumen; mantenimiento, movimiento de carga y energía crecen 10% anual fijo (Costos filas 11, 15 y 16): si el nuevo volumen exige más, ajustarlo y documentarlo.</t>
+        </is>
+      </c>
+      <c r="F65" s="367" t="inlineStr">
         <is>
           <t>Ningún costo negativo en Ej_Costos filas 37-42.</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="43.6" customHeight="1">
-      <c r="B65" s="370" t="inlineStr">
+    <row r="66" ht="43.6" customHeight="1">
+      <c r="B66" s="370" t="inlineStr">
         <is>
           <t>D7</t>
         </is>
       </c>
-      <c r="C65" s="368" t="inlineStr">
+      <c r="C66" s="368" t="inlineStr">
         <is>
           <t>Servicios de terceros de Steel Frame</t>
         </is>
       </c>
-      <c r="D65" s="371" t="inlineStr">
+      <c r="D66" s="371" t="inlineStr">
         <is>
           <t>Ej_Costos!R36</t>
         </is>
       </c>
-      <c r="E65" s="367" t="inlineStr">
+      <c r="E66" s="367" t="inlineStr">
         <is>
           <t>Si cambia el volumen de Steel Frame, tipear los meses 2027 en R36:AC36 (sin tocar AE36, que es plan) y poner Mano de Obra!D13 =Ej_Costos!AD36, que es la base de los años 3-10.</t>
         </is>
       </c>
-      <c r="F65" s="367" t="inlineStr">
+      <c r="F66" s="367" t="inlineStr">
         <is>
           <t>Mano de Obra!D13 = Ej_Costos!AD36.</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="56.8" customHeight="1">
-      <c r="B66" s="370" t="inlineStr">
+    <row r="67" ht="56.8" customHeight="1">
+      <c r="B67" s="370" t="inlineStr">
         <is>
           <t>D8</t>
         </is>
       </c>
-      <c r="C66" s="368" t="inlineStr">
+      <c r="C67" s="368" t="inlineStr">
         <is>
           <t>Parámetros de costos de los años 3-10</t>
         </is>
       </c>
-      <c r="D66" s="371" t="inlineStr">
+      <c r="D67" s="371" t="inlineStr">
         <is>
           <t>Supuestos!B18</t>
         </is>
       </c>
-      <c r="E66" s="367" t="inlineStr">
+      <c r="E67" s="367" t="inlineStr">
         <is>
           <t>Solo la columna B: B18 costo MP/Tn (+3%); B21 salarios (+3%); B22 cargas (43,09%); B61 insumos (5 USD/Tn); B62 packaging (0,95% de la MP); B64 alimentación; B56 seguros; B58 honorarios. No tienen ningún efecto: B6, B53, B54, B55, B57, B63, B65, B75, B86 y B87.</t>
         </is>
       </c>
-      <c r="F66" s="367" t="inlineStr">
+      <c r="F67" s="367" t="inlineStr">
         <is>
           <t>Costos!F17/E17 − 1 razonable (hoy 8,1%).</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="20" customHeight="1">
-      <c r="B68" s="364" t="inlineStr">
+    <row r="69" ht="20" customHeight="1">
+      <c r="B69" s="364" t="inlineStr">
         <is>
           <t>FASE E — CAPITAL DE TRABAJO, CAJA Y PRÉSTAMOS CP</t>
         </is>
       </c>
-      <c r="C68" s="364"/>
-      <c r="D68" s="364"/>
-      <c r="E68" s="364"/>
-      <c r="F68" s="364"/>
-    </row>
-    <row r="69" ht="18" customHeight="1">
-      <c r="B69" s="365" t="inlineStr">
+      <c r="C69" s="364"/>
+      <c r="D69" s="364"/>
+      <c r="E69" s="364"/>
+      <c r="F69" s="364"/>
+    </row>
+    <row r="70" ht="18" customHeight="1">
+      <c r="B70" s="365" t="inlineStr">
         <is>
           <t>Paso</t>
         </is>
       </c>
-      <c r="C69" s="365" t="inlineStr">
+      <c r="C70" s="365" t="inlineStr">
         <is>
           <t>Qué hacer</t>
         </is>
       </c>
-      <c r="D69" s="365" t="inlineStr">
+      <c r="D70" s="365" t="inlineStr">
         <is>
           <t>Dónde</t>
         </is>
       </c>
-      <c r="E69" s="365" t="inlineStr">
+      <c r="E70" s="365" t="inlineStr">
         <is>
           <t>Cómo / criterio</t>
         </is>
       </c>
-      <c r="F69" s="365" t="inlineStr">
+      <c r="F70" s="365" t="inlineStr">
         <is>
           <t>Control / resultado esperado</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="43.6" customHeight="1">
-      <c r="B70" s="370" t="inlineStr">
+    <row r="71" ht="43.6" customHeight="1">
+      <c r="B71" s="370" t="inlineStr">
         <is>
           <t>E1</t>
         </is>
       </c>
-      <c r="C70" s="368" t="inlineStr">
+      <c r="C71" s="368" t="inlineStr">
         <is>
           <t>Días de capital de trabajo</t>
         </is>
       </c>
-      <c r="D70" s="371" t="inlineStr">
+      <c r="D71" s="371" t="inlineStr">
         <is>
           <t>Supuestos!B77</t>
         </is>
       </c>
-      <c r="E70" s="367" t="inlineStr">
+      <c r="E71" s="367" t="inlineStr">
         <is>
           <t>Mantener 2 / 15 / 45 / 90 / 0 / 0 / 15 salvo un cambio de política. Si cambia B80 (cobro), también hay que mover el desfase de los cobros de Ej_Flujo fila 6 (hoy fijo en 3 meses) y corregir los rótulos de Capital Trabajo!B7:B15.</t>
         </is>
       </c>
-      <c r="F70" s="367" t="inlineStr">
+      <c r="F71" s="367" t="inlineStr">
         <is>
           <t>Control 18 en OK.</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="30.4" customHeight="1">
-      <c r="B71" s="370" t="inlineStr">
+    <row r="72" ht="30.4" customHeight="1">
+      <c r="B72" s="370" t="inlineStr">
         <is>
           <t>E2</t>
         </is>
       </c>
-      <c r="C71" s="368" t="inlineStr">
+      <c r="C72" s="368" t="inlineStr">
         <is>
           <t>Base de compra de chapas 2027</t>
         </is>
       </c>
-      <c r="D71" s="371" t="inlineStr">
+      <c r="D72" s="371" t="inlineStr">
         <is>
           <t>Ej_Flujo!O40</t>
         </is>
       </c>
-      <c r="E71" s="367" t="inlineStr">
+      <c r="E72" s="367" t="inlineStr">
         <is>
           <t>O40 = MP 2027 redondeada: =REDONDEAR(Costos!E6;-5) (hoy 14.100.000). O37 (órdenes hasta ene-2027) solo cambia si esas órdenes no se emitieron.</t>
         </is>
       </c>
-      <c r="F71" s="367" t="inlineStr">
+      <c r="F72" s="367" t="inlineStr">
         <is>
           <t>Ej_Flujo!O40 − Costos!E6 entre −100.000 y +100.000.</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="122.8" customHeight="1">
-      <c r="B72" s="370" t="inlineStr">
+    <row r="73" ht="188.8" customHeight="1">
+      <c r="B73" s="370" t="inlineStr">
         <is>
           <t>E3</t>
         </is>
       </c>
-      <c r="C72" s="368" t="inlineStr">
+      <c r="C73" s="368" t="inlineStr">
         <is>
           <t>Re-dimensionar los préstamos CP para chapas</t>
         </is>
       </c>
-      <c r="D72" s="371" t="inlineStr">
+      <c r="D73" s="371" t="inlineStr">
         <is>
           <t>Ej_Flujo!P8</t>
         </is>
       </c>
-      <c r="E72" s="367" t="inlineStr">
-        <is>
-          <t>Filas 8, 16, 17 y 29 (solo columnas de mes). Con B1-B3 y la prospección cargados, recorrer el saldo mensual (fila 29) desde ago-2026. Para cada préstamo: (a) monto en la fila 8 del mes de desembolso (múltiplos de 100.000); (b) en la fila 16 del mes de devolución =+&lt;celda de la fila 8&gt; (ej. V16 =+P8); (c) en la fila 17 de esa columna =((8%/365)*DÍAS)*&lt;celda fila 16&gt;, con DÍAS = 30 × meses (ene→jul = 180); (d) si se mueve o elimina un desembolso, mover o borrar también su devolución y su interés. Meta: saldo ≥ 0 todos los meses, con un colchón de 100.000 a 400.000, y todo devuelto antes de dic-2035. Hoy ya hay déficit en ago-2032 (CJ29 = −245.726).</t>
-        </is>
-      </c>
-      <c r="F72" s="367" t="inlineStr">
+      <c r="E73" s="367" t="inlineStr">
+        <is>
+          <t>Filas 8, 16, 17 y 29 (solo columnas de mes). Con B1-B3 y la prospección cargados, recorrer el saldo mensual (fila 29) desde ago-2026. Para cada préstamo: (a) monto en la fila 8 del mes de desembolso (múltiplos de 100.000); (b) en la fila 16 del mes de devolución =+&lt;celda de la fila 8&gt; (ej. V16 =+P8); (c) en la fila 17 de esa columna =((8%/365)*DÍAS)*&lt;celda fila 16&gt;, con DÍAS = 30 × meses (ene→jul = 180); (d) si se mueve o elimina un desembolso, mover o borrar también su devolución y su interés; (e) un préstamo CP en 2026 se carga igual; si se devuelve dentro de 2026, sumar su interés en Ej_Costos (paso E4). L16 (2.779.626) y L17 (125.862) son la devolución a CIE S.A., no préstamos CP: no tocarlas. Meta: saldo ≥ 0 todos los meses, con un colchón de 100.000 a 400.000, y todo devuelto antes de dic-2035. Antes de la fase B el único déficit es ago-2032 (CJ29 = −245.726). Después de la fase B, con los datos actuales, hay faltantes de calce desde abr-2030 (máximo −736.000 en ago-2032 sin contar dividendos) y el saldo de dic-2035 queda en ≈ −2,22M después de los dividendos: ver E5.</t>
+        </is>
+      </c>
+      <c r="F73" s="367" t="inlineStr">
         <is>
           <t>Controles 13 y 14 en OK.</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="56.8" customHeight="1">
-      <c r="B73" s="370" t="inlineStr">
+    <row r="74" ht="83.2" customHeight="1">
+      <c r="B74" s="370" t="inlineStr">
         <is>
           <t>E4</t>
         </is>
       </c>
-      <c r="C73" s="368" t="inlineStr">
+      <c r="C74" s="368" t="inlineStr">
         <is>
           <t>Intereses CP de 2027 en Resultados</t>
         </is>
       </c>
-      <c r="D73" s="371" t="inlineStr">
+      <c r="D74" s="371" t="inlineStr">
         <is>
           <t>Ej_Costos!R62</t>
         </is>
       </c>
-      <c r="E73" s="367" t="inlineStr">
-        <is>
-          <t>Hoy solo X62, AA62 y AC62 suman Ej_Flujo!V17, Y17 y AA17. Si una devolución de 2027 cambió de mes: R62 =+Ej_Deuda!R7+Ej_Deuda!R13+Ej_Flujo!P17 y copiar hasta AC62 (columna de Ej_Costos = columna de Ej_Flujo + 2). Para 2028-2035 no hay que hacer nada: Costos!F34:M34 ya toman los totales de la fila 17.</t>
-        </is>
-      </c>
-      <c r="F73" s="367" t="inlineStr">
+      <c r="E74" s="367" t="inlineStr">
+        <is>
+          <t>Hoy solo X62, AA62 y AC62 suman Ej_Flujo!V17, Y17 y AA17. Si una devolución de 2027 cambió de mes: R62 =+Ej_Deuda!R7+Ej_Deuda!R13+Ej_Flujo!P17 y copiar hasta AC62 (columna de Ej_Costos = columna de Ej_Flujo + 2). Si un préstamo CP se devuelve dentro de 2026, sumar su interés en la misma columna de Ej_Costos (en 2026 coinciden; p. ej. M62 =+Ej_Deuda!M7+Ej_Deuda!M13+Ej_Flujo!M17), sin incluir L17. Para 2028-2035 no hay que hacer nada: Costos!F34:M34 ya toman los totales de la fila 17.</t>
+        </is>
+      </c>
+      <c r="F74" s="367" t="inlineStr">
         <is>
           <t>Controles 15 y 16 en OK.</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="56.8" customHeight="1">
-      <c r="B74" s="370" t="inlineStr">
+    <row r="75" ht="122.8" customHeight="1">
+      <c r="B75" s="370" t="inlineStr">
         <is>
           <t>E5</t>
         </is>
       </c>
-      <c r="C74" s="368" t="inlineStr">
+      <c r="C75" s="368" t="inlineStr">
         <is>
           <t>Iterar dividendos y caja</t>
         </is>
       </c>
-      <c r="D74" s="371" t="inlineStr">
+      <c r="D75" s="371" t="inlineStr">
         <is>
           <t>Resultados!H18</t>
         </is>
       </c>
-      <c r="E74" s="367" t="inlineStr">
-        <is>
-          <t>Las nuevas utilidades cambian los dividendos (calendario fijo desde 2031; montos tipeados 500.000 y 800.000) y estos cambian la caja de Ej_Flujo (fila 20). Si cambia la caja, volver a E3 hasta que el saldo mínimo se estabilice (2 o 3 vueltas). No cambiar la política de dividendos sin instrucción de la Dirección.</t>
-        </is>
-      </c>
-      <c r="F74" s="367" t="inlineStr">
+      <c r="E75" s="367" t="inlineStr">
+        <is>
+          <t>Las nuevas utilidades cambian los dividendos (Resultados fila 18; calendario fijo desde 2031, con montos tipeados de 500.000 y 800.000), que se pagan en diciembre en Ej_Flujo fila 20 (CA20, CN20, DA20, DN20 y EA20; esa fila no tiene totales anuales). Si cambia la caja, volver a E3 hasta que el saldo mínimo se estabilice (2 o 3 vueltas). Si con todos los CP devueltos el saldo de dic-2035 sigue negativo (hoy ≈ −2,22M después de la fase B, con ≈ USD 10M de dividendos en 2031-2035), el calendario de dividendos excede la caja disponible: presentar a la Gerencia las alternativas (diferir o reducir dividendos, mantener deuda CP al cierre o refinanciar a largo plazo). No cambiar la política sin instrucción de la Dirección.</t>
+        </is>
+      </c>
+      <c r="F75" s="367" t="inlineStr">
         <is>
           <t>Control 23 en OK.</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="20" customHeight="1">
-      <c r="B76" s="364" t="inlineStr">
+    <row r="77" ht="20" customHeight="1">
+      <c r="B77" s="364" t="inlineStr">
         <is>
           <t>FASE F — RESULTADOS Y CONTROLES</t>
         </is>
       </c>
-      <c r="C76" s="364"/>
-      <c r="D76" s="364"/>
-      <c r="E76" s="364"/>
-      <c r="F76" s="364"/>
-    </row>
-    <row r="77" ht="18" customHeight="1">
-      <c r="B77" s="365" t="inlineStr">
+      <c r="C77" s="364"/>
+      <c r="D77" s="364"/>
+      <c r="E77" s="364"/>
+      <c r="F77" s="364"/>
+    </row>
+    <row r="78" ht="18" customHeight="1">
+      <c r="B78" s="365" t="inlineStr">
         <is>
           <t>Paso</t>
         </is>
       </c>
-      <c r="C77" s="365" t="inlineStr">
+      <c r="C78" s="365" t="inlineStr">
         <is>
           <t>Qué hacer</t>
         </is>
       </c>
-      <c r="D77" s="365" t="inlineStr">
+      <c r="D78" s="365" t="inlineStr">
         <is>
           <t>Dónde</t>
         </is>
       </c>
-      <c r="E77" s="365" t="inlineStr">
+      <c r="E78" s="365" t="inlineStr">
         <is>
           <t>Cómo / criterio</t>
         </is>
       </c>
-      <c r="F77" s="365" t="inlineStr">
+      <c r="F78" s="365" t="inlineStr">
         <is>
           <t>Control / resultado esperado</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="43.6" customHeight="1">
-      <c r="B78" s="370" t="inlineStr">
+    <row r="79" ht="56.8" customHeight="1">
+      <c r="B79" s="370" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="C78" s="368" t="inlineStr">
+      <c r="C79" s="368" t="inlineStr">
         <is>
           <t>Recalcular y revisar los controles</t>
         </is>
       </c>
-      <c r="D78" s="371" t="inlineStr">
+      <c r="D79" s="371" t="inlineStr">
         <is>
           <t>CONTROLES Y PPT, sección 1</t>
         </is>
       </c>
-      <c r="E78" s="367" t="inlineStr">
-        <is>
-          <t>Presionar F9 (o Ctrl+Alt+F9). Todos los controles deben quedar en OK; la última columna indica qué paso revisar. Con el libro tal como llegó, varios controles salen en REVISAR: son los que corrige la fase B.</t>
-        </is>
-      </c>
-      <c r="F78" s="367" t="inlineStr">
-        <is>
-          <t>25 de 25 controles en OK.</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="70.0" customHeight="1">
-      <c r="B79" s="370" t="inlineStr">
+      <c r="E79" s="367" t="inlineStr">
+        <is>
+          <t>Presionar F9 (o Ctrl+Alt+F9). Todos los controles deben quedar en OK; la última columna indica qué paso revisar. Con el libro tal como llegó hay 8 controles en REVISAR: el 9, 11, 12, 17, 21, 22 y 26 se corrigen en la fase B; el 13 (déficit de caja) se corrige en E3 y E5, y empeora después de la fase B.</t>
+        </is>
+      </c>
+      <c r="F79" s="367" t="inlineStr">
+        <is>
+          <t>26 de 26 controles en OK.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="96.4" customHeight="1">
+      <c r="B80" s="370" t="inlineStr">
         <is>
           <t>F2</t>
         </is>
       </c>
-      <c r="C79" s="368" t="inlineStr">
+      <c r="C80" s="368" t="inlineStr">
         <is>
           <t>Leer resultados y valuación (sin editar)</t>
         </is>
       </c>
-      <c r="D79" s="371" t="inlineStr">
+      <c r="D80" s="371" t="inlineStr">
         <is>
           <t>VAN-TIR!C22</t>
         </is>
       </c>
-      <c r="E79" s="367" t="inlineStr">
-        <is>
-          <t>Confirmar que ingresos, EBITDA, gastos financieros y utilidad reflejan la prospección. El WACC debe seguir en 9,87% si no cambió el financiamiento. Para explicar el cambio del VAN, separar el efecto EBITDA (VAN-TIR fila 5) del efecto capital de trabajo (fila 9 y recupero en M6): cada USD 1M de ventas anuales adicionales inmoviliza unos USD 252.000 de capital de trabajo.</t>
-        </is>
-      </c>
-      <c r="F79" s="367" t="inlineStr">
+      <c r="E80" s="367" t="inlineStr">
+        <is>
+          <t>Confirmar que ingresos, EBITDA, gastos financieros y utilidad reflejan la prospección. El WACC debe seguir en 9,87% si no cambió el financiamiento. Para explicar el cambio del VAN, separar el efecto EBITDA (VAN-TIR fila 5) del efecto capital de trabajo (fila 9 y recupero en M6): cada USD 1M de ventas anuales adicionales inmoviliza ≈ USD 252.000 de capital de trabajo si viene de precio (caja 2 días + crédito 90 días) y ≈ USD 350.000 si viene de volumen (se suma el stock de MP de 45 días, con MP ≈ 81% de las ventas).</t>
+        </is>
+      </c>
+      <c r="F80" s="367" t="inlineStr">
         <is>
           <t>VAN y TIR se mueven en el sentido esperado frente a la foto del paso A4.</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="30.4" customHeight="1">
-      <c r="B80" s="370" t="inlineStr">
+    <row r="81" ht="30.4" customHeight="1">
+      <c r="B81" s="370" t="inlineStr">
         <is>
           <t>F3</t>
         </is>
       </c>
-      <c r="C80" s="368" t="inlineStr">
+      <c r="C81" s="368" t="inlineStr">
         <is>
           <t>Registrar la actualización</t>
         </is>
       </c>
-      <c r="D80" s="367" t="inlineStr">
+      <c r="D81" s="367" t="inlineStr">
         <is>
           <t>Registro al final de esta hoja</t>
         </is>
       </c>
-      <c r="E80" s="367" t="inlineStr">
+      <c r="E81" s="367" t="inlineStr">
         <is>
           <t>Fecha, versión, corte de reales, fuente de la prospección y criterios modificados (precio 2027, merma, TC, dotación, préstamos CP).</t>
         </is>
       </c>
-      <c r="F80" s="367" t="inlineStr">
+      <c r="F81" s="367" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="20" customHeight="1">
-      <c r="B82" s="364" t="inlineStr">
+    <row r="83" ht="20" customHeight="1">
+      <c r="B83" s="364" t="inlineStr">
         <is>
           <t>FASE G — ACTUALIZAR EL POWERPOINT «PLAN ORIGINAL VS PROYECCIÓN ACTUALIZADA A 10 AÑOS»</t>
         </is>
       </c>
-      <c r="C82" s="364"/>
-      <c r="D82" s="364"/>
-      <c r="E82" s="364"/>
-      <c r="F82" s="364"/>
-    </row>
-    <row r="83" ht="18" customHeight="1">
-      <c r="B83" s="365" t="inlineStr">
+      <c r="C83" s="364"/>
+      <c r="D83" s="364"/>
+      <c r="E83" s="364"/>
+      <c r="F83" s="364"/>
+    </row>
+    <row r="84" ht="18" customHeight="1">
+      <c r="B84" s="365" t="inlineStr">
         <is>
           <t>Paso</t>
         </is>
       </c>
-      <c r="C83" s="365" t="inlineStr">
+      <c r="C84" s="365" t="inlineStr">
         <is>
           <t>Qué hacer</t>
         </is>
       </c>
-      <c r="D83" s="365" t="inlineStr">
+      <c r="D84" s="365" t="inlineStr">
         <is>
           <t>Dónde</t>
         </is>
       </c>
-      <c r="E83" s="365" t="inlineStr">
+      <c r="E84" s="365" t="inlineStr">
         <is>
           <t>Cómo / criterio</t>
         </is>
       </c>
-      <c r="F83" s="365" t="inlineStr">
+      <c r="F84" s="365" t="inlineStr">
         <is>
           <t>Control / resultado esperado</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="56.8" customHeight="1">
-      <c r="B84" s="370" t="inlineStr">
+    <row r="85" ht="109.6" customHeight="1">
+      <c r="B85" s="370" t="inlineStr">
         <is>
           <t>G1</t>
         </is>
       </c>
-      <c r="C84" s="368" t="inlineStr">
+      <c r="C85" s="368" t="inlineStr">
         <is>
           <t>Series de los gráficos</t>
         </is>
       </c>
-      <c r="D84" s="371" t="inlineStr">
+      <c r="D85" s="371" t="inlineStr">
         <is>
           <t>CONTROLES Y PPT, sección 3</t>
         </is>
       </c>
-      <c r="E84" s="367" t="inlineStr">
-        <is>
-          <t>En cada gráfico: clic derecho &gt; Editar datos y pegar SOLO la fila «Actualizado» de la sección 3: diap. 4 producción, 5 ingresos, 6 costos de producción, 7 EBITDA, 8 préstamos CP, 10 ventas y punto de equilibrio. La serie «Plan original» no se toca (sección 4).</t>
-        </is>
-      </c>
-      <c r="F84" s="367" t="inlineStr">
-        <is>
-          <t>Los datos de cada gráfico coinciden con la sección 3.</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="56.8" customHeight="1">
-      <c r="B85" s="370" t="inlineStr">
+      <c r="E85" s="367" t="inlineStr">
+        <is>
+          <t>Copiar las celdas E:N de la fila «Actualizado» de la sección 3. En el PPT: clic derecho en el gráfico &gt; Editar datos; seleccionar la primera celda de la serie &gt; Pegado especial &gt; Valores + Transponer (en el gráfico los años van en filas). Destinos: diap. 4 producción (fila 81) → C2; diap. 5 ingresos (fila 84) → C2; diap. 6 costos de producción (fila 86) → C2; diap. 7 EBITDA (fila 88) → C2; diap. 8 préstamos CP (fila 95) → B2; diap. 10 ventas (fila 83) → B2 y punto de equilibrio (fila 93) → C2. La serie «Plan original» (columna B de las diap. 4 a 7; filas 82, 85, 87 y 89 de la sección 3) no se toca.</t>
+        </is>
+      </c>
+      <c r="F85" s="367" t="inlineStr">
+        <is>
+          <t>Los datos de cada gráfico coinciden con la sección 3 (años en A2:A11).</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="70.0" customHeight="1">
+      <c r="B86" s="370" t="inlineStr">
         <is>
           <t>G2</t>
         </is>
       </c>
-      <c r="C85" s="368" t="inlineStr">
+      <c r="C86" s="368" t="inlineStr">
         <is>
           <t>Tablas e indicadores</t>
         </is>
       </c>
-      <c r="D85" s="371" t="inlineStr">
+      <c r="D86" s="371" t="inlineStr">
         <is>
           <t>CONTROLES Y PPT, sección 2</t>
         </is>
       </c>
-      <c r="E85" s="367" t="inlineStr">
-        <is>
-          <t>Copiar cada valor de la columna «Libro (vivo)» con el redondeo de la diapositiva (USD con separador de miles; % con 1 decimal; diferencias de TIR en puntos porcentuales). Las variaciones contra el plan ya están calculadas contra la suma de la serie plan de los gráficos.</t>
-        </is>
-      </c>
-      <c r="F85" s="367" t="inlineStr">
+      <c r="E86" s="367" t="inlineStr">
+        <is>
+          <t>Copiar cada valor de la columna «Libro (vivo)» con el redondeo de la diapositiva (USD con separador de miles; % con 1 decimal; diferencias de TIR en puntos porcentuales). Las variaciones contra el plan se calculan contra los rótulos plan del PPT (sección 4: 150K Tn, USD 180M, USD 21,1M y USD 17,8M), con el mismo criterio que la versión de junio; así la tabla de la diap. 3 queda coherente.</t>
+        </is>
+      </c>
+      <c r="F86" s="367" t="inlineStr">
         <is>
           <t>Columna «Diferencia» explicada.</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="83.2" customHeight="1">
-      <c r="B86" s="370" t="inlineStr">
+    <row r="87" ht="136.0" customHeight="1">
+      <c r="B87" s="370" t="inlineStr">
         <is>
           <t>G3</t>
         </is>
       </c>
-      <c r="C86" s="368" t="inlineStr">
+      <c r="C87" s="368" t="inlineStr">
         <is>
           <t>Textos y conclusiones</t>
         </is>
       </c>
-      <c r="D86" s="367" t="inlineStr">
-        <is>
-          <t>Diapositivas 2, 3, 5, 7, 9, 13 y 14</t>
-        </is>
-      </c>
-      <c r="E86" s="367" t="inlineStr">
-        <is>
-          <t>Buscar (Ctrl+F) cada cifra que cambió y reemplazarla en todas las diapositivas donde se repite. Corregir además los errores de la versión de junio: acumulados de ingresos (217M → 215,6M), EBITDA (26,4M → 25,4M) y utilidad neta (19,6M → 18,0M); variaciones +21% / +25% / +10% / +7%; TIR −0,29 → −0,27 pp; margen de seguridad 52-69% → 50-69%; préstamos CP 5-12M → 4-12M; «11 productos activos en el año 1» (son 9). Rotular el año 1 como «real a &lt;mes&gt; + proyección».</t>
-        </is>
-      </c>
-      <c r="F86" s="367" t="inlineStr">
+      <c r="D87" s="367" t="inlineStr">
+        <is>
+          <t>Diapositivas 2 a 14</t>
+        </is>
+      </c>
+      <c r="E87" s="367" t="inlineStr">
+        <is>
+          <t>Buscar (Ctrl+F) cada cifra que cambió y reemplazarla en todas las diapositivas donde se repite. Corregir además los errores de la versión de junio: acumulados de ingresos (217M → 215,6M), EBITDA (26,4M → 25,4M) y utilidad neta (19,6M → 18,0M); variaciones +21% / +25% / +10% / +7%; TIR −0,29 → −0,27 pp; margen de seguridad 52-69% → 50-69%; préstamos CP 5-12M → 4-12M; «11 productos activos en el año 1» (son 9); materia prima acumulada 183M → 181,1M (diap. 6); desvío del costo de MP 6-16% → 2,7-15,8%, o «5,9-15,8% sin Accesorios» si se documenta (diap. 2, 6, 11 y 13); en la diap. 13, «USD 4-7M adicionales» = indicadores 31 y 32. El 95,3% de MP/costos del plan (diap. 6) es un valor plan: no cambiarlo sin definir la fuente oficial del plan (sección 4). Rotular el año 1 como «real a &lt;mes&gt; + proyección».</t>
+        </is>
+      </c>
+      <c r="F87" s="367" t="inlineStr">
         <is>
           <t>Cada cifra del PPT = celda de la sección 2 o 3.</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="43.6" customHeight="1">
-      <c r="B87" s="370" t="inlineStr">
+    <row r="88" ht="43.6" customHeight="1">
+      <c r="B88" s="370" t="inlineStr">
         <is>
           <t>G4</t>
         </is>
       </c>
-      <c r="C87" s="368" t="inlineStr">
+      <c r="C88" s="368" t="inlineStr">
         <is>
           <t>Payback</t>
         </is>
       </c>
-      <c r="D87" s="367" t="inlineStr">
+      <c r="D88" s="367" t="inlineStr">
         <is>
           <t>Diapositiva 9</t>
         </is>
       </c>
-      <c r="E87" s="367" t="inlineStr">
+      <c r="E88" s="367" t="inlineStr">
         <is>
           <t>Usar el valor calculado de la sección 2 (inversión propia 6,4 años: se recupera durante el año 7), no el texto del Dashboard. Indicar el criterio: dividendos descontados a Ke.</t>
         </is>
       </c>
-      <c r="F87" s="367" t="inlineStr">
+      <c r="F88" s="367" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="96.4" customHeight="1">
-      <c r="B88" s="370" t="inlineStr">
+    <row r="89" ht="162.4" customHeight="1">
+      <c r="B89" s="370" t="inlineStr">
         <is>
           <t>G5</t>
         </is>
       </c>
-      <c r="C88" s="368" t="inlineStr">
+      <c r="C89" s="368" t="inlineStr">
         <is>
           <t>Sensibilidad del VAN (diapositiva 12)</t>
         </is>
       </c>
-      <c r="D88" s="367" t="inlineStr">
+      <c r="D89" s="367" t="inlineStr">
         <is>
           <t>Copia del libro</t>
         </is>
       </c>
-      <c r="E88" s="367" t="inlineStr">
-        <is>
-          <t>El libro no tiene cálculo de sensibilidad. Para cada variable, en una COPIA: aplicar el cambio (precio: Ej_Ingresos!L8:N18 y R8:AC18 × 1,05; costo de MP: Ej_Costos!L9:N19 y R9:AC19 × 1,05; volumen: Ej_Producción L22:N32, L37:N47, R22:AC32 y R37:AC47 × 1,10; cobranza: Supuestos!B80 = 60 y desfase de 2 meses en Ej_Flujo fila 6), anotar VAN-TIR!C24 y restar el VAN base. Atención: una réplica del modelo da ≈ ±USD 5,9M de VAN por ±5% de precio y ≈ ∓USD 5,2M por ±5% de MP, muy por encima de lo que muestra la diapositiva de junio (±1,2M y ±1,0M).</t>
-        </is>
-      </c>
-      <c r="F88" s="367" t="inlineStr">
+      <c r="E89" s="367" t="inlineStr">
+        <is>
+          <t>El libro no tiene cálculo de sensibilidad. Para cada variable, en una COPIA: aplicar el cambio (precio: Ej_Ingresos!L8:N18 y R8:AC18 × 1,05; costo de MP: Ej_Costos!L9:N19 y R9:AC19 × 1,05; volumen: Ej_Producción L22:N32, L37:N47, R22:AC32 y R37:AC47 × 1,10; cobranza: Supuestos!B80 = 60 y desfase de 2 meses en Ej_Flujo fila 6), anotar VAN-TIR!C24 y restar el VAN base. Atención: una réplica del modelo da ≈ ±USD 5,9M de VAN por ±5% de precio y ≈ ∓USD 5,2M por ±5% de MP, muy por encima de lo que muestra la diapositiva de junio (±1,2M y ±1,0M). Tasa CP +2% y tipo de cambio ±10%: con este libro el VAN no cambia (el interés CP no entra al VAN y las proyecciones están en USD); informar ≈ 0 en VAN y, si se quiere mostrar, el efecto en la utilidad neta acumulada y en la caja (la tasa CP exige cambiar el 8% de cada fórmula de Ej_Flujo fila 17). Aplicar los cambios a todos los meses posteriores al corte (con corte a setiembre, L:N).</t>
+        </is>
+      </c>
+      <c r="F89" s="367" t="inlineStr">
         <is>
           <t>Diferencias documentadas por escenario.</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="30.4" customHeight="1">
-      <c r="B89" s="370" t="inlineStr">
+    <row r="90" ht="30.4" customHeight="1">
+      <c r="B90" s="370" t="inlineStr">
         <is>
           <t>G6</t>
         </is>
       </c>
-      <c r="C89" s="368" t="inlineStr">
+      <c r="C90" s="368" t="inlineStr">
         <is>
           <t>Fecha y fuente</t>
         </is>
       </c>
-      <c r="D89" s="367" t="inlineStr">
+      <c r="D90" s="367" t="inlineStr">
         <is>
           <t>Portada y cierre</t>
         </is>
       </c>
-      <c r="E89" s="367" t="inlineStr">
+      <c r="E90" s="367" t="inlineStr">
         <is>
           <t>Cambiar «Junio 2026» por la fecha de la nueva versión y citar el archivo y la versión del libro usados.</t>
         </is>
       </c>
-      <c r="F89" s="367" t="inlineStr">
+      <c r="F90" s="367" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="20" customHeight="1">
-      <c r="B91" s="364" t="inlineStr">
+    <row r="92" ht="20" customHeight="1">
+      <c r="B92" s="364" t="inlineStr">
         <is>
           <t>REGISTRO DE ACTUALIZACIONES</t>
         </is>
       </c>
-      <c r="C91" s="364"/>
-      <c r="D91" s="364"/>
-      <c r="E91" s="364"/>
-      <c r="F91" s="364"/>
-    </row>
-    <row r="92" ht="18" customHeight="1">
-      <c r="B92" s="365" t="inlineStr">
+      <c r="C92" s="364"/>
+      <c r="D92" s="364"/>
+      <c r="E92" s="364"/>
+      <c r="F92" s="364"/>
+    </row>
+    <row r="93" ht="18" customHeight="1">
+      <c r="B93" s="365" t="inlineStr">
         <is>
           <t>N.°</t>
         </is>
       </c>
-      <c r="C92" s="365" t="inlineStr">
+      <c r="C93" s="365" t="inlineStr">
         <is>
           <t>Fecha y versión</t>
         </is>
       </c>
-      <c r="D92" s="365" t="inlineStr">
+      <c r="D93" s="365" t="inlineStr">
         <is>
           <t>Corte de reales y fuente de la prospección</t>
         </is>
       </c>
-      <c r="E92" s="365" t="inlineStr">
+      <c r="E93" s="365" t="inlineStr">
         <is>
           <t>Criterios modificados y observaciones</t>
         </is>
       </c>
-      <c r="F92" s="365" t="inlineStr">
+      <c r="F93" s="365" t="inlineStr">
         <is>
           <t>Responsable</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="30.4" customHeight="1">
-      <c r="B93" s="369">
-        <v>0</v>
-      </c>
-      <c r="C93" s="367" t="inlineStr">
+    <row r="94" ht="30.4" customHeight="1">
+      <c r="B94" s="369">
+        <v>0</v>
+      </c>
+      <c r="C94" s="367" t="inlineStr">
         <is>
           <t>09/06/2026 · INFORME2 ajustado a 10 años</t>
         </is>
       </c>
-      <c r="D93" s="367" t="inlineStr">
+      <c r="D94" s="367" t="inlineStr">
         <is>
           <t>Volumen real a mayo-2026; precio real a abril-2026</t>
         </is>
       </c>
-      <c r="E93" s="367" t="inlineStr">
+      <c r="E94" s="367" t="inlineStr">
         <is>
           <t>Versión base usada en el PPT «Plan vs Actualizado 10 años» de junio 2026. Guía y controles agregados el 13/10/2026 sin modificar el modelo.</t>
         </is>
       </c>
-      <c r="F93" s="367" t="inlineStr">
+      <c r="F94" s="367" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-    </row>
-    <row r="94" ht="18" customHeight="1">
-      <c r="B94" s="369">
-        <v>1</v>
-      </c>
-      <c r="C94" s="379"/>
-      <c r="D94" s="379"/>
-      <c r="E94" s="379"/>
-      <c r="F94" s="379"/>
     </row>
     <row r="95" ht="18" customHeight="1">
       <c r="B95" s="369">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C95" s="379"/>
       <c r="D95" s="379"/>
@@ -49757,7 +49816,7 @@
     </row>
     <row r="96" ht="18" customHeight="1">
       <c r="B96" s="369">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C96" s="379"/>
       <c r="D96" s="379"/>
@@ -49766,7 +49825,7 @@
     </row>
     <row r="97" ht="18" customHeight="1">
       <c r="B97" s="369">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C97" s="379"/>
       <c r="D97" s="379"/>
@@ -49775,7 +49834,7 @@
     </row>
     <row r="98" ht="18" customHeight="1">
       <c r="B98" s="369">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C98" s="379"/>
       <c r="D98" s="379"/>
@@ -49784,12 +49843,21 @@
     </row>
     <row r="99" ht="18" customHeight="1">
       <c r="B99" s="369">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C99" s="379"/>
       <c r="D99" s="379"/>
       <c r="E99" s="379"/>
       <c r="F99" s="379"/>
+    </row>
+    <row r="100" ht="18" customHeight="1">
+      <c r="B100" s="369">
+        <v>6</v>
+      </c>
+      <c r="C100" s="379"/>
+      <c r="D100" s="379"/>
+      <c r="E100" s="379"/>
+      <c r="F100" s="379"/>
     </row>
   </sheetData>
   <mergeCells count="31">
@@ -49818,49 +49886,50 @@
     <mergeCell ref="D26:F26"/>
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B46:F46"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B68:F68"/>
-    <mergeCell ref="B76:F76"/>
-    <mergeCell ref="B82:F82"/>
-    <mergeCell ref="B91:F91"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B92:F92"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D31" location="'Servicio Deuda'!D18" tooltip="Ir a 'Servicio Deuda'!D18"/>
     <hyperlink ref="D32" location="'Ej_Producción'!B6" tooltip="Ir a 'Ej_Producción'!B6"/>
-    <hyperlink ref="D33" location="'CONTROLES Y PPT'!B35" tooltip="Ir a 'CONTROLES Y PPT'!B35"/>
+    <hyperlink ref="D33" location="'CONTROLES Y PPT'!B36" tooltip="Ir a 'CONTROLES Y PPT'!B36"/>
     <hyperlink ref="D38" location="'Ej_Flujo'!AC6" tooltip="Ir a 'Ej_Flujo'!AC6"/>
     <hyperlink ref="D39" location="'Ej_Flujo'!AC24" tooltip="Ir a 'Ej_Flujo'!AC24"/>
     <hyperlink ref="D40" location="'Ej_Flujo'!AC23" tooltip="Ir a 'Ej_Flujo'!AC23"/>
-    <hyperlink ref="D41" location="'Producción'!D26" tooltip="Ir a 'Producción'!D26"/>
+    <hyperlink ref="D41" location="'Ej_Producción'!O31" tooltip="Ir a 'Ej_Producción'!O31"/>
     <hyperlink ref="D42" location="'Ej_Costos'!O9" tooltip="Ir a 'Ej_Costos'!O9"/>
     <hyperlink ref="D43" location="'Payback'!D11" tooltip="Ir a 'Payback'!D11"/>
     <hyperlink ref="D44" location="'Payback'!C8" tooltip="Ir a 'Payback'!C8"/>
-    <hyperlink ref="D48" location="'Ej_Producción'!H22" tooltip="Ir a 'Ej_Producción'!H22"/>
-    <hyperlink ref="D49" location="'Ej_Producción'!L22" tooltip="Ir a 'Ej_Producción'!L22"/>
-    <hyperlink ref="D50" location="'Ej_Producción'!R22" tooltip="Ir a 'Ej_Producción'!R22"/>
-    <hyperlink ref="D51" location="'Supuestos'!B11" tooltip="Ir a 'Supuestos'!B11"/>
-    <hyperlink ref="D52" location="'Producción'!F6" tooltip="Ir a 'Producción'!F6"/>
-    <hyperlink ref="D53" location="'Ingresos'!F6" tooltip="Ir a 'Ingresos'!F6"/>
-    <hyperlink ref="D54" location="'Ej_Producción'!C31" tooltip="Ir a 'Ej_Producción'!C31"/>
-    <hyperlink ref="D55" location="'Producción'!D28" tooltip="Ir a 'Producción'!D28"/>
-    <hyperlink ref="D59" location="'Ej_Producción'!C22" tooltip="Ir a 'Ej_Producción'!C22"/>
-    <hyperlink ref="D60" location="'Ej_Costos'!O1" tooltip="Ir a 'Ej_Costos'!O1"/>
-    <hyperlink ref="D61" location="'Ej_Costos'!G9" tooltip="Ir a 'Ej_Costos'!G9"/>
-    <hyperlink ref="D62" location="'Ej_Costos'!G34" tooltip="Ir a 'Ej_Costos'!G34"/>
-    <hyperlink ref="D63" location="'Ej_Costos'!R34" tooltip="Ir a 'Ej_Costos'!R34"/>
-    <hyperlink ref="D64" location="'Ej_Costos'!AJ37" tooltip="Ir a 'Ej_Costos'!AJ37"/>
-    <hyperlink ref="D65" location="'Ej_Costos'!R36" tooltip="Ir a 'Ej_Costos'!R36"/>
-    <hyperlink ref="D66" location="'Supuestos'!B18" tooltip="Ir a 'Supuestos'!B18"/>
-    <hyperlink ref="D70" location="'Supuestos'!B77" tooltip="Ir a 'Supuestos'!B77"/>
-    <hyperlink ref="D71" location="'Ej_Flujo'!O40" tooltip="Ir a 'Ej_Flujo'!O40"/>
-    <hyperlink ref="D72" location="'Ej_Flujo'!P8" tooltip="Ir a 'Ej_Flujo'!P8"/>
-    <hyperlink ref="D73" location="'Ej_Costos'!R62" tooltip="Ir a 'Ej_Costos'!R62"/>
-    <hyperlink ref="D74" location="'Resultados'!H18" tooltip="Ir a 'Resultados'!H18"/>
-    <hyperlink ref="D78" location="'CONTROLES Y PPT'!B5" tooltip="Ir a 'CONTROLES Y PPT'!B5"/>
-    <hyperlink ref="D79" location="'VAN-TIR'!C22" tooltip="Ir a 'VAN-TIR'!C22"/>
-    <hyperlink ref="D84" location="'CONTROLES Y PPT'!B78" tooltip="Ir a 'CONTROLES Y PPT'!B78"/>
-    <hyperlink ref="D85" location="'CONTROLES Y PPT'!B35" tooltip="Ir a 'CONTROLES Y PPT'!B35"/>
+    <hyperlink ref="D45" location="'Ej_Flujo'!AC13" tooltip="Ir a 'Ej_Flujo'!AC13"/>
+    <hyperlink ref="D49" location="'Ej_Producción'!H22" tooltip="Ir a 'Ej_Producción'!H22"/>
+    <hyperlink ref="D50" location="'Ej_Producción'!L22" tooltip="Ir a 'Ej_Producción'!L22"/>
+    <hyperlink ref="D51" location="'Ej_Producción'!R22" tooltip="Ir a 'Ej_Producción'!R22"/>
+    <hyperlink ref="D52" location="'Supuestos'!B11" tooltip="Ir a 'Supuestos'!B11"/>
+    <hyperlink ref="D53" location="'Producción'!F6" tooltip="Ir a 'Producción'!F6"/>
+    <hyperlink ref="D54" location="'Ingresos'!F6" tooltip="Ir a 'Ingresos'!F6"/>
+    <hyperlink ref="D55" location="'Ej_Producción'!C31" tooltip="Ir a 'Ej_Producción'!C31"/>
+    <hyperlink ref="D56" location="'Producción'!D28" tooltip="Ir a 'Producción'!D28"/>
+    <hyperlink ref="D60" location="'Ej_Producción'!C22" tooltip="Ir a 'Ej_Producción'!C22"/>
+    <hyperlink ref="D61" location="'Ej_Costos'!O1" tooltip="Ir a 'Ej_Costos'!O1"/>
+    <hyperlink ref="D62" location="'Ej_Costos'!G9" tooltip="Ir a 'Ej_Costos'!G9"/>
+    <hyperlink ref="D63" location="'Ej_Costos'!G34" tooltip="Ir a 'Ej_Costos'!G34"/>
+    <hyperlink ref="D64" location="'Ej_Costos'!R34" tooltip="Ir a 'Ej_Costos'!R34"/>
+    <hyperlink ref="D65" location="'Ej_Costos'!AJ37" tooltip="Ir a 'Ej_Costos'!AJ37"/>
+    <hyperlink ref="D66" location="'Ej_Costos'!R36" tooltip="Ir a 'Ej_Costos'!R36"/>
+    <hyperlink ref="D67" location="'Supuestos'!B18" tooltip="Ir a 'Supuestos'!B18"/>
+    <hyperlink ref="D71" location="'Supuestos'!B77" tooltip="Ir a 'Supuestos'!B77"/>
+    <hyperlink ref="D72" location="'Ej_Flujo'!O40" tooltip="Ir a 'Ej_Flujo'!O40"/>
+    <hyperlink ref="D73" location="'Ej_Flujo'!P8" tooltip="Ir a 'Ej_Flujo'!P8"/>
+    <hyperlink ref="D74" location="'Ej_Costos'!R62" tooltip="Ir a 'Ej_Costos'!R62"/>
+    <hyperlink ref="D75" location="'Resultados'!H18" tooltip="Ir a 'Resultados'!H18"/>
+    <hyperlink ref="D79" location="'CONTROLES Y PPT'!B5" tooltip="Ir a 'CONTROLES Y PPT'!B5"/>
+    <hyperlink ref="D80" location="'VAN-TIR'!C22" tooltip="Ir a 'VAN-TIR'!C22"/>
+    <hyperlink ref="D85" location="'CONTROLES Y PPT'!B79" tooltip="Ir a 'CONTROLES Y PPT'!B79"/>
+    <hyperlink ref="D86" location="'CONTROLES Y PPT'!B36" tooltip="Ir a 'CONTROLES Y PPT'!B36"/>
   </hyperlinks>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" fitToHeight="0"/>

--- a/alianza/Informe_Financiero_ALIANZA_DEL_ACERO_INFORME2_09062026_AJUSTADO_A_10_AÑOS_CON_GUIA.xlsx
+++ b/alianza/Informe_Financiero_ALIANZA_DEL_ACERO_INFORME2_09062026_AJUSTADO_A_10_AÑOS_CON_GUIA.xlsx
@@ -43502,7 +43502,7 @@
     <row r="5" ht="20" customHeight="1">
       <c r="B5" s="339" t="inlineStr">
         <is>
-          <t>1. CONTROLES (todos deben quedar en OK antes de pasar al PowerPoint)</t>
+          <t>1. CONTROLES (todos en OK antes de pasar al PowerPoint, salvo el 13 si depende de la decisión de dividendos: ver paso E5)</t>
         </is>
       </c>
       <c r="C5" s="339"/>
@@ -44072,7 +44072,7 @@
       </c>
       <c r="H19" s="342" t="inlineStr">
         <is>
-          <t>E3: re-dimensionar los préstamos CP (Ej_Flujo fila 8) hasta que el saldo no sea negativo. Es normal que siga en REVISAR hasta terminar la fase E: la fase B lo empeora.</t>
+          <t>E3: redimensionar los préstamos CP (Ej_Flujo fila 8) hasta que el saldo no sea negativo. Es normal que siga en REVISAR hasta terminar la fase E: la fase B lo empeora.</t>
         </is>
       </c>
       <c r="I19" s="342"/>
@@ -44112,7 +44112,7 @@
       </c>
       <c r="H20" s="342" t="inlineStr">
         <is>
-          <t>E3: cada desembolso de la fila 8 necesita su devolución en la fila 16 antes de dic-2035.</t>
+          <t>E3: cada desembolso de la fila 8 necesita su devolución en la fila 16, a más tardar en dic-2035 (EA16).</t>
         </is>
       </c>
       <c r="I20" s="342"/>
@@ -44152,7 +44152,7 @@
       </c>
       <c r="H21" s="342" t="inlineStr">
         <is>
-          <t>E4: cablear Ej_Costos!R62:AC62 a Ej_Flujo fila 17 del mismo mes.</t>
+          <t>E4: vincular Ej_Costos!R62:AC62 a Ej_Flujo fila 17 del mismo mes.</t>
         </is>
       </c>
       <c r="I21" s="342"/>
@@ -44472,7 +44472,7 @@
       </c>
       <c r="H29" s="342" t="inlineStr">
         <is>
-          <t>E5: con utilidades menores a 500.000 (año 6) u 800.000 (año 7) el calendario fijo da negativo; consultar a la Dirección.</t>
+          <t>E5: con utilidades menores a 500.000 (año 6) u 800.000 (año 7) el calendario fijo da negativo; la Gerencia lo presenta a la Dirección.</t>
         </is>
       </c>
       <c r="I29" s="342"/>
@@ -46206,7 +46206,7 @@
     <row r="79" ht="20" customHeight="1">
       <c r="B79" s="339" t="inlineStr">
         <is>
-          <t>3. SERIES ANUALES PARA LOS GRÁFICOS (clic derecho en el gráfico &gt; Editar datos &gt; pegar la fila «Actualizado»)</t>
+          <t>3. SERIES ANUALES PARA LOS GRÁFICOS (copiar E:N de la fila «Actualizado»; en el PPT: Editar datos &gt; primera celda de la serie &gt; Pegado especial &gt; Valores + Transponer; ver paso G1)</t>
         </is>
       </c>
       <c r="C79" s="339"/>
@@ -47972,7 +47972,7 @@
     <row r="3" ht="30" customHeight="1">
       <c r="B3" s="363" t="inlineStr">
         <is>
-          <t>Alianza del Acero · Modelo a 10 años (Año 1 = 2026 … Año 10 = 2035) · Libro base: INFORME2 ajustado a 10 años (09/06/2026) · Guía preparada el 13/10/2026 · Controles y datos para el PowerPoint en la hoja «CONTROLES Y PPT».</t>
+          <t>Alianza del Acero · Modelo a 10 años (Año 1 = 2026 … Año 10 = 2035) · Libro base: INFORME2 ajustado a 10 años (09/06/2026) · Guía preparada el 13/10/2026 y actualizada el 16/10/2026 · Controles y datos para el PowerPoint en la hoja «CONTROLES Y PPT».</t>
         </is>
       </c>
       <c r="C3" s="363"/>
@@ -47999,7 +47999,7 @@
       </c>
       <c r="C6" s="367" t="inlineStr">
         <is>
-          <t>Seguir las fases en orden: A Preparar → B Correcciones únicas → C Ventas → D Costos → E Caja y préstamos CP → F Resultados y controles → G PowerPoint. Al terminar cada fase presionar F9 y revisar en «CONTROLES Y PPT» los controles que indica cada paso (columna «Control / resultado esperado»). Los controles 13, 14 y 23 (caja, préstamos CP y dividendos) recién deben quedar en OK al terminar la fase E; en el paso F1, todos.</t>
+          <t>Seguir las fases en orden: A Preparar → B Correcciones únicas → C Ventas → D Costos → E Caja y préstamos CP → F Resultados y controles → G PowerPoint. Al terminar cada fase presionar F9 y revisar en «CONTROLES Y PPT» los controles que indica cada paso (columna «Control / resultado esperado»). Los controles 13, 14 y 23 (caja, préstamos CP y dividendos) recién deben quedar en OK al terminar la fase E; en el paso F1, todos (salvo el 13 si depende de la decisión de dividendos: paso E5).</t>
         </is>
       </c>
       <c r="D6" s="367"/>
@@ -48051,7 +48051,7 @@
       <c r="E9" s="367"/>
       <c r="F9" s="367"/>
     </row>
-    <row r="10" ht="43.6" customHeight="1">
+    <row r="10" ht="56.8" customHeight="1">
       <c r="B10" s="369" t="inlineStr">
         <is>
           <t>•</t>
@@ -48059,7 +48059,7 @@
       </c>
       <c r="C10" s="367" t="inlineStr">
         <is>
-          <t>Escribir solo en las celdas indicadas. No escribir en columnas de total o promedio (O y AD de las hojas Ej_; O, AB, AO, BB, BO, CB, CO, DB, DO, EB y EF de Ej_Flujo), salvo las celdas que un paso indica expresamente: Ej_Producción!O31:O32 y O46:O47 (B4), Ej_Costos!O9:O19 y AD9:AD19 (B5), Ej_Costos!O1 (D2) y Ej_Flujo!O37 y O40 (E2). Tampoco en el plan original (columnas P y AE de las hojas Ej_; columna E de Supuestos).</t>
+          <t>Escribir solo en las celdas indicadas. No escribir en columnas de total o promedio (O y AD de Ej_Producción, Ej_Ingresos, Ej_Costos, Ej_Resultados y Ej_Deuda; O, AB, AO, BB, BO, CB, CO, DB, DO, EB y EF de Ej_Flujo), salvo las celdas que un paso indica expresamente: Ej_Producción!O31:O32 y O46:O47 (B4), Ej_Costos!O9:O19 y AD9:AD19 (B5), Ej_Costos!O1 (D2) y Ej_Flujo!O37 y O40 (E2). Tampoco en el plan original (columnas P y AE de esas cinco hojas; columna E de Supuestos). En Ej_Flujo no hay columnas de plan: P, AD y AE son meses (ene-2027, feb-2028 y mar-2028) y se editan cuando un paso lo indica. El auxiliar Ej_Costos!O88:P114 (paso D5) no es plan ni total.</t>
         </is>
       </c>
       <c r="D10" s="367"/>
@@ -48224,7 +48224,7 @@
       </c>
       <c r="D21" s="367" t="inlineStr">
         <is>
-          <t>Días de Supuestos!B77:B83: caja 2, sueldos 15, stock MP 45, ventas a crédito 90, proveedores menores 15. En el flujo mensual, las ventas se cobran a los 3 meses.</t>
+          <t>Días de Supuestos!B77:B83: caja 2, sueldos 15, stock MP 45, ventas a crédito 90, producto terminado 0, crédito de proveedores de MP 0 (sin crédito del proveedor de chapa) y proveedores menores 15. En el flujo mensual, las ventas se cobran a los 3 meses.</t>
         </is>
       </c>
       <c r="E21" s="367"/>
@@ -48298,7 +48298,7 @@
       <c r="E25" s="367"/>
       <c r="F25" s="367"/>
     </row>
-    <row r="26" ht="30.4" customHeight="1">
+    <row r="26" ht="43.6" customHeight="1">
       <c r="B26" s="369">
         <v>12</v>
       </c>
@@ -48309,7 +48309,7 @@
       </c>
       <c r="D26" s="367" t="inlineStr">
         <is>
-          <t>En el libro solo están el plan de los años 1 y 2 (columnas P y AE de las hojas Ej_) y los supuestos originales (Supuestos, columna E). El VAN y la TIR del plan y las series de los años 3-10 están en «CONTROLES Y PPT», sección 4.</t>
+          <t>En el libro solo están el plan de los años 1 y 2 (columnas P y AE de Ej_Producción, Ej_Ingresos, Ej_Costos, Ej_Resultados y Ej_Deuda) y los supuestos originales (Supuestos, columna E). En «CONTROLES Y PPT», el VAN, la TIR, el payback y los rótulos acumulados del plan están en la sección 4, y las series plan de los gráficos (los 10 años, copiadas del PPT de junio) en la sección 3, filas 82, 85, 87 y 89.</t>
         </is>
       </c>
       <c r="E26" s="367"/>
@@ -48353,7 +48353,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="30.4" customHeight="1">
+    <row r="30" ht="70.0" customHeight="1">
       <c r="B30" s="370" t="inlineStr">
         <is>
           <t>A1</t>
@@ -48371,16 +48371,16 @@
       </c>
       <c r="E30" s="367" t="inlineStr">
         <is>
-          <t>Archivo &gt; Guardar como: «…_RV01_PROSPECCION_AAAAMMDD.xlsx». Trabajar siempre sobre la copia y conservar la versión anterior para comparar.</t>
+          <t>Archivo &gt; Guardar como: «…_RV01_PROSPECCION_AAAAMMDD.xlsx». Trabajar siempre sobre la copia y conservar la versión anterior para comparar. Antes de la fase G, hacer lo mismo con el PowerPoint (Informe_Ejecutivo_Plan_vs_Actualizado_ALIANZA_DEL_ACERO_10_AÑOS.pptx): guardarlo con un nombre nuevo («…_RV01_AAAAMMDD.pptx») y editar solo la copia.</t>
         </is>
       </c>
       <c r="F30" s="367" t="inlineStr">
         <is>
-          <t>El nombre del archivo indica versión y fecha.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="43.6" customHeight="1">
+          <t>Los nombres del libro y del PPT indican versión y fecha.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="56.8" customHeight="1">
       <c r="B31" s="370" t="inlineStr">
         <is>
           <t>A2</t>
@@ -48398,12 +48398,12 @@
       </c>
       <c r="E31" s="367" t="inlineStr">
         <is>
-          <t>Datos &gt; Editar vínculos. Ante el aviso de vínculos externos, elegir «No actualizar»: la deuda LP de 'Servicio Deuda'!D18:I20 viene del archivo CALCULADORA PRESTAMO, que no está en este equipo. Fórmulas &gt; Opciones para el cálculo &gt; Automático.</t>
+          <t>Al abrir el libro, ante el aviso de vínculos externos, elegir «No actualizar»: la deuda LP de 'Servicio Deuda'!D18:I20 viene del archivo CALCULADORA PRESTAMO, que no está en este equipo. En Datos &gt; Editar vínculos se puede confirmar que el vínculo quedó sin actualizar. Fórmulas &gt; Opciones para el cálculo &gt; Automático.</t>
         </is>
       </c>
       <c r="F31" s="367" t="inlineStr">
         <is>
-          <t>'Servicio Deuda'!D18 sigue en 29.277,76, sin error.</t>
+          <t>Después del paso A3 (la hoja Servicio Deuda está oculta): 'Servicio Deuda'!D18 sigue en 29.277,76, sin error.</t>
         </is>
       </c>
     </row>
@@ -48598,7 +48598,7 @@
       </c>
       <c r="E40" s="367" t="inlineStr">
         <is>
-          <t>Opción exacta: AC23:AN23 =('Servicio Deuda'!$F$23+'Servicio Deuda'!$F$24+'Servicio Deuda'!$F$25)/12; AP23:BA23 igual con la columna G; BC23:BN23 con la H; BP23:BY23 =('Servicio Deuda'!$I$23+'Servicio Deuda'!$I$24+'Servicio Deuda'!$I$25)/10. Agrega unos USD 464.000 de egresos en jul-oct 2031 (4 × 116.058) y, neto de la baja de las cuotas 2028-2030, unos USD 387.000 (= valor actual del control 17). Después hay que revisar los préstamos CP (paso E3).</t>
+          <t>AC23:AN23 =('Servicio Deuda'!$F$23+'Servicio Deuda'!$F$24+'Servicio Deuda'!$F$25)/12; AP23:BA23 igual con la columna G; BC23:BN23 con la H; BP23:BY23 =('Servicio Deuda'!$I$23+'Servicio Deuda'!$I$24+'Servicio Deuda'!$I$25)/10. Agrega unos USD 464.000 de egresos en jul-oct 2031 (4 × 116.058) y, neto de la baja de las cuotas de ene-2028 a jun-2031 (≈ USD 77.000), unos USD 387.000 (≈ valor actual del control 17). Después hay que revisar los préstamos CP (paso E3).</t>
         </is>
       </c>
       <c r="F40" s="367" t="inlineStr">
@@ -48688,7 +48688,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="70.0" customHeight="1">
+    <row r="44" ht="96.4" customHeight="1">
       <c r="B44" s="370" t="inlineStr">
         <is>
           <t>B7</t>
@@ -48706,7 +48706,7 @@
       </c>
       <c r="E44" s="367" t="inlineStr">
         <is>
-          <t>B8 «Payback inversión propia (años)». C8 =SI.ERROR(CONTAR.SI(D7:M7;"&lt;0")+(-INDICE(C7:M7;CONTAR.SI(C7:M7;"&lt;0")))/INDICE(C6:M6;CONTAR.SI(C7:M7;"&lt;0")+1);"No recupera en 10 años"). B13 «Payback inversión total (años)» y en C13 la misma fórmula sobre las filas 11 (flujo) y 12 (acumulado). Luego Dashboard!C12 =Payback!C8 y C13 =Payback!C13, con formato 0,0 "años".</t>
+          <t>En Payback!B8 escribir el rótulo «Payback inversión propia (años)» y en Payback!C8: =SI.ERROR(CONTAR.SI(D7:M7;"&lt;0")+(-INDICE(C7:M7;CONTAR.SI(C7:M7;"&lt;0")))/INDICE(C6:M6;CONTAR.SI(C7:M7;"&lt;0")+1);"No recupera en 10 años"). En Payback!B13 escribir «Payback inversión total (años)» y en Payback!C13: =SI.ERROR(CONTAR.SI(D12:M12;"&lt;0")+(-INDICE(C12:M12;CONTAR.SI(C12:M12;"&lt;0")))/INDICE(C11:M11;CONTAR.SI(C12:M12;"&lt;0")+1);"No recupera en 10 años"). Luego Dashboard!C12 =Payback!C8 y Dashboard!C13 =Payback!C13 (hoy dicen «4 Años» y «7 Años» tipeados), con formato 0,0 "años".</t>
         </is>
       </c>
       <c r="F44" s="367" t="inlineStr">
@@ -48715,7 +48715,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="188.8" customHeight="1">
+    <row r="45" ht="202.0" customHeight="1">
       <c r="B45" s="370" t="inlineStr">
         <is>
           <t>B8</t>
@@ -48733,7 +48733,7 @@
       </c>
       <c r="E45" s="367" t="inlineStr">
         <is>
-          <t>Mismo mapeo que 2027, con el costo anual de la hoja Costos / 12. Para 2028: AC13:AN13 =(Costos!$F$10+Costos!$F$13+Costos!$F$27)/12 (insumos, packaging y honorarios); AC19:AN19 =(Costos!$F$7+Costos!$F$8+Costos!$F$14+Costos!$F$20+Costos!$F$21)/12 (nómina y alimentación); AC21:AN21 =(Costos!$F$16+Costos!$F$22+Costos!$F$23)/12 (energía, servicios y alquileres); AC22:AN22 =(Costos!$F$9+Costos!$F$11+Costos!$F$12+Costos!$F$15+Costos!$F$24+Costos!$F$25+Costos!$F$26)/12 (otros). Repetir con la columna G de Costos en AP:BA, H en BC:BN, I en BP:CA, J en CC:CN, K en CP:DA, L en DC:DN y M en DP:EA, sin escribir en las columnas de total. Hoy esas filas repiten los montos de 2027 y no siguen al volumen: el cambio agrega ≈ USD 1,62M de egresos en 2028-2035. Atención: la fila 25 («Inversiones / CAPEX») repite desde feb-2027 los servicios de terceros de Steel Frame que ya están en la fila 22 (USD 3.750/mes; 371.250 en 2027-2035). Confirmarlo con quien armó el modelo; si es una duplicación, dejar en 0 las columnas de mes de la fila 25 desde feb-2027 y anotarlo en el registro.</t>
+          <t>Mismo mapeo que 2027, con el costo anual de la hoja Costos / 12. Para 2028: AC13:AN13 =(Costos!$F$10+Costos!$F$13+Costos!$F$27)/12 (insumos, packaging y honorarios); AC19:AN19 =(Costos!$F$7+Costos!$F$8+Costos!$F$14+Costos!$F$20+Costos!$F$21)/12 (nómina y alimentación); AC21:AN21 =(Costos!$F$16+Costos!$F$22+Costos!$F$23)/12 (energía, servicios y alquileres); AC22:AN22 =(Costos!$F$9+Costos!$F$11+Costos!$F$12+Costos!$F$15+Costos!$F$24+Costos!$F$25+Costos!$F$26)/12 (otros). Repetir con la columna G de Costos en AP:BA, H en BC:BN, I en BP:CA, J en CC:CN, K en CP:DA, L en DC:DN y M en DP:EA, sin escribir en las columnas de total. Hoy esas filas son valores pegados, iguales en los ocho años 2028-2035 (parecidos a 2027, pero no iguales en las filas 13 y 22), y no siguen al volumen: el cambio agrega ≈ USD 1,62M de egresos en 2028-2035. Atención: la fila 25 («Inversiones / CAPEX») repite desde feb-2027 los servicios de terceros de Steel Frame que ya están en la fila 22 (USD 3.750/mes; 371.250 en 2027-2035). Confirmarlo con quien armó el modelo; si es una duplicación, dejar en 0 las columnas de mes de la fila 25 desde feb-2027 y anotarlo en el registro.</t>
         </is>
       </c>
       <c r="F45" s="367" t="inlineStr">
@@ -48780,7 +48780,7 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="109.6" customHeight="1">
+    <row r="49" ht="136.0" customHeight="1">
       <c r="B49" s="370" t="inlineStr">
         <is>
           <t>C1</t>
@@ -48798,7 +48798,7 @@
       </c>
       <c r="E49" s="367" t="inlineStr">
         <is>
-          <t>Rangos: Ej_Producción!H22:K32 (producción) y H37:K47 (ventas); Ej_Ingresos!G8:K18 (precio). Desde el primer mes no real hasta el corte (hoy: volumen desde junio, columna H; precio desde mayo, columna G). Producción en Tn producidas y ventas en Tn facturadas, por producto y mes. Precio = facturación del mes en USD sin IVA ÷ Tn vendidas del mismo producto (si se facturó en Gs, convertir con el TC del mes). Mes sin venta: Tn = 0. Pasar los meses reales a formato azul (Copiar formato desde C22 y C8) y actualizar los títulos B2 («…EJECUTADO A &lt;MES&gt;…») de Ej_Producción, Ej_Ingresos y Ej_Costos.</t>
+          <t>Rangos (ejemplo con corte a setiembre; si el corte es otro, terminar en la columna de ese mes): Ej_Producción!H22:K32 (producción) y H37:K47 (ventas); Ej_Ingresos!G8:K18 (precio). Desde el primer mes no real (hoy: volumen desde junio, columna H; precio desde mayo, columna G) hasta el mes del corte (setiembre = columna K). Producción en Tn producidas y ventas en Tn facturadas, por producto y mes. Precio = facturación del mes en USD sin IVA ÷ Tn vendidas del mismo producto (si se facturó en Gs, convertir con el TC del mes). Mes sin venta: Tn = 0. Pasar los meses reales a formato azul (Copiar formato desde C22 y C8) y actualizar los títulos B2: en Ej_Producción y Ej_Ingresos, «…EJECUTADO A ABRIL…» → mes del corte; en Ej_Costos, «…EJECUTADO &amp; PROYECTADO» → «…EJECUTADO A &lt;MES&gt; &amp; PROYECTADO».</t>
         </is>
       </c>
       <c r="F49" s="367" t="inlineStr">
@@ -48884,7 +48884,7 @@
       </c>
       <c r="F52" s="367" t="inlineStr">
         <is>
-          <t>Producción!F6/E6 − 1 = B11 en cada producto.</t>
+          <t>Producción!F6/E6 − 1 ≈ B11 en cada producto (por el redondeo a Tn enteras difiere hasta ±0,2 puntos; hoy da entre 4,96% y 5,15% con B11 = 5%).</t>
         </is>
       </c>
     </row>
@@ -49115,7 +49115,7 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="56.8" customHeight="1">
+    <row r="63" ht="70.0" customHeight="1">
       <c r="B63" s="370" t="inlineStr">
         <is>
           <t>D4</t>
@@ -49133,7 +49133,7 @@
       </c>
       <c r="E63" s="367" t="inlineStr">
         <is>
-          <t>Rango: G34:K54 (meses cerrados). Mismo criterio que ene-abr: los montos en Gs se cargan como =MontoGs/USD (p. ej. =29898626/USD), encima de la fórmula de proyección del mes. Los meses sin gasto, en 0. Las filas 35 y 48 quedan en 0 porque las cargas sociales ya están en las filas 34 y 47.</t>
+          <t>Rango (ejemplo con corte a setiembre): G34:K54 (may-sep, meses cerrados). Mismo criterio que ene-abr: los montos en Gs se cargan como =MontoGs/USD (p. ej. =29898626/USD), encima de la fórmula de proyección del mes. Los meses sin gasto, en 0. Las filas 35 y 48 quedan en 0 porque las cargas sociales ya están en las filas 34 y 47.</t>
         </is>
       </c>
       <c r="F63" s="367" t="inlineStr">
@@ -49165,7 +49165,7 @@
       </c>
       <c r="F64" s="367" t="inlineStr">
         <is>
-          <t>MO año 2 → año 3 crece ≈ 3,8%.</t>
+          <t>=(Costos!F7+Costos!F8+Costos!F20+Costos!F21)/(Costos!E7+Costos!E8+Costos!E20+Costos!E21)-1 ≈ 3,8% (= 1,03 × 1,4309 / 1,42 − 1, cualquiera sea la dotación de 2027).</t>
         </is>
       </c>
     </row>
@@ -49288,7 +49288,7 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="43.6" customHeight="1">
+    <row r="71" ht="96.4" customHeight="1">
       <c r="B71" s="370" t="inlineStr">
         <is>
           <t>E1</t>
@@ -49306,7 +49306,7 @@
       </c>
       <c r="E71" s="367" t="inlineStr">
         <is>
-          <t>Mantener 2 / 15 / 45 / 90 / 0 / 0 / 15 salvo un cambio de política. Si cambia B80 (cobro), también hay que mover el desfase de los cobros de Ej_Flujo fila 6 (hoy fijo en 3 meses) y corregir los rótulos de Capital Trabajo!B7:B15.</t>
+          <t>Mantener B77 caja 2, B78 sueldos 15, B79 stock MP 45, B80 ventas a crédito 90, B81 producto terminado 0, B82 crédito de proveedores de MP 0 y B83 proveedores menores 15 (días), salvo un cambio de política. Si cambia B80 (cobro), también hay que mover el desfase de los cobros de Ej_Flujo fila 6 (hoy cada mes cobra la venta de 3 meses antes; p. ej. F6 =+Ej_Ingresos!C34 cobra en abril la venta de enero) y corregir los rótulos de Capital Trabajo!B7:B15. Ese desfase solo afecta la caja mensual: el VAN toma el capital de trabajo de la hoja Capital Trabajo.</t>
         </is>
       </c>
       <c r="F71" s="367" t="inlineStr">
@@ -49342,7 +49342,7 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="188.8" customHeight="1">
+    <row r="73" ht="202.0" customHeight="1">
       <c r="B73" s="370" t="inlineStr">
         <is>
           <t>E3</t>
@@ -49350,7 +49350,7 @@
       </c>
       <c r="C73" s="368" t="inlineStr">
         <is>
-          <t>Re-dimensionar los préstamos CP para chapas</t>
+          <t>Redimensionar los préstamos CP para chapas</t>
         </is>
       </c>
       <c r="D73" s="371" t="inlineStr">
@@ -49360,12 +49360,12 @@
       </c>
       <c r="E73" s="367" t="inlineStr">
         <is>
-          <t>Filas 8, 16, 17 y 29 (solo columnas de mes). Con B1-B3 y la prospección cargados, recorrer el saldo mensual (fila 29) desde ago-2026. Para cada préstamo: (a) monto en la fila 8 del mes de desembolso (múltiplos de 100.000); (b) en la fila 16 del mes de devolución =+&lt;celda de la fila 8&gt; (ej. V16 =+P8); (c) en la fila 17 de esa columna =((8%/365)*DÍAS)*&lt;celda fila 16&gt;, con DÍAS = 30 × meses (ene→jul = 180); (d) si se mueve o elimina un desembolso, mover o borrar también su devolución y su interés; (e) un préstamo CP en 2026 se carga igual; si se devuelve dentro de 2026, sumar su interés en Ej_Costos (paso E4). L16 (2.779.626) y L17 (125.862) son la devolución a CIE S.A., no préstamos CP: no tocarlas. Meta: saldo ≥ 0 todos los meses, con un colchón de 100.000 a 400.000, y todo devuelto antes de dic-2035. Antes de la fase B el único déficit es ago-2032 (CJ29 = −245.726). Después de la fase B, con los datos actuales, hay faltantes de calce desde abr-2030 (máximo −736.000 en ago-2032 sin contar dividendos) y el saldo de dic-2035 queda en ≈ −2,22M después de los dividendos: ver E5.</t>
+          <t>Se escribe en las filas 8, 16 y 17 (solo columnas de mes); la fila 29 (saldo acumulado) es fórmula y solo se lee. Con la fase B completa (B1-B8) y la prospección cargada, recorrer el saldo mensual (fila 29) desde ago-2026. Para cada préstamo: (a) monto en la fila 8 del mes de desembolso (múltiplos de 100.000); (b) en la fila 16 del mes de devolución =+&lt;celda de la fila 8&gt; (ej. V16 =+P8); (c) en la fila 17 de esa columna =((8%/365)*DÍAS)*&lt;celda fila 16&gt;, con DÍAS = 30 × meses (ene→jul = 180); (d) si se mueve o elimina un desembolso, mover o borrar también su devolución y su interés; (e) un préstamo CP en 2026 se carga igual; si se devuelve dentro de 2026, sumar su interés en Ej_Costos (paso E4). L16 (2.779.626) y L17 (125.862) son la devolución a CIE S.A., no préstamos CP: no tocarlas. Meta: saldo ≥ 0 todos los meses, con un colchón de 100.000 a 400.000, y todo devuelto a más tardar en dic-2035 (columna EA). Antes de la fase B el único déficit es ago-2032 (CJ29 = −245.726). Después de la fase B, con los datos actuales, hay faltantes de calce desde abr-2030 (máximo −736.000 en ago-2032 sin contar dividendos) y el saldo de dic-2035 queda en ≈ −2,22M después de los dividendos: ver E5.</t>
         </is>
       </c>
       <c r="F73" s="367" t="inlineStr">
         <is>
-          <t>Controles 13 y 14 en OK.</t>
+          <t>Controles 13 y 14 en OK (el 13, salvo que dependa de la decisión de dividendos: paso E5).</t>
         </is>
       </c>
     </row>
@@ -49396,7 +49396,7 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="122.8" customHeight="1">
+    <row r="75" ht="175.6" customHeight="1">
       <c r="B75" s="370" t="inlineStr">
         <is>
           <t>E5</t>
@@ -49414,7 +49414,7 @@
       </c>
       <c r="E75" s="367" t="inlineStr">
         <is>
-          <t>Las nuevas utilidades cambian los dividendos (Resultados fila 18; calendario fijo desde 2031, con montos tipeados de 500.000 y 800.000), que se pagan en diciembre en Ej_Flujo fila 20 (CA20, CN20, DA20, DN20 y EA20; esa fila no tiene totales anuales). Si cambia la caja, volver a E3 hasta que el saldo mínimo se estabilice (2 o 3 vueltas). Si con todos los CP devueltos el saldo de dic-2035 sigue negativo (hoy ≈ −2,22M después de la fase B, con ≈ USD 10M de dividendos en 2031-2035), el calendario de dividendos excede la caja disponible: presentar a la Gerencia las alternativas (diferir o reducir dividendos, mantener deuda CP al cierre o refinanciar a largo plazo). No cambiar la política sin instrucción de la Dirección.</t>
+          <t>Las nuevas utilidades cambian los dividendos (Resultados fila 18, calculados en las filas 25-31 sobre la retención de utilidades de la fila 17). El calendario es fijo: en 2031 se paga el 50% de la utilidad de 2027; en 2032, el otro 50% de 2027 y la de 2028; en 2033, la de 2029; en 2034, la de 2030 y 500.000 de la de 2031 (H29, tipeado); en 2035, el resto de 2031 y 800.000 de la de 2032 (I30, tipeado). Se pagan en diciembre en Ej_Flujo fila 20 (CA20, CN20, DA20, DN20 y EA20; esa fila no tiene totales anuales). Si cambia la caja, volver a E3 hasta que el saldo mínimo se estabilice (2 o 3 vueltas). Si con todos los CP devueltos el saldo de dic-2035 sigue negativo (hoy ≈ −2,22M después de la fase B, con ≈ USD 10M de dividendos en 2031-2035), el calendario de dividendos excede la caja disponible: la Gerencia presenta a la Dirección las alternativas (diferir o reducir dividendos, mantener deuda CP al cierre o refinanciar a largo plazo). No cambiar la política sin instrucción de la Dirección.</t>
         </is>
       </c>
       <c r="F75" s="367" t="inlineStr">
@@ -49461,7 +49461,7 @@
         </is>
       </c>
     </row>
-    <row r="79" ht="56.8" customHeight="1">
+    <row r="79" ht="122.8" customHeight="1">
       <c r="B79" s="370" t="inlineStr">
         <is>
           <t>F1</t>
@@ -49479,12 +49479,12 @@
       </c>
       <c r="E79" s="367" t="inlineStr">
         <is>
-          <t>Presionar F9 (o Ctrl+Alt+F9). Todos los controles deben quedar en OK; la última columna indica qué paso revisar. Con el libro tal como llegó hay 8 controles en REVISAR: el 9, 11, 12, 17, 21, 22 y 26 se corrigen en la fase B; el 13 (déficit de caja) se corrige en E3 y E5, y empeora después de la fase B.</t>
+          <t>Presionar F9 (o Ctrl+Alt+F9). Todos los controles deben quedar en OK; la última columna indica qué paso revisar. Con el libro tal como llegó hay 8 controles en REVISAR: el 9, 11, 12, 17, 21, 22 y 26 se corrigen en la fase B; el 13 (déficit de caja) se corrige en E3 y E5, y empeora después de la fase B. Excepción: si el control 13 solo puede pasar a OK cambiando la política de dividendos o dejando préstamos CP sin devolver al cierre (control 14), no forzarlo: dejarlo en REVISAR, anotar en el registro el saldo de dic-2035 y las alternativas presentadas (paso E5) y seguir con la fase G, aclarando en el PPT que la caja 2031-2035 depende de esa decisión.</t>
         </is>
       </c>
       <c r="F79" s="367" t="inlineStr">
         <is>
-          <t>26 de 26 controles en OK.</t>
+          <t>26 de 26 controles en OK, o 25 de 26 con el control 13 pendiente de la decisión de dividendos y anotado en el registro.</t>
         </is>
       </c>
     </row>
@@ -49526,9 +49526,9 @@
           <t>Registrar la actualización</t>
         </is>
       </c>
-      <c r="D81" s="367" t="inlineStr">
-        <is>
-          <t>Registro al final de esta hoja</t>
+      <c r="D81" s="371" t="inlineStr">
+        <is>
+          <t>Registro de actualizaciones</t>
         </is>
       </c>
       <c r="E81" s="367" t="inlineStr">
@@ -49607,7 +49607,7 @@
         </is>
       </c>
     </row>
-    <row r="86" ht="70.0" customHeight="1">
+    <row r="86" ht="83.2" customHeight="1">
       <c r="B86" s="370" t="inlineStr">
         <is>
           <t>G2</t>
@@ -49625,7 +49625,7 @@
       </c>
       <c r="E86" s="367" t="inlineStr">
         <is>
-          <t>Copiar cada valor de la columna «Libro (vivo)» con el redondeo de la diapositiva (USD con separador de miles; % con 1 decimal; diferencias de TIR en puntos porcentuales). Las variaciones contra el plan se calculan contra los rótulos plan del PPT (sección 4: 150K Tn, USD 180M, USD 21,1M y USD 17,8M), con el mismo criterio que la versión de junio; así la tabla de la diap. 3 queda coherente.</t>
+          <t>Copiar cada valor de la columna «Libro (vivo)» con el redondeo de la diapositiva (USD con separador de miles; % con 1 decimal; diferencias de TIR en puntos porcentuales). Las variaciones contra el plan se calculan contra los rótulos plan del PPT (sección 4 de «CONTROLES Y PPT»: 150K Tn, USD 180M, USD 21,1M y USD 17,8M), con el mismo criterio que la versión de junio; así la tabla de la diap. 3 queda coherente.</t>
         </is>
       </c>
       <c r="F86" s="367" t="inlineStr">
@@ -49634,7 +49634,7 @@
         </is>
       </c>
     </row>
-    <row r="87" ht="136.0" customHeight="1">
+    <row r="87" ht="320.8" customHeight="1">
       <c r="B87" s="370" t="inlineStr">
         <is>
           <t>G3</t>
@@ -49652,16 +49652,16 @@
       </c>
       <c r="E87" s="367" t="inlineStr">
         <is>
-          <t>Buscar (Ctrl+F) cada cifra que cambió y reemplazarla en todas las diapositivas donde se repite. Corregir además los errores de la versión de junio: acumulados de ingresos (217M → 215,6M), EBITDA (26,4M → 25,4M) y utilidad neta (19,6M → 18,0M); variaciones +21% / +25% / +10% / +7%; TIR −0,29 → −0,27 pp; margen de seguridad 52-69% → 50-69%; préstamos CP 5-12M → 4-12M; «11 productos activos en el año 1» (son 9); materia prima acumulada 183M → 181,1M (diap. 6); desvío del costo de MP 6-16% → 2,7-15,8%, o «5,9-15,8% sin Accesorios» si se documenta (diap. 2, 6, 11 y 13); en la diap. 13, «USD 4-7M adicionales» = indicadores 31 y 32. El 95,3% de MP/costos del plan (diap. 6) es un valor plan: no cambiarlo sin definir la fuente oficial del plan (sección 4). Rotular el año 1 como «real a &lt;mes&gt; + proyección».</t>
+          <t>Buscar (Ctrl+F) cada cifra que cambió y reemplazarla en todas las diapositivas donde se repite, siempre con el valor vivo de las secciones 2 y 3 de «CONTROLES Y PPT» (con el libro ya actualizado). La versión de junio, además, tenía cifras que no coincidían con el libro de ese momento; como referencia (PPT de junio → libro de junio): ingresos acumulados 217M → 215,6M; EBITDA acumulado 26,4M → 25,4M; utilidad neta acumulada 19,6M → 18,0M; variaciones contra el plan +7% → +7,5% (producción, indicador 13; diap. 3, 4 y 13), +21% → +19,8% (ingresos, indicador 15; diap. 3, 5, 9 y 13), +25% → +20,4% (EBITDA, indicador 17; diap. 3, 7, 9 y 13) y +10% → +1,3% (utilidad neta, indicador 19; diap. 3); el «+25%» de la diap. 5 es otro dato (ingresos del año 10 contra el plan, hoy +25,3%): no reemplazarlo por el del EBITDA; TIR −0,29 → −0,27 pp; margen de seguridad 52-69% → 50-69% (diap. 10); préstamos CP «5-12M» → «4-12M» (diap. 11 y 13) y «5-11.9M» → «4-11.9M» (diap. 8); «11 vs 8 productos activos en Año 1» → «9 vs 8» (diap. 4); materia prima acumulada 183M → 181,1M (diap. 6); desvío del costo de MP 6-16% → 2,7-15,8%, o «5,9-15,8% sin Accesorios» si se documenta (diap. 2, 6, 11 y 13). Revisar también dos frases que no coinciden con las series: diap. 7, «los márgenes EBITDA actualizados son superiores en años 2-5» (solo el año 2 supera al plan: 14,1% frente a 12,8%; el año 3 queda igual y los años 4 a 10, por debajo); diap. 10, «a partir del Año 6 (fin de deuda LP), el PE baja significativamente» (sube de 6.204 Tn en el año 5 a 6.433 en el año 6, baja a 5.492 en el año 7 y vuelve a subir hasta 7.854 en el año 10). En la diap. 13, «USD 4-7M adicionales» = indicadores 31 y 32. El 95,3% de MP/costos del plan (diap. 6) es un valor plan: no cambiarlo sin definir la fuente oficial del plan (sección 4 de «CONTROLES Y PPT»). Rotular el año 1 como «real a &lt;mes&gt; + proyección».</t>
         </is>
       </c>
       <c r="F87" s="367" t="inlineStr">
         <is>
-          <t>Cada cifra del PPT = celda de la sección 2 o 3.</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="43.6" customHeight="1">
+          <t>Cada cifra del PPT = celda de la sección 2 o 3 de «CONTROLES Y PPT».</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="96.4" customHeight="1">
       <c r="B88" s="370" t="inlineStr">
         <is>
           <t>G4</t>
@@ -49679,7 +49679,7 @@
       </c>
       <c r="E88" s="367" t="inlineStr">
         <is>
-          <t>Usar el valor calculado de la sección 2 (inversión propia 6,4 años: se recupera durante el año 7), no el texto del Dashboard. Indicar el criterio: dividendos descontados a Ke.</t>
+          <t>Usar el valor calculado de la sección 2 de «CONTROLES Y PPT» (indicador 38: hoy 6,4 años; se recupera durante el año 7), no el texto del Dashboard. Actualizar también la diferencia contra el plan («(+3)»; plan = 3 años, sección 4 de «CONTROLES Y PPT») y la frase de la conclusión «extienden el Payback de inversión propia en 3 años más». En la nota «El Payback es considerado desde el año 6…», indicar el criterio del modelo: dividendos descontados a Ke (16,32%) contra el aporte propio (USD 606.000), con dividendos desde 2031 (año 6).</t>
         </is>
       </c>
       <c r="F88" s="367" t="inlineStr">
@@ -49688,7 +49688,7 @@
         </is>
       </c>
     </row>
-    <row r="89" ht="162.4" customHeight="1">
+    <row r="89" ht="228.4" customHeight="1">
       <c r="B89" s="370" t="inlineStr">
         <is>
           <t>G5</t>
@@ -49706,7 +49706,7 @@
       </c>
       <c r="E89" s="367" t="inlineStr">
         <is>
-          <t>El libro no tiene cálculo de sensibilidad. Para cada variable, en una COPIA: aplicar el cambio (precio: Ej_Ingresos!L8:N18 y R8:AC18 × 1,05; costo de MP: Ej_Costos!L9:N19 y R9:AC19 × 1,05; volumen: Ej_Producción L22:N32, L37:N47, R22:AC32 y R37:AC47 × 1,10; cobranza: Supuestos!B80 = 60 y desfase de 2 meses en Ej_Flujo fila 6), anotar VAN-TIR!C24 y restar el VAN base. Atención: una réplica del modelo da ≈ ±USD 5,9M de VAN por ±5% de precio y ≈ ∓USD 5,2M por ±5% de MP, muy por encima de lo que muestra la diapositiva de junio (±1,2M y ±1,0M). Tasa CP +2% y tipo de cambio ±10%: con este libro el VAN no cambia (el interés CP no entra al VAN y las proyecciones están en USD); informar ≈ 0 en VAN y, si se quiere mostrar, el efecto en la utilidad neta acumulada y en la caja (la tasa CP exige cambiar el 8% de cada fórmula de Ej_Flujo fila 17). Aplicar los cambios a todos los meses posteriores al corte (con corte a setiembre, L:N).</t>
+          <t>El libro no tiene cálculo de sensibilidad. Para cada variable, en una COPIA del libro ya actualizado, aplicar el cambio a todos los meses posteriores al corte (con corte a setiembre: L:N de 2026 y R:AC de 2027; los años 3-10 se ajustan solos porque parten de 2027; si se usaron Prosp_Tn o Prosp_Precio, aplicar el mismo factor en esas hojas): precio, Ej_Ingresos!L8:N18 y R8:AC18 × 1,05; costo de MP, Ej_Costos!L9:N19 y R9:AC19 × 1,05; volumen, Ej_Producción!L22:N32, L37:N47, R22:AC32 y R37:AC47 × 1,10; cobranza, Supuestos!B80 = 60 (el VAN toma el capital de trabajo de la hoja Capital Trabajo y no depende de Ej_Flujo: no hace falta cambiar el desfase de la fila 6). Anotar VAN-TIR!C24 y restar el VAN base. Atención: con los datos actuales y este método, el VAN cambia ≈ ±USD 5,8M por ±5% de precio (≈ ±5,9M si el cambio se aplica a todo el año 1) y ≈ ∓USD 5,2M por ±5% de MP, muy por encima de lo que muestra la diapositiva de junio (±1,2M y ±1,0M); con un precio 5% menor, el VAN sería negativo (≈ −USD 3,0M). Tasa CP +2% y tipo de cambio ±10%: con este libro el VAN no cambia (el interés CP no entra al VAN y las proyecciones están en USD); informar ≈ 0 en VAN y, si se quiere mostrar, el efecto en la utilidad neta acumulada y en la caja (la tasa CP exige cambiar el 8% de cada fórmula de Ej_Flujo fila 17).</t>
         </is>
       </c>
       <c r="F89" s="367" t="inlineStr">
@@ -49930,6 +49930,7 @@
     <hyperlink ref="D80" location="'VAN-TIR'!C22" tooltip="Ir a 'VAN-TIR'!C22"/>
     <hyperlink ref="D85" location="'CONTROLES Y PPT'!B79" tooltip="Ir a 'CONTROLES Y PPT'!B79"/>
     <hyperlink ref="D86" location="'CONTROLES Y PPT'!B36" tooltip="Ir a 'CONTROLES Y PPT'!B36"/>
+    <hyperlink ref="D81" location="'PASO A PASO'!B92" tooltip="Ir al registro de actualizaciones"/>
   </hyperlinks>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" fitToHeight="0"/>

--- a/alianza/Informe_Financiero_ALIANZA_DEL_ACERO_INFORME2_09062026_AJUSTADO_A_10_AÑOS_CON_GUIA.xlsx
+++ b/alianza/Informe_Financiero_ALIANZA_DEL_ACERO_INFORME2_09062026_AJUSTADO_A_10_AÑOS_CON_GUIA.xlsx
@@ -45062,7 +45062,7 @@
       </c>
       <c r="H47" s="342" t="inlineStr">
         <is>
-          <t>Diap. 2 y 4 («39% del Plan»).</t>
+          <t>Diap. 2 y 4 («39% del Plan»; la diap. 4 dice además «61% inferior al Plan» = 1 − este valor).</t>
         </is>
       </c>
       <c r="I47" s="342"/>
@@ -45491,7 +45491,7 @@
       <c r="N58" s="342"/>
       <c r="O58" s="342"/>
     </row>
-    <row r="59" ht="17.2" customHeight="1">
+    <row r="59" ht="30.4" customHeight="1">
       <c r="B59" s="344">
         <v>22</v>
       </c>
@@ -45518,7 +45518,7 @@
       </c>
       <c r="H59" s="342" t="inlineStr">
         <is>
-          <t>Diap. 6. Plan en el libro: Ej_Costos!AE22/AE44 = 96,45% (el PPT dice 95,3%).</t>
+          <t>Diap. 6 (tabla «96.1%» y texto «&gt;96% de los costos variables»), 11 y 13 («&gt;96% de costos variables»). Plan en el libro: Ej_Costos!AE22/AE44 = 96,45% (el PPT dice 95,3%).</t>
         </is>
       </c>
       <c r="I59" s="342"/>
@@ -45936,7 +45936,7 @@
       </c>
       <c r="H70" s="342" t="inlineStr">
         <is>
-          <t>Diap. 8, 11 y 13 («USD 5-11,9M/año»). Hoy el año 7 es 4,0M.</t>
+          <t>Diap. 8 («USD 5-11.9M/año»), 11 y 13 («USD 5-12M/año»); el máximo también va en la diap. 2 («hasta USD 11.9M/año»). Hoy el año 7 es 4,0M.</t>
         </is>
       </c>
       <c r="I70" s="342"/>
@@ -48059,7 +48059,7 @@
       </c>
       <c r="C10" s="367" t="inlineStr">
         <is>
-          <t>Escribir solo en las celdas indicadas. No escribir en columnas de total o promedio (O y AD de Ej_Producción, Ej_Ingresos, Ej_Costos, Ej_Resultados y Ej_Deuda; O, AB, AO, BB, BO, CB, CO, DB, DO, EB y EF de Ej_Flujo), salvo las celdas que un paso indica expresamente: Ej_Producción!O31:O32 y O46:O47 (B4), Ej_Costos!O9:O19 y AD9:AD19 (B5), Ej_Costos!O1 (D2) y Ej_Flujo!O37 y O40 (E2). Tampoco en el plan original (columnas P y AE de esas cinco hojas; columna E de Supuestos). En Ej_Flujo no hay columnas de plan: P, AD y AE son meses (ene-2027, feb-2028 y mar-2028) y se editan cuando un paso lo indica. El auxiliar Ej_Costos!O88:P114 (paso D5) no es plan ni total.</t>
+          <t>Escribir solo en las celdas indicadas. No escribir en columnas de total o promedio (O y AD de Ej_Producción, Ej_Ingresos, Ej_Costos, Ej_Resultados y Ej_Deuda; O, AB, AO, BB, BO, CB, CO, DB, DO, EB y EF de Ej_Flujo), salvo las celdas que un paso indica expresamente: Ej_Producción!O31:O32 y O46:O47 (B4), Ej_Costos!O9:O19 y AD9:AD19 (B5), Ej_Costos!O1 (D2) y Ej_Flujo!O37 y O40 (E2). Tampoco en el plan original (columnas P y AE de esas cinco hojas, salvo el rótulo Ej_Costos!P1, que se actualiza en el paso D2; columna E de Supuestos). En Ej_Flujo no hay columnas de plan: P, AD y AE son meses (ene-2027, feb-2028 y mar-2028) y se editan cuando un paso lo indica. El auxiliar Ej_Costos!O88:P114 (paso D5) no es plan ni total.</t>
         </is>
       </c>
       <c r="D10" s="367"/>
@@ -48376,7 +48376,7 @@
       </c>
       <c r="F30" s="367" t="inlineStr">
         <is>
-          <t>Los nombres del libro y del PPT indican versión y fecha.</t>
+          <t>El nombre del libro indica versión y fecha (y, antes de empezar la fase G, también el del PPT).</t>
         </is>
       </c>
     </row>
@@ -49780,7 +49780,7 @@
         </is>
       </c>
     </row>
-    <row r="94" ht="30.4" customHeight="1">
+    <row r="94" ht="43.6" customHeight="1">
       <c r="B94" s="369">
         <v>0</v>
       </c>
@@ -49796,7 +49796,7 @@
       </c>
       <c r="E94" s="367" t="inlineStr">
         <is>
-          <t>Versión base usada en el PPT «Plan vs Actualizado 10 años» de junio 2026. Guía y controles agregados el 13/10/2026 sin modificar el modelo.</t>
+          <t>Versión base usada en el PPT «Plan vs Actualizado 10 años» de junio 2026. Guía y controles agregados el 13/10/2026 y actualizados el 16/10/2026, sin modificar el modelo.</t>
         </is>
       </c>
       <c r="F94" s="367" t="inlineStr">
